--- a/cache/open_items_2026-06-20.xlsx
+++ b/cache/open_items_2026-06-20.xlsx
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>SIGLOG-VERIFY-MON</t>
+          <t>MODE-4</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -1136,22 +1136,22 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Data Integrity</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Confirm SIGLOG-ORDER-FIX end-to-end on a live scan</t>
+          <t>Walk-forward validation of Phase-3 per-mode pillar weights</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>The signal_log ordering fix (SIGLOG-ORDER-FIX) is verified statically but not yet on a live post-fix scan (weekend quota gate blocked running one).</t>
+          <t>MODE-3 shipped intuition-based pillar weights without backtest evidence (principle 7 override). Need walk-forward validation that the per-mode weights don't degrade vs the single-set baseline.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Added scripts/verify_signal_log_fix.py + launchd com.swingtrade.siglog-verify (Mon 7:30am PT, after the 6:30 scan) — compares signal_log BUYs vs canonical bundle BUYs + flags sub-60 leakage, posts result to Slack (PASS=INFO/MISMATCH=WARN). Recurring weekly = ongoing regression guard. Awaiting Monday 2026-06-22 run.</t>
+          <t>scripts/validate_per_mode_weights.py: runs baseline backtest + 3 mode-weighted backtests (252d, min_score=50), compares WR/PF/maxDD/Sharpe per mode. Revert criterion: any mode ≤1.0× PF or ≤-5pp WR vs baseline → flip per_mode_pillar_reweight._enabled to false. See docs/per_mode_decisions_roadmap.md Phase 3.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -1166,13 +1166,13 @@
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="8" t="inlineStr"/>
     </row>
-    <row r="12" ht="75" customHeight="1">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>MODE-4</t>
+          <t>SCALE-1</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -1182,22 +1182,22 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Deployment · 500-user</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward validation of Phase-3 per-mode pillar weights</t>
+          <t>Multi-worker server + concurrency load test</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>MODE-3 shipped intuition-based pillar weights without backtest evidence (principle 7 override). Need walk-forward validation that the per-mode weights don't degrade vs the single-set baseline.</t>
+          <t>Single uvicorn worker (uvicorn.run, no workers=); CPU-bound paths (65MB ML-file parse, scoring) block the event loop; untested at 500 concurrent on one Cloudflare tunnel</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>scripts/validate_per_mode_weights.py: runs baseline backtest + 3 mode-weighted backtests (252d, min_score=50), compares WR/PF/maxDD/Sharpe per mode. Revert criterion: any mode ≤1.0× PF or ≤-5pp WR vs baseline → flip per_mode_pillar_reweight._enabled to false. See docs/per_mode_decisions_roadmap.md Phase 3.</t>
+          <t>gunicorn/uvicorn --workers N (or app server), profile + offload blocking calls, run a 500-concurrent load test before certifying</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -1212,13 +1212,13 @@
       <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="8" t="inlineStr"/>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="75" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>SCALE-1</t>
+          <t>PARITY-PAPER-TRADING-RT</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -1228,22 +1228,22 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Deployment · 500-user</t>
+          <t>Execution / Paper / Platform Parity</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Multi-worker server + concurrency load test</t>
+          <t>Real-Time Paper Trading</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Single uvicorn worker (uvicorn.run, no workers=); CPU-bound paths (65MB ML-file parse, scoring) block the event loop; untested at 500 concurrent on one Cloudflare tunnel</t>
+          <t>Execute simulated trades against live market prices via the Alpaca paper account; track fills, slippage and PnL in real time so paper validation mirrors what live trading would look like.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>gunicorn/uvicorn --workers N (or app server), profile + offload blocking calls, run a 500-concurrent load test before certifying</t>
+          <t>Extend executor.py to route signals through the Alpaca paper REST + websocket API; webhook fills back into cache/portfolio.json; expose a 'Paper Trade' toggle on the Trade Plan card. Partially built (executor.py --submit), needs always-on wrapper.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -1258,13 +1258,13 @@
       <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="8" t="inlineStr"/>
     </row>
-    <row r="14" ht="75" customHeight="1">
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>PARITY-PAPER-TRADING-RT</t>
+          <t>REGIME-CONDITIONAL-MODELS</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -1274,22 +1274,22 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Execution / Paper / Platform Parity</t>
+          <t>ML / Accuracy</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Real-Time Paper Trading</t>
+          <t>Regime-conditional ML models (principle 5)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Execute simulated trades against live market prices via the Alpaca paper account; track fills, slippage and PnL in real time so paper validation mirrors what live trading would look like.</t>
+          <t>train separate direction models per regime instead of one spanning all; #1 accuracy lever</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Extend executor.py to route signals through the Alpaca paper REST + websocket API; webhook fills back into cache/portfolio.json; expose a 'Paper Trade' toggle on the Trade Plan card. Partially built (executor.py --submit), needs always-on wrapper.</t>
+          <t>ml/train.py regime split</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>REGIME-CONDITIONAL-MODELS</t>
+          <t>OPS-1</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -1320,27 +1320,39 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>ML / Accuracy</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional ML models (principle 5)</t>
+          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>train separate direction models per regime instead of one spanning all; #1 accuracy lever</t>
+          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>ml/train.py regime split</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr"/>
+          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2 min</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Win: cleaner repo.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Calendar reminder for 2026-05-16.</t>
+        </is>
+      </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1348,15 +1360,19 @@
       </c>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16" ht="45" customHeight="1">
+      <c r="N15" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>OPS-1</t>
+          <t>QUOTA-WEEKDAY-CADENCE</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1366,39 +1382,27 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
+          <t>Restore daily scan to spec'd 5x/day (was 16x drift)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
+          <t>daily plist fired run_daily_scan.sh 16x/day (1 heavy + light every 30min) but docs/bullveda_refresh_spec.md line 156 + the script header both specify '1 heavy + 4 light/day'. The 16x was undocumented drift; its cost model ('~250 net/light scan, ~8K/day') was wrong — cold-cache light scans hit ~1042 net + intraday billed-units, feeding the 96-100% quota days.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2 min</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Win: cleaner repo.</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>Calendar reminder for 2026-05-16.</t>
-        </is>
-      </c>
+          <t>Edited infra/launchd/com.swingtrade.daily.plist StartCalendarInterval 16-&gt;5 slots (05:15 heavy + 07:00/09:30/11:30/13:30 light), deployed to ~/Library/LaunchAgents + launchctl reload (verified 5 slots active). Scores/setups/RVOL now refresh ~every 2h intraday (ample for 2-5d swings; live price still ticks via Schwab tape). Reversible: restore 16 slots + reload.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1406,19 +1410,15 @@
       </c>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr">
-        <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
+      <c r="N16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17" ht="105" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>QUOTA-WEEKDAY-CADENCE</t>
+          <t>QUOTA-WEEKEND-GATE</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -1433,17 +1433,17 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Restore daily scan to spec'd 5x/day (was 16x drift)</t>
+          <t>Weekend/holiday gate on EODHD scan stack</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>daily plist fired run_daily_scan.sh 16x/day (1 heavy + light every 30min) but docs/bullveda_refresh_spec.md line 156 + the script header both specify '1 heavy + 4 light/day'. The 16x was undocumented drift; its cost model ('~250 net/light scan, ~8K/day') was wrong — cold-cache light scans hit ~1042 net + intraday billed-units, feeding the 96-100% quota days.</t>
+          <t>EODHD daily quota chronically hot (06-08 maxed 100%, 06-12/06-13 96%); root cause = scan/snapshot jobs (daily 16x, premarket-scan 10x, morning-briefing, rolling-tail 45x, ticker-snapshots 25x) had NO weekday restriction, so they ran full 1078-ticker x14-endpoint enrichment on weekends with no new market data. full-enrich-weekly also runs Sat 17:00 (=00:00 UTC reset, by design).</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Edited infra/launchd/com.swingtrade.daily.plist StartCalendarInterval 16-&gt;5 slots (05:15 heavy + 07:00/09:30/11:30/13:30 light), deployed to ~/Library/LaunchAgents + launchctl reload (verified 5 slots active). Scores/setups/RVOL now refresh ~every 2h intraday (ample for 2-5d swings; live price still ticks via Schwab tape). Reversible: restore 16 slots + reload.</t>
+          <t>Script-level weekend+holiday guards (no launchctl reload needed): run_daily_scan.sh direct guard + launchd_wrapper.sh WEEKDAY_ONLY allowlist; both skip Sat/Sun (date +%u&gt;=6) and US market holidays (seasonality.is_market_holiday, fail-open). Gates 5 jobs, leaves ~60 untouched. Verified: gated jobs skip, edgar/corporate-events still run. Weekday cadence bloat (daily 16x vs script-intended 5x) is separate Tier-2 item.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -1458,13 +1458,13 @@
       <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="8" t="inlineStr"/>
     </row>
-    <row r="18" ht="105" customHeight="1">
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>QUOTA-WEEKEND-GATE</t>
+          <t>SCHWAB-REAUTH-PENDING</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -1474,22 +1474,22 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Ops / Schwab (operational)</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Weekend/holiday gate on EODHD scan stack</t>
+          <t>Schwab re-auth to unlock option Greeks</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>EODHD daily quota chronically hot (06-08 maxed 100%, 06-12/06-13 96%); root cause = scan/snapshot jobs (daily 16x, premarket-scan 10x, morning-briefing, rolling-tail 45x, ticker-snapshots 25x) had NO weekday restriction, so they ran full 1078-ticker x14-endpoint enrichment on weekends with no new market data. full-enrich-weekly also runs Sat 17:00 (=00:00 UTC reset, by design).</t>
+          <t>refresh token expired (invalid_grant, 7-day). Run python3 schwab_auth.py oauth -&gt; real option premiums/Greeks flow into the Options calc (currently honest BS-model fallback).</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Script-level weekend+holiday guards (no launchctl reload needed): run_daily_scan.sh direct guard + launchd_wrapper.sh WEEKDAY_ONLY allowlist; both skip Sat/Sun (date +%u&gt;=6) and US market holidays (seasonality.is_market_holiday, fail-open). Gates 5 jobs, leaves ~60 untouched. Verified: gated jobs skip, edgar/corporate-events still run. Weekday cadence bloat (daily 16x vs script-intended 5x) is separate Tier-2 item.</t>
+          <t>user action: schwab_auth.py oauth</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>SCHWAB-REAUTH-PENDING</t>
+          <t>QUANT-5</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -1520,27 +1520,39 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Ops / Schwab (operational)</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Schwab re-auth to unlock option Greeks</t>
+          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>refresh token expired (invalid_grant, 7-day). Run python3 schwab_auth.py oauth -&gt; real option premiums/Greeks flow into the Options calc (currently honest BS-model fallback).</t>
+          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>user action: schwab_auth.py oauth</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr"/>
+          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Caveat: exploratory research, not config-tuning.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
+        </is>
+      </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1548,15 +1560,19 @@
       </c>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
-    </row>
-    <row r="20" ht="60" customHeight="1">
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>QUANT-5</t>
+          <t>KILL-TO-LABEL-2026-06-11</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -1566,39 +1582,27 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Signal quality</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
+          <t>Convert setup kills to honest labels + regime edge tier</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
+          <t>Setup-level kills (universal_setup_multiplier 0.0x VCP/Pocket Pivot) hid signals; composite score anti-predictive (r=-0.10). Convert kills-&gt;labels (signal stays visible BUY) + add honest regime-conditional edge_tier (PROVEN/DEVELOPING/WEAK/UNPROVEN) from picks_history realized PF.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>Caveat: exploratory research, not config-tuning.</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
-        </is>
-      </c>
+          <t>Phase 1: signal_edge_labeling.mode=label in config; analysis.py emits edge_warning instead of zeroing score; swing_trade.py feeds empty kill-lists in label mode. Phase 2: edge_labels.py computes (family x coarse-regime) tier from picks_history, wired into scan, surfaced via /api/universe + BullVeda scan-column badge/chip. Survival rails untouched. Reversible via mode=suppress.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
       <c r="K20" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1606,19 +1610,15 @@
       </c>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="8" t="inlineStr">
-        <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="90" customHeight="1">
+      <c r="N20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21" ht="165" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>KILL-TO-LABEL-2026-06-11</t>
+          <t>TV-RATING-CROSS-CHECK</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -1628,27 +1628,39 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Signal quality</t>
+          <t>Signals / Cross-Check</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Convert setup kills to honest labels + regime edge tier</t>
+          <t>Validate (or zero out) the ±3 TV-rating tech-score bonus</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Setup-level kills (universal_setup_multiplier 0.0x VCP/Pocket Pivot) hid signals; composite score anti-predictive (r=-0.10). Convert kills-&gt;labels (signal stays visible BUY) + add honest regime-conditional edge_tier (PROVEN/DEVELOPING/WEAK/UNPROVEN) from picks_history realized PF.</t>
+          <t>DISCOVERY 2026-05-11: TV-rating ±3 score bonus has been live in analysis.py:8627 for some time, modifying every BUY signal's technical pillar score. NO _validations entry, NO Wilson-CI, NO walk-forward justification for the ±3 magnitude. Worse: tv_rating was never captured on the 689 closed trades in picks_history or 1,301 signal_log entries — retroactive validation is impossible. Violates Principle 1 (n&lt;30 refusal) + Principle 7 (no knob-tweaking without evidence).</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Phase 1: signal_edge_labeling.mode=label in config; analysis.py emits edge_warning instead of zeroing score; swing_trade.py feeds empty kill-lists in label mode. Phase 2: edge_labels.py computes (family x coarse-regime) tier from picks_history, wired into scan, surfaced via /api/universe + BullVeda scan-column badge/chip. Survival rails untouched. Reversible via mode=suppress.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr"/>
+          <t>Phase 1 (SHIPPED 2026-05-11): (a) tv_bonus zeroed in analysis.py:8627 — score no longer mutated; (b) tv_recommendation + tv_rec_value + buy/sell/neutral counts now logged per signal in signal_tracker.log_signals() so prospective evidence accumulates; (c) tv_rating still surfaced in tech['details'] as INFORMATIONAL only — no score impact. Phase 2 (PENDING n&gt;=30, est. 6-12 weeks): run Wilson-LB(BUY|TV STRONG_BUY) vs Wilson-LB(BUY) over the prospectively-logged signals. If the agreement-conditional Wilson-LB beats unconditional by a meaningful margin (&gt;=3pp), re-enable with a magnitude justified by the regression. If not, kill the cross-check permanently (Principle 4 falsification — do not retune, do not lower the threshold).</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Phase 1: hours (done). Phase 2: hours of analysis + calendar wait for n&gt;=30.</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Mechanism (Principle 2): TV rating is an independent server-side aggregation of ~26 indicators. Two independent technical aggregations may improve precision over our 5-pillar score alone. Falsification (Principle 4): if agreement-conditional Wilson-LB &lt;= unconditional after n&gt;=30, the cross-check has no edge — kill, don't retune. Risk of CURRENT state (Phase 1): we have been over-weighting TV-STRONG_BUY signals by +3 tech-pts with zero evidence; this could have systematically biased BUY selection. Capping at 0 removes that bias going forward but does not undo past trade selection bias.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Default apply_to_score=false locked. Validation requires logged tv_rating on &gt;=30 CLOSED BUY trades (currently 0). Earliest Phase-2 validation window: ~6-12 weeks of scans from 2026-05-11. Pairs with the v2 dashboard TV sub-tab (infra/prototype/subtabs/tv/) which is iframe-only today. Do NOT add per-mode / per-regime elaboration until Phase 2 evidence justifies even the basic bonus.</t>
+        </is>
+      </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1656,15 +1668,19 @@
       </c>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr"/>
-    </row>
-    <row r="22" ht="165" customHeight="1">
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1 smoke: run python3 swing_trade.py and confirm (1) tech['details']['tv_rating'] still appears in deep-dive output labeled 'informational — bonus disabled pending validation'; (2) signal_log.json entries for new scans contain tv_recommendation + tv_rec_value + buy/sell/neutral_count populated. Phase 2 trigger: when `python3 -c 'import json; print(sum(1 for r in json.load(open("data/signal_log.json")) if r.get("tv_recommendation") and r.get("result")))'` &gt;= 30, run the agreement-conditional Wilson-LB analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>TV-RATING-CROSS-CHECK</t>
+          <t>TEST-MAE-MFE</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -1674,39 +1690,27 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Signals / Cross-Check</t>
+          <t>Testing / Validation (Tier 1)</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Validate (or zero out) the ±3 TV-rating tech-score bonus</t>
+          <t>MAE / MFE Analyzer — tune stops + targets from data</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>DISCOVERY 2026-05-11: TV-rating ±3 score bonus has been live in analysis.py:8627 for some time, modifying every BUY signal's technical pillar score. NO _validations entry, NO Wilson-CI, NO walk-forward justification for the ±3 magnitude. Worse: tv_rating was never captured on the 689 closed trades in picks_history or 1,301 signal_log entries — retroactive validation is impossible. Violates Principle 1 (n&lt;30 refusal) + Principle 7 (no knob-tweaking without evidence).</t>
+          <t>Maximum Adverse Excursion vs Maximum Favorable Excursion analyzer. signal_log.json already tracks mae_pct + mfe_pct for closed trades. Output: 'Stops triggered at -5% on winners that later hit +20% → stops too tight' or 'Trades exited at +6% target left avg +12% on table → targets too conservative'. Directly improves trade-plan math.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (SHIPPED 2026-05-11): (a) tv_bonus zeroed in analysis.py:8627 — score no longer mutated; (b) tv_recommendation + tv_rec_value + buy/sell/neutral counts now logged per signal in signal_tracker.log_signals() so prospective evidence accumulates; (c) tv_rating still surfaced in tech['details'] as INFORMATIONAL only — no score impact. Phase 2 (PENDING n&gt;=30, est. 6-12 weeks): run Wilson-LB(BUY|TV STRONG_BUY) vs Wilson-LB(BUY) over the prospectively-logged signals. If the agreement-conditional Wilson-LB beats unconditional by a meaningful margin (&gt;=3pp), re-enable with a magnitude justified by the regression. If not, kill the cross-check permanently (Principle 4 falsification — do not retune, do not lower the threshold).</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Phase 1: hours (done). Phase 2: hours of analysis + calendar wait for n&gt;=30.</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>Mechanism (Principle 2): TV rating is an independent server-side aggregation of ~26 indicators. Two independent technical aggregations may improve precision over our 5-pillar score alone. Falsification (Principle 4): if agreement-conditional Wilson-LB &lt;= unconditional after n&gt;=30, the cross-check has no edge — kill, don't retune. Risk of CURRENT state (Phase 1): we have been over-weighting TV-STRONG_BUY signals by +3 tech-pts with zero evidence; this could have systematically biased BUY selection. Capping at 0 removes that bias going forward but does not undo past trade selection bias.</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>Default apply_to_score=false locked. Validation requires logged tv_rating on &gt;=30 CLOSED BUY trades (currently 0). Earliest Phase-2 validation window: ~6-12 weeks of scans from 2026-05-11. Pairs with the v2 dashboard TV sub-tab (infra/prototype/subtabs/tv/) which is iframe-only today. Do NOT add per-mode / per-regime elaboration until Phase 2 evidence justifies even the basic bonus.</t>
-        </is>
-      </c>
+          <t>Read signal_log.json closed entries; scatter-plot mae vs realized PnL + mfe vs realized PnL; quantile bins (10/25/50/75/90); render as a new Testing tab card. Effort ~30min — data already there.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1714,11 +1718,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="3" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr">
-        <is>
-          <t>Phase 1 smoke: run python3 swing_trade.py and confirm (1) tech['details']['tv_rating'] still appears in deep-dive output labeled 'informational — bonus disabled pending validation'; (2) signal_log.json entries for new scans contain tv_recommendation + tv_rec_value + buy/sell/neutral_count populated. Phase 2 trigger: when `python3 -c 'import json; print(sum(1 for r in json.load(open("data/signal_log.json")) if r.get("tv_recommendation") and r.get("result")))'` &gt;= 30, run the agreement-conditional Wilson-LB analysis.</t>
-        </is>
-      </c>
+      <c r="N22" s="8" t="inlineStr"/>
     </row>
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="2" t="n">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>TEST-MAE-MFE</t>
+          <t>TEST-MC-BOOTSTRAP</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -1741,17 +1741,17 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>MAE / MFE Analyzer — tune stops + targets from data</t>
+          <t>Monte Carlo Bootstrap — confidence intervals on Sharpe/PF/WR</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Maximum Adverse Excursion vs Maximum Favorable Excursion analyzer. signal_log.json already tracks mae_pct + mfe_pct for closed trades. Output: 'Stops triggered at -5% on winners that later hit +20% → stops too tight' or 'Trades exited at +6% target left avg +12% on table → targets too conservative'. Directly improves trade-plan math.</t>
+          <t>Randomly resample closed trades 10,000x to build distributions over each metric. Wilson LB only covers WR; this covers Sharpe, Sortino, PF, max-DD, hit-rate, payoff ratio. Output: 'Sharpe 1.42, 95% CI [0.88, 1.94]' — you would know whether 1.42 is robust or noise. Standard hedge-fund metric, supports principle #1 (statistical rigor).</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Read signal_log.json closed entries; scatter-plot mae vs realized PnL + mfe vs realized PnL; quantile bins (10/25/50/75/90); render as a new Testing tab card. Effort ~30min — data already there.</t>
+          <t>Numpy bootstrap on signal_log trade PnL array, k=10000 resamples; compute distributions over each metric; render percentile bands. Effort 1-2hr.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>TEST-MC-BOOTSTRAP</t>
+          <t>TEST-PERMUTATION</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -1787,17 +1787,17 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Monte Carlo Bootstrap — confidence intervals on Sharpe/PF/WR</t>
+          <t>Permutation Test — is the edge REAL or coin flip?</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Randomly resample closed trades 10,000x to build distributions over each metric. Wilson LB only covers WR; this covers Sharpe, Sortino, PF, max-DD, hit-rate, payoff ratio. Output: 'Sharpe 1.42, 95% CI [0.88, 1.94]' — you would know whether 1.42 is robust or noise. Standard hedge-fund metric, supports principle #1 (statistical rigor).</t>
+          <t>Randomly shuffle BUY/SELL/AVOID labels on historical signals 1000x, recompute strategy returns. If real returns are not significantly better than scrambled returns, there is no edge. Direct test of principle #4 (adversarial mindset / falsification). Output: 'Real strategy: +18.7%. Random labels (1000 sims): +0.2% +/- 4.1%. p-value: 0.0001'.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Numpy bootstrap on signal_log trade PnL array, k=10000 resamples; compute distributions over each metric; render percentile bands. Effort 1-2hr.</t>
+          <t>Shuffle decision-column of signal_log 1000x; recompute portfolio return per shuffle; rank real return vs null distribution; report p-value. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>TEST-PERMUTATION</t>
+          <t>TEST-REGIME-COND</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -1833,17 +1833,17 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Permutation Test — is the edge REAL or coin flip?</t>
+          <t>Regime-Conditional Performance — where does it work?</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Randomly shuffle BUY/SELL/AVOID labels on historical signals 1000x, recompute strategy returns. If real returns are not significantly better than scrambled returns, there is no edge. Direct test of principle #4 (adversarial mindset / falsification). Output: 'Real strategy: +18.7%. Random labels (1000 sims): +0.2% +/- 4.1%. p-value: 0.0001'.</t>
+          <t>Partition closed trades by regime (risk_on_trending / choppy / risk_off / panic) and compute WR / PF / Sharpe per regime. Per principle #5 (regime conditioning over averages). Example output: 'Trend Continuation WR: 41% overall · 62% in risk_on_trending · 18% in choppy'. Tells you which sleeves to size up/down per regime.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Shuffle decision-column of signal_log 1000x; recompute portfolio return per shuffle; rank real return vs null distribution; report p-value. Effort ~1hr.</t>
+          <t>Group signal_log entries by regime_at_signal (already logged); compute Wilson LB on WR + bootstrapped PF/Sharpe per regime; output a (setup x regime) heatmap. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -1858,38 +1858,38 @@
       <c r="M25" s="3" t="inlineStr"/>
       <c r="N25" s="8" t="inlineStr"/>
     </row>
-    <row r="26" ht="90" customHeight="1">
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>TEST-REGIME-COND</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>PARITY-BACKTEST-UI</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Testing / Validation (Tier 1)</t>
+          <t>Backtesting / Platform Parity</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Regime-Conditional Performance — where does it work?</t>
+          <t>In-app Backtesting UI</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Partition closed trades by regime (risk_on_trending / choppy / risk_off / panic) and compute WR / PF / Sharpe per regime. Per principle #5 (regime conditioning over averages). Example output: 'Trend Continuation WR: 41% overall · 62% in risk_on_trending · 18% in choppy'. Tells you which sleeves to size up/down per regime.</t>
+          <t>Expose backtest.py + walk_forward_v2.py inside the kairos UI — a user picks a strategy/date range/universe and runs it without dropping to the terminal.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Group signal_log entries by regime_at_signal (already logged); compute Wilson LB on WR + bootstrapped PF/Sharpe per regime; output a (setup x regime) heatmap. Effort ~1hr.</t>
+          <t>Add a 'Backtest' workspace in the kairos sidebar; wire a form to a /v2/backtest endpoint that shells out to backtest.py and streams stdout via SSE; render Sharpe / PF / Wilson-LB / equity curve when the run completes.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>PARITY-BACKTEST-UI</t>
+          <t>BUG-MISSING-D1S</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Backtesting / Platform Parity</t>
+          <t>Bugs / Audit Ledger</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>In-app Backtesting UI</t>
+          <t>4 missing D1s for May 15 (out of 87)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Expose backtest.py + walk_forward_v2.py inside the kairos UI — a user picks a strategy/date range/universe and runs it without dropping to the terminal.</t>
+          <t>4 of 87 May-15 picks have null D1 (next-day close). Probably thin EODHD coverage on small-caps — acceptable noise band but worth confirming.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Add a 'Backtest' workspace in the kairos sidebar; wire a form to a /v2/backtest endpoint that shells out to backtest.py and streams stdout via SSE; render Sharpe / PF / Wilson-LB / equity curve when the run completes.</t>
+          <t>Identify the 4 tickers; check EODHD eod() response for each on 2026-05-16; if EODHD returned null, document as known-limitation; if EODHD returned a value, fix the ingest. Effort ~20min.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>BUG-MISSING-D1S</t>
+          <t>PARITY-CHANNEL-BAR</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -1966,22 +1966,22 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Bugs / Audit Ledger</t>
+          <t>Chart Indicators / Platform Parity</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>4 missing D1s for May 15 (out of 87)</t>
+          <t>Channel Bar overlay</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>4 of 87 May-15 picks have null D1 (next-day close). Probably thin EODHD coverage on small-caps — acceptable noise band but worth confirming.</t>
+          <t>Donchian / Keltner / Bollinger envelope overlay on the chart — top + bottom band with mid-line.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Identify the 4 tickers; check EODHD eod() response for each on 2026-05-16; if EODHD returned null, document as known-limitation; if EODHD returned a value, fix the ingest. Effort ~20min.</t>
+          <t>Compute channels via pandas-ta in feature_extractor.py (or live in chart.js using bar data); render as semi-transparent band; toggle in the Chart sub-tab control bar.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>PARITY-CHANNEL-BAR</t>
+          <t>PARITY-RBI-GBI-WINDOW</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Channel Bar overlay</t>
+          <t>RBI/GBI Window (regime bias bands)</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Donchian / Keltner / Bollinger envelope overlay on the chart — top + bottom band with mid-line.</t>
+          <t>Color-coded vertical bands on the chart timeline showing risk-on (green/GBI) vs risk-off (red/RBI) regime windows so the user can see at-a-glance whether prior price action happened in a hostile or friendly regime.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Compute channels via pandas-ta in feature_extractor.py (or live in chart.js using bar data); render as semi-transparent band; toggle in the Chart sub-tab control bar.</t>
+          <t>Read cache/regime_history.json and draw vertical color bands at each regime transition on the chart canvas; tooltip explains the regime classification (4-regime model: risk_on_trending / risk_on_choppy / risk_off_trending / panic).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -2042,13 +2042,13 @@
       <c r="M29" s="3" t="inlineStr"/>
       <c r="N29" s="8" t="inlineStr"/>
     </row>
-    <row r="30" ht="60" customHeight="1">
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>PARITY-RBI-GBI-WINDOW</t>
+          <t>CLEAN-HOT-SECTORS-DEAD</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -2058,22 +2058,22 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Chart Indicators / Platform Parity</t>
+          <t>Code Cleanup</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>RBI/GBI Window (regime bias bands)</t>
+          <t>panelHotSectors() dead-code in kairos.html</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Color-coded vertical bands on the chart timeline showing risk-on (green/GBI) vs risk-off (red/RBI) regime windows so the user can see at-a-glance whether prior price action happened in a hostile or friendly regime.</t>
+          <t>Hot Sectors panel was removed from the Signal Scanner grid but the panelHotSectors() function is still defined in kairos.html — dead code.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Read cache/regime_history.json and draw vertical color bands at each regime transition on the chart canvas; tooltip explains the regime classification (4-regime model: risk_on_trending / risk_on_choppy / risk_off_trending / panic).</t>
+          <t>grep for panelHotSectors callers; delete function + any unused helpers; verify no console errors. Effort ~2min.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-HOT-SECTORS-DEAD</t>
+          <t>CLEAN-4</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -2104,27 +2104,39 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>panelHotSectors() dead-code in kairos.html</t>
+          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Hot Sectors panel was removed from the Signal Scanner grid but the panelHotSectors() function is still defined in kairos.html — dead code.</t>
+          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>grep for panelHotSectors callers; delete function + any unused helpers; verify no console errors. Effort ~2min.</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
+          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>1 min</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Win: -X lines.</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Couples with OPS-1.</t>
+        </is>
+      </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -2132,15 +2144,19 @@
       </c>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="8" t="inlineStr"/>
-    </row>
-    <row r="32" ht="45" customHeight="1">
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-4</t>
+          <t>BREAKOUT-DISPLAY-1</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -2150,39 +2166,27 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
+          <t>Breakout fired vs coiled split</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
+          <t>Breakout Expansion family conflated 12 fired breakouts (cleared base+vol) with 134 coiled VCP bases (pivot overhead); reads as 225 breakouts when only 12 fired.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>1 min</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>Win: -X lines.</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>Couples with OPS-1.</t>
-        </is>
-      </c>
+          <t>Engine now emits breakout_state (fired/coiled/unconfirmed) + breakout_vol_ratio_50d per row. REMAINING: wire BullVeda display to split the family view and show the 50d gate ratio next to BREAKOUT tag.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
       <c r="K32" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -2190,19 +2194,15 @@
       </c>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="3" t="inlineStr"/>
-      <c r="N32" s="8" t="inlineStr">
-        <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="60" customHeight="1">
+      <c r="N32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33" ht="75" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>BREAKOUT-DISPLAY-1</t>
+          <t>STRUCT-LADDER-GATE-P2</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -2217,17 +2217,17 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Breakout fired vs coiled split</t>
+          <t>Phase 2: migrate BUY/AVOID R:R gate onto structural ladder</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Breakout Expansion family conflated 12 fired breakouts (cleared base+vol) with 134 coiled VCP bases (pivot overhead); reads as 225 breakouts when only 12 fired.</t>
+          <t>Phase 1 unified DISPLAY only; the verdict gate still computes R:R from decisions_by_mode (ATR). Displayed structural R:R can differ from the R:R that drove the verdict (e.g. NOW shows 0.73R while gate used 1.93R)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Engine now emits breakout_state (fired/coiled/unconfirmed) + breakout_vol_ratio_50d per row. REMAINING: wire BullVeda display to split the family view and show the 50d gate ratio next to BREAKOUT tag.</t>
+          <t>Migrate decision_engine R:R gate to structural target_engine R:R. HIGH RISK — re-decides BUY/WATCH/AVOID across 1800 names for 500+ users. Requires walk-forward (n&gt;=30/fold, holds across regimes) BEFORE shipping per feedback_signal_enable_bar_500users</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
@@ -2242,13 +2242,13 @@
       <c r="M33" s="3" t="inlineStr"/>
       <c r="N33" s="8" t="inlineStr"/>
     </row>
-    <row r="34" ht="75" customHeight="1">
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-LADDER-GATE-P2</t>
+          <t>DATA-FUTURE-EARNINGS-CAL-PIT</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -2258,22 +2258,22 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Data / Calendars (future)</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Phase 2: migrate BUY/AVOID R:R gate onto structural ladder</t>
+          <t>earnings_calendar_pit — point-in-time integrity</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 unified DISPLAY only; the verdict gate still computes R:R from decisions_by_mode (ATR). Displayed structural R:R can differ from the R:R that drove the verdict (e.g. NOW shows 0.73R while gate used 1.93R)</t>
+          <t>Earnings calendar with point-in-time integrity (what was expected when). Needed for clean PEAD backtest replay; today's calendar uses the most-recent snapshot only, which leaks future revisions into prior dates.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Migrate decision_engine R:R gate to structural target_engine R:R. HIGH RISK — re-decides BUY/WATCH/AVOID across 1800 names for 500+ users. Requires walk-forward (n&gt;=30/fold, holds across regimes) BEFORE shipping per feedback_signal_enable_bar_500users</t>
+          <t>Snapshot the EODHD earnings calendar daily into a versioned earnings_calendar_history table; join on (ticker, report_date, snapshot_date) for PIT correctness in PEAD backtests.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -2288,13 +2288,13 @@
       <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="8" t="inlineStr"/>
     </row>
-    <row r="35" ht="60" customHeight="1">
+    <row r="35" ht="45" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-EARNINGS-CAL-PIT</t>
+          <t>DATA-FUTURE-ECONOMIC-CAL</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -2309,17 +2309,17 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>earnings_calendar_pit — point-in-time integrity</t>
+          <t>economic_calendar — CPI/PCE/NFP/FOMC dates</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Earnings calendar with point-in-time integrity (what was expected when). Needed for clean PEAD backtest replay; today's calendar uses the most-recent snapshot only, which leaks future revisions into prior dates.</t>
+          <t>Macro event calendar with consensus expectations. No source wired today; the pre-FOMC sleeve uses hard-coded FOMC dates and there is no CPI/PCE/NFP awareness.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Snapshot the EODHD earnings calendar daily into a versioned earnings_calendar_history table; join on (ticker, report_date, snapshot_date) for PIT correctness in PEAD backtests.</t>
+          <t>Investing.com calendar scrape OR Trading Economics free tier; daily refresh; write to economic_calendar; feed pre-FOMC sleeve + risk_off blackout windows.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-ECONOMIC-CAL</t>
+          <t>DATA-FUTURE-FDA-CAL</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -2355,17 +2355,17 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>economic_calendar — CPI/PCE/NFP/FOMC dates</t>
+          <t>fda_calendar — PDUFA / AdCom dates</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Macro event calendar with consensus expectations. No source wired today; the pre-FOMC sleeve uses hard-coded FOMC dates and there is no CPI/PCE/NFP awareness.</t>
+          <t>FDA decision calendar (PDUFA dates, Advisory Committee meetings) for biotech catalyst tracking.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Investing.com calendar scrape OR Trading Economics free tier; daily refresh; write to economic_calendar; feed pre-FOMC sleeve + risk_off blackout windows.</t>
+          <t>FDA public calendar scrape + BiopharmCatalyst free RSS; write to fda_calendar; surface as catalyst tier in any biotech sleeve.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-FDA-CAL</t>
+          <t>DATA-EMPTY-SPLITS-CALENDAR</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -2396,22 +2396,22 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Data / Calendars (future)</t>
+          <t>Data / Corporate Actions (empty by sample)</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>fda_calendar — PDUFA / AdCom dates</t>
+          <t>splits_calendar — 0 splits in current universe sample</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>FDA decision calendar (PDUFA dates, Advisory Committee meetings) for biotech catalyst tracking.</t>
+          <t>corporate_actions table populates from EODHD but the current universe sample (449 tickers) had 0 splits in the recent window. Calendar reads empty.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>FDA public calendar scrape + BiopharmCatalyst free RSS; write to fda_calendar; surface as catalyst tier in any biotech sleeve.</t>
+          <t>Expand corporate-actions polling universe to S&amp;P 500 + Russell 1000 (universe list already available); 1-line change in the populator script.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-SPLITS-CALENDAR</t>
+          <t>DATA-EMPTY-MODEL-CALIBRATION</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -2442,22 +2442,22 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Data / Corporate Actions (empty by sample)</t>
+          <t>Data / ML (empty by design)</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>splits_calendar — 0 splits in current universe sample</t>
+          <t>model_calibration — waiting on realization</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>corporate_actions table populates from EODHD but the current universe sample (449 tickers) had 0 splits in the recent window. Calendar reads empty.</t>
+          <t>Calibration metrics table has no rows because the 5-20 day prediction horizons have not elapsed yet (today's predictions realize over 1-4 weeks).</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Expand corporate-actions polling universe to S&amp;P 500 + Russell 1000 (universe list already available); 1-line change in the populator script.</t>
+          <t>No code action; populates passively as time passes. Re-check after 2026-06-15 (30d post-shipping).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-MODEL-CALIBRATION</t>
+          <t>DATA-EMPTY-VAR-BREACHES</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -2488,22 +2488,22 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Data / ML (empty by design)</t>
+          <t>Data / Risk (empty by design)</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>model_calibration — waiting on realization</t>
+          <t>var_breaches — waiting on snapshots + drawdown</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Calibration metrics table has no rows because the 5-20 day prediction horizons have not elapsed yet (today's predictions realize over 1-4 weeks).</t>
+          <t>VaR breach log empty because (1) daily portfolio_risk snapshots are still ramping up and (2) no real drawdown day has happened to trigger a breach.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>No code action; populates passively as time passes. Re-check after 2026-06-15 (30d post-shipping).</t>
+          <t>No code action; populates passively. Re-check after first portfolio drawdown &gt;2% or after 60 daily snapshots.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -2518,13 +2518,13 @@
       <c r="M39" s="3" t="inlineStr"/>
       <c r="N39" s="8" t="inlineStr"/>
     </row>
-    <row r="40" ht="45" customHeight="1">
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-VAR-BREACHES</t>
+          <t>DATA-FUTURE-INSIDER-EDGAR</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -2534,22 +2534,22 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Data / Risk (empty by design)</t>
+          <t>Data / SEC EDGAR (future)</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>var_breaches — waiting on snapshots + drawdown</t>
+          <t>insider_transactions via Form 4 XBRL</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>VaR breach log empty because (1) daily portfolio_risk snapshots are still ramping up and (2) no real drawdown day has happened to trigger a breach.</t>
+          <t>Per-ticker insider buy/sell stream sourced direct from SEC Form 4 filings. Today sourced indirectly via Finviz Elite bulk; direct EDGAR is point-in-time accurate and free.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>No code action; populates passively. Re-check after first portfolio drawdown &gt;2% or after 60 daily snapshots.</t>
+          <t>Build Form 4 XBRL parser; daily ingest from efts.sec.gov; write to insider_transactions table; reconcile against Finviz bulk for cross-check.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -2564,13 +2564,13 @@
       <c r="M40" s="3" t="inlineStr"/>
       <c r="N40" s="8" t="inlineStr"/>
     </row>
-    <row r="41" ht="60" customHeight="1">
+    <row r="41" ht="45" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-INSIDER-EDGAR</t>
+          <t>DATA-FUTURE-INSTITUTIONAL-EDGAR</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>insider_transactions via Form 4 XBRL</t>
+          <t>institutional_holdings via 13F XBRL</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker insider buy/sell stream sourced direct from SEC Form 4 filings. Today sourced indirectly via Finviz Elite bulk; direct EDGAR is point-in-time accurate and free.</t>
+          <t>Per-ticker institutional ownership tracking (Form 13F, quarterly). Useful for the Smart Money pillar; today only Finviz inst_own_pct snapshot.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Build Form 4 XBRL parser; daily ingest from efts.sec.gov; write to insider_transactions table; reconcile against Finviz bulk for cross-check.</t>
+          <t>13F XBRL parser; quarterly ingest from EDGAR; write to institutional_holdings table with the 45-day reporting lag accounted for in any backtest joins.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-INSTITUTIONAL-EDGAR</t>
+          <t>DATA-FUTURE-CONGRESSIONAL-EDGAR</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -2626,22 +2626,22 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future)</t>
+          <t>Data / SEC EDGAR (future, alt for broken)</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>institutional_holdings via 13F XBRL</t>
+          <t>congressional_trades via EDGAR / House Clerk (alt source)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker institutional ownership tracking (Form 13F, quarterly). Useful for the Smart Money pillar; today only Finviz inst_own_pct snapshot.</t>
+          <t>Alternate sourcing for congressional trades after Senate Stock Watcher death (see DATA-BROKEN-CONGRESSIONAL-TRADES). Direct from House Clerk + Senate eFD.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>13F XBRL parser; quarterly ingest from EDGAR; write to institutional_holdings table with the 45-day reporting lag accounted for in any backtest joins.</t>
+          <t>Scrape House STOCK Act PTR PDFs (House Clerk site); Senate eFD JSON; merge into normalized congressional_trades table.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-CONGRESSIONAL-EDGAR</t>
+          <t>SUPABASE-SYNC-VERIFY</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -2672,22 +2672,22 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future, alt for broken)</t>
+          <t>Data / Supabase</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>congressional_trades via EDGAR / House Clerk (alt source)</t>
+          <t>Verify supabase_analysis_sync actually writes</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Alternate sourcing for congressional trades after Senate Stock Watcher death (see DATA-BROKEN-CONGRESSIONAL-TRADES). Direct from House Clerk + Senate eFD.</t>
+          <t>confirm sync_scan writes (psycopg2 raw SQL not .table API); not silent no-op</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Scrape House STOCK Act PTR PDFs (House Clerk site); Senate eFD JSON; merge into normalized congressional_trades table.</t>
+          <t>supabase_analysis_sync.py</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -2702,13 +2702,13 @@
       <c r="M43" s="3" t="inlineStr"/>
       <c r="N43" s="8" t="inlineStr"/>
     </row>
-    <row r="44" ht="45" customHeight="1">
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>SUPABASE-SYNC-VERIFY</t>
+          <t>DATA-EMPTY-PROD-ENGINE-DEFERRED</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -2718,22 +2718,22 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Data / Supabase</t>
+          <t>Data / Telemetry (deferred for safety)</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Verify supabase_analysis_sync actually writes</t>
+          <t>8 empty slots — production-engine touches deferred</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>confirm sync_scan writes (psycopg2 raw SQL not .table API); not silent no-op</t>
+          <t>8 telemetry/data slots remain empty because populating them requires editing backtest.py / executor.py / signal_filter.py / analysis.py. Deliberately deferred to avoid risk to the live scan + exec paths.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>supabase_analysis_sync.py</t>
+          <t>Enumerate the 8 specifically and grade each one for in-place vs side-car instrumentation. Side-car (write to telemetry DB without changing decision flow) is preferred over hot-path edits.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -2748,13 +2748,13 @@
       <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="8" t="inlineStr"/>
     </row>
-    <row r="45" ht="60" customHeight="1">
+    <row r="45" ht="45" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-PROD-ENGINE-DEFERRED</t>
+          <t>BARSTORE-4</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -2764,22 +2764,22 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Data / Telemetry (deferred for safety)</t>
+          <t>Data Infra / Bar-Store</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>8 empty slots — production-engine touches deferred</t>
+          <t>Daily incremental via bulk_eod</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>8 telemetry/data slots remain empty because populating them requires editing backtest.py / executor.py / signal_filter.py / analysis.py. Deliberately deferred to avoid risk to the live scan + exec paths.</t>
+          <t>After backfill, only the latest bar is needed daily; bulk_eod returns the whole exchange in 1 call.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Enumerate the 8 specifically and grade each one for in-place vs side-car instrumentation. Side-car (write to telemetry DB without changing decision flow) is preferred over hot-path edits.</t>
+          <t>Daily launchd job: 1 bulk_eod(exchange) appends last-day bar for all tickers into daily_bars. Target &lt;=2 EODHD calls/day total for OHLCV.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-4</t>
+          <t>BARSTORE-5</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -2815,17 +2815,17 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Daily incremental via bulk_eod</t>
+          <t>Corporate-action re-adjustment</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>After backfill, only the latest bar is needed daily; bulk_eod returns the whole exchange in 1 call.</t>
+          <t>Stored history must stay split/div-adjusted; a new split re-bases all prior bars. This is where data-integrity bugs hide.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Daily launchd job: 1 bulk_eod(exchange) appends last-day bar for all tickers into daily_bars. Target &lt;=2 EODHD calls/day total for OHLCV.</t>
+          <t>Store raw + adjusted_close; small daily job re-adjusts history on split/div events (EODHD div/splits endpoints). Validate no adjustment drift.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -2840,13 +2840,13 @@
       <c r="M46" s="3" t="inlineStr"/>
       <c r="N46" s="8" t="inlineStr"/>
     </row>
-    <row r="47" ht="45" customHeight="1">
+    <row r="47" ht="60" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-5</t>
+          <t>BARSTORE-6</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Corporate-action re-adjustment</t>
+          <t>Delisted backfill -&gt; survivorship fix</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Stored history must stay split/div-adjusted; a new split re-bases all prior bars. This is where data-integrity bugs hide.</t>
+          <t>Honest backtests need delisted tickers' history + point-in-time membership (membership snapshots already DONE via AIPRED-SURVIVORSHIP). Unblocks audit #1.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Store raw + adjusted_close; small daily job re-adjusts history on split/div events (EODHD div/splits endpoints). Validate no adjustment drift.</t>
+          <t>Backfill delisted-ticker history into daily_bars; point walk_forward_v2 at DB over 20yr. Enables survivorship-bias-free backtests + free validation of staged accuracy tweaks.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>BARSTORE-6</t>
+          <t>EODHD-WIRES-VALIDATE</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -2902,22 +2902,22 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Data Infra / Bar-Store</t>
+          <t>Data Wiring (validate)</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Delisted backfill -&gt; survivorship fix</t>
+          <t>Validate EODHD-side wires on quota reset</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Honest backtests need delisted tickers' history + point-in-time membership (membership snapshots already DONE via AIPRED-SURVIVORSHIP). Unblocks audit #1.</t>
+          <t>DCF net-debt/FCF + per-name beta + Book Risk crowding are code-complete + fallback-safe but untested against live EODHD (quota was exhausted). Confirm real values flow after reset.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Backfill delisted-ticker history into daily_bars; point walk_forward_v2 at DB over 20yr. Enables survivorship-bias-free backtests + free validation of staged accuracy tweaks.</t>
+          <t>Stocksmith.html /api/fundamentals consumers</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -2932,13 +2932,13 @@
       <c r="M48" s="3" t="inlineStr"/>
       <c r="N48" s="8" t="inlineStr"/>
     </row>
-    <row r="49" ht="60" customHeight="1">
+    <row r="49" ht="105" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>EODHD-WIRES-VALIDATE</t>
+          <t>OVERVIEW-VERDICT-RECON</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -2948,27 +2948,31 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Data Wiring (validate)</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Validate EODHD-side wires on quota reset</t>
+          <t>Reconcile compute_final_verdict (stage) vs decisions_by_mode</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>DCF net-debt/FCF + per-name beta + Book Risk crowding are code-complete + fallback-safe but untested against live EODHD (quota was exhausted). Confirm real values flow after reset.</t>
+          <t>Two engines emit different swing score+verdict for the same name (FTNT: stage=BUY/67 vs decisions_by_mode.swing=WATCH/57). decisions_by_mode omits the catalyst-sleeve EXTENDED-entry relaxation that compute_final_verdict applies, so they disagree.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html /api/fundamentals consumers</t>
+          <t>Have decisions_by_mode consume the same relaxation OR emit a diverges-from-composite flag; decide direction after the entry-quality EXTENDED/MISSED A/B validation lands. Display already fixed (overview.js binds stage).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>PATH B (2026-06-09): also propagate the engine per-mode composite_score (analysis.py:8387 mode_score) into decisions_by_mode so composite-verdict.jsx + Overview can BIND a real per-mode score instead of recomputing. composite-verdict.jsx Path A shipped (binds canonical ticker.score as headline, lenses=why only); per-mode engine score is the deferred Path B. Resolve alongside the stage-vs-decisions_by_mode verdict question.</t>
+        </is>
+      </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -2978,13 +2982,13 @@
       <c r="M49" s="3" t="inlineStr"/>
       <c r="N49" s="8" t="inlineStr"/>
     </row>
-    <row r="50" ht="105" customHeight="1">
+    <row r="50" ht="75" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>OVERVIEW-VERDICT-RECON</t>
+          <t>KAIROS-TRAFFIC-LIGHT-INPUTS</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -2994,31 +2998,27 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Detail Lens / Traffic Lights</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Reconcile compute_final_verdict (stage) vs decisions_by_mode</t>
+          <t>Per-ticker risk/fundamentals inputs for lens dots</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Two engines emit different swing score+verdict for the same name (FTNT: stage=BUY/67 vs decisions_by_mode.swing=WATCH/57). decisions_by_mode omits the catalyst-sleeve EXTENDED-entry relaxation that compute_final_verdict applies, so they disagree.</t>
+          <t>Wire t.f_score · t.altman_z · t.roic · t.wacc · t.sharpe_1y · t.dd_recovery_months · t.peer_rank · t.is_held into build_data.py. _qdComputeLensStatus has cascading fallbacks (PEG → fund_score → F-score; beta → kelly → Sharpe), so dots upgrade automatically as fields land.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Have decisions_by_mode consume the same relaxation OR emit a diverges-from-composite flag; decide direction after the entry-quality EXTENDED/MISSED A/B validation lands. Display already fixed (overview.js binds stage).</t>
+          <t>Compute in analysis.py / portfolio.py: Piotroski F (existing data), Altman Z (existing data), ROIC vs WACC, 1y Sharpe from price history, peer_rank from cohort, is_held from portfolio_state.json.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>PATH B (2026-06-09): also propagate the engine per-mode composite_score (analysis.py:8387 mode_score) into decisions_by_mode so composite-verdict.jsx + Overview can BIND a real per-mode score instead of recomputing. composite-verdict.jsx Path A shipped (binds canonical ticker.score as headline, lenses=why only); per-mode engine score is the deferred Path B. Resolve alongside the stage-vs-decisions_by_mode verdict question.</t>
-        </is>
-      </c>
+      <c r="J50" s="5" t="inlineStr"/>
       <c r="K50" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -3028,13 +3028,13 @@
       <c r="M50" s="3" t="inlineStr"/>
       <c r="N50" s="8" t="inlineStr"/>
     </row>
-    <row r="51" ht="75" customHeight="1">
+    <row r="51" ht="60" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-TRAFFIC-LIGHT-INPUTS</t>
+          <t>KAIROS-COHORT-SYMPATHY</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -3044,22 +3044,22 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Detail Lens / Traffic Lights</t>
+          <t>Earnings Lens / Cohort</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Per-ticker risk/fundamentals inputs for lens dots</t>
+          <t>Peer cohort sympathy correlations</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Wire t.f_score · t.altman_z · t.roic · t.wacc · t.sharpe_1y · t.dd_recovery_months · t.peer_rank · t.is_held into build_data.py. _qdComputeLensStatus has cascading fallbacks (PEG → fund_score → F-score; beta → kelly → Sharpe), so dots upgrade automatically as fields land.</t>
+          <t>Wire t.cohort_peers[].er_sympathy_corr + er_sympathy_move_1d + t.sympathy_history in build_data.py. Today: renderEarnings_Sympathy shows scaffold rows from t.cohort_peers if populated, else placeholder.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Compute in analysis.py / portfolio.py: Piotroski F (existing data), Altman Z (existing data), ROIC vs WACC, 1y Sharpe from price history, peer_rank from cohort, is_held from portfolio_state.json.</t>
+          <t>Compute 8-quarter rolling correlation of 1d post-print move between this name and each cohort peer's ER date. Persist to data.json under t.cohort_peers + t.sympathy_history.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -3074,13 +3074,13 @@
       <c r="M51" s="3" t="inlineStr"/>
       <c r="N51" s="8" t="inlineStr"/>
     </row>
-    <row r="52" ht="60" customHeight="1">
+    <row r="52" ht="75" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-COHORT-SYMPATHY</t>
+          <t>PARITY-IN-APP-TRADING</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -3090,22 +3090,22 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Earnings Lens / Cohort</t>
+          <t>Execution / Live / Platform Parity</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Peer cohort sympathy correlations</t>
+          <t>In-app Trading (broker-integrated live execution)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Wire t.cohort_peers[].er_sympathy_corr + er_sympathy_move_1d + t.sympathy_history in build_data.py. Today: renderEarnings_Sympathy shows scaffold rows from t.cohort_peers if populated, else placeholder.</t>
+          <t>One-click BUY/SELL from the dashboard to a live Schwab/Alpaca brokerage account.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Compute 8-quarter rolling correlation of 1d post-print move between this name and each cohort peer's ER date. Persist to data.json under t.cohort_peers + t.sympathy_history.</t>
+          <t>OAuth-link the Schwab API (already paid stack); surface an 'Execute' button on the Trade Plan card; explicit AUTHORIZE LIVE TRADING gate per CLAUDE.md security protocol; route every order through the existing risk checks (max-loss-pct, drawdown haircut, regime gate).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>PARITY-IN-APP-TRADING</t>
+          <t>KAIROS-LIVE-D1</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -3136,22 +3136,22 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Execution / Live / Platform Parity</t>
+          <t>Kairos / Audit Ledger</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>In-app Trading (broker-integrated live execution)</t>
+          <t>Live D1 estimate from Schwab quote during RTH</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>One-click BUY/SELL from the dashboard to a live Schwab/Alpaca brokerage account.</t>
+          <t>Replace placeholder D1 (yesterday's close-to-close) with a live Schwab-quote-based intraday estimate during market hours so the audit ledger D1 column is non-stale. Discussed and deferred as semantically muddy (D1 = next-day close, intraday quote is a forecast not a fill).</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>OAuth-link the Schwab API (already paid stack); surface an 'Execute' button on the Trade Plan card; explicit AUTHORIZE LIVE TRADING gate per CLAUDE.md security protocol; route every order through the existing risk checks (max-loss-pct, drawdown haircut, regime gate).</t>
+          <t>Add a SCHWAB_LIVE_D1=1 env flag; when ON and during RTH, compute D1_est = (live_quote - signal_entry) / signal_entry and annotate the cell with an 'est' chip. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -3166,13 +3166,13 @@
       <c r="M53" s="3" t="inlineStr"/>
       <c r="N53" s="8" t="inlineStr"/>
     </row>
-    <row r="54" ht="75" customHeight="1">
+    <row r="54" ht="45" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-LIVE-D1</t>
+          <t>KAIROS-SCANNER-BEARS</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -3182,22 +3182,22 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Kairos / Audit Ledger</t>
+          <t>Kairos / Signal Scanner</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Live D1 estimate from Schwab quote during RTH</t>
+          <t>Top 5 Bears panel</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Replace placeholder D1 (yesterday's close-to-close) with a live Schwab-quote-based intraday estimate during market hours so the audit ledger D1 column is non-stale. Discussed and deferred as semantically muddy (D1 = next-day close, intraday quote is a forecast not a fill).</t>
+          <t>Add a 'Top 5 Bears' panel to the Signal Scanner alongside Fresh / Momentum / Earnings / Volume — was proposed but not selected in the initial build.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Add a SCHWAB_LIVE_D1=1 env flag; when ON and during RTH, compute D1_est = (live_quote - signal_entry) / signal_entry and annotate the cell with an 'est' chip. Effort ~1hr.</t>
+          <t>Mirror existing 4 panels' structure; sort universe by composite bear-score desc; cap at 5; render in the Scanner grid. Effort ~10min.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -3212,13 +3212,13 @@
       <c r="M54" s="3" t="inlineStr"/>
       <c r="N54" s="8" t="inlineStr"/>
     </row>
-    <row r="55" ht="45" customHeight="1">
+    <row r="55" ht="60" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-SCANNER-BEARS</t>
+          <t>KAIROS-SCANNER-FLIPS</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -3233,17 +3233,17 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Top 5 Bears panel</t>
+          <t>Today's Flips panel</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Add a 'Top 5 Bears' panel to the Signal Scanner alongside Fresh / Momentum / Earnings / Volume — was proposed but not selected in the initial build.</t>
+          <t>Add a 'Today's Flips' panel to the Signal Scanner — tickers whose verdict flipped vs yesterday (e.g., BUY -&gt; WATCH, WATCH -&gt; BUY, AVOID -&gt; WATCH). Proposed in the 'what else' menu, not selected.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Mirror existing 4 panels' structure; sort universe by composite bear-score desc; cap at 5; render in the Scanner grid. Effort ~10min.</t>
+          <t>Diff today's bundle.verdict against yesterday.verdict per ticker; surface the 5-10 most material flips. Effort ~30min.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-SCANNER-FLIPS</t>
+          <t>ML-RETRAIN-FINBERT-FEATURE</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -3274,22 +3274,22 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Kairos / Signal Scanner</t>
+          <t>ML / Features (future)</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Today's Flips panel</t>
+          <t>Add FinBERT as a GBM training feature (leak-free)</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Add a 'Today's Flips' panel to the Signal Scanner — tickers whose verdict flipped vs yesterday (e.g., BUY -&gt; WATCH, WATCH -&gt; BUY, AVOID -&gt; WATCH). Proposed in the 'what else' menu, not selected.</t>
+          <t>needs historical sentiment series — accumulate forward via cache/ml/sentiment_log.jsonl (asof-stamped); add as feature #18 + retrain once ~3-6mo of leak-free history exists</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Diff today's bundle.verdict against yesterday.verdict per ticker; surface the 5-10 most material flips. Effort ~30min.</t>
+          <t>ml/feature_extractor + historical backfill</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>ML-RETRAIN-FINBERT-FEATURE</t>
+          <t>ML-AUTOREFRESH-VALIDATE</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -3320,22 +3320,22 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>ML / Features (future)</t>
+          <t>ML / Pipeline (validate)</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Add FinBERT as a GBM training feature (leak-free)</t>
+          <t>Validate ML auto-refresh post-scan + cached-bar reuse</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>needs historical sentiment series — accumulate forward via cache/ml/sentiment_log.jsonl (asof-stamped); add as feature #18 + retrain once ~3-6mo of leak-free history exists</t>
+          <t>ml_edge.run_after_scan=true runs ml.run_ml_edge over the fresh bundle; feature_extractor prefers data_archive (no re-fetch). Confirm end-to-end on next clean scan.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>ml/feature_extractor + historical backfill</t>
+          <t>swing_trade ML hook + ml/feature_extractor</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>ML-AUTOREFRESH-VALIDATE</t>
+          <t>KAIROS-MACRO-EVENTS</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -3366,22 +3366,22 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>ML / Pipeline (validate)</t>
+          <t>Macro Lens / Calendar</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Validate ML auto-refresh post-scan + cached-bar reuse</t>
+          <t>14-day high-impact event window flag</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>ml_edge.run_after_scan=true runs ml.run_ml_edge over the fresh bundle; feature_extractor prefers data_archive (no re-fetch). Confirm end-to-end on next clean scan.</t>
+          <t>Wire t.next_macro_event_days = days to next FOMC/CPI/NFP/jobs. _qdComputeLensStatus reads this and downgrades macro lens to amber when event &lt;= 14d even in risk_on_trending regime.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>swing_trade ML hook + ml/feature_extractor</t>
+          <t>Add macro_calendar fetch in data_fetcher.py (FRED/Trading Economics free tier or EODHD calendar). Persist to t.next_macro_event_days.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -3396,13 +3396,13 @@
       <c r="M58" s="3" t="inlineStr"/>
       <c r="N58" s="8" t="inlineStr"/>
     </row>
-    <row r="59" ht="60" customHeight="1">
+    <row r="59" ht="90" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-MACRO-EVENTS</t>
+          <t>JOB-CADENCE-CENSUS-2026-06-14</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -3412,22 +3412,22 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Macro Lens / Calendar</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>14-day high-impact event window flag</t>
+          <t>Job cadence census — most jobs justified, not over-done</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Wire t.next_macro_event_days = days to next FOMC/CPI/NFP/jobs. _qdComputeLensStatus reads this and downgrades macro lens to amber when event &lt;= 14d even in risk_on_trending regime.</t>
+          <t>Audited all 59 launchd jobs for over-frequency. FINDING: the census mostly DISSOLVED — rolling-tail (9x), source-health (3x), prewarm (2x) all have documented rationale (archive-first/zero-API tail sweep; cost-trivial liveness probe catching dead-Finviz 10x-fallback; prewarm already cut 14-&gt;2). Run-count != EODHD cost. System better-governed than the frequency heuristic implied.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Add macro_calendar fetch in data_fetcher.py (FRED/Trading Economics free tier or EODHD calendar). Persist to t.next_macro_event_days.</t>
+          <t>Applied only the justified change: positionwatch StartInterval 60-&gt;300s (close-based swing stops dont need minute monitoring; cuts ~1950-&gt;390 Schwab quotes/day + bail churn). Governance: exported untracked com.swingtrade.audit-ledger-intraday.plist into infra/launchd/ (was loaded from ~/Library/LaunchAgents only). Left rolling-tail/source-health/prewarm untouched — justified.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -3442,13 +3442,13 @@
       <c r="M59" s="3" t="inlineStr"/>
       <c r="N59" s="8" t="inlineStr"/>
     </row>
-    <row r="60" ht="90" customHeight="1">
+    <row r="60" ht="45" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>JOB-CADENCE-CENSUS-2026-06-14</t>
+          <t>CACHE-RECLAIM</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -3458,22 +3458,22 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Ops / Hygiene</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Job cadence census — most jobs justified, not over-done</t>
+          <t>Reclaim ~6GB cache (stray bak + edgar TTL)</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Audited all 59 launchd jobs for over-frequency. FINDING: the census mostly DISSOLVED — rolling-tail (9x), source-health (3x), prewarm (2x) all have documented rationale (archive-first/zero-API tail sweep; cost-trivial liveness probe catching dead-Finviz 10x-fallback; prewarm already cut 14-&gt;2). Run-count != EODHD cost. System better-governed than the frequency heuristic implied.</t>
+          <t>delete 300MB last_bundle.json.bak.precap_promote + add edgar companyfacts prune/TTL (6.1GB)</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Applied only the justified change: positionwatch StartInterval 60-&gt;300s (close-based swing stops dont need minute monitoring; cuts ~1950-&gt;390 Schwab quotes/day + bail churn). Governance: exported untracked com.swingtrade.audit-ledger-intraday.plist into infra/launchd/ (was loaded from ~/Library/LaunchAgents only). Left rolling-tail/source-health/prewarm untouched — justified.</t>
+          <t>cache cleanup + edgar_client TTL</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>CACHE-RECLAIM</t>
+          <t>JOBS-MOMENTUM-SNAPSHOT</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -3504,22 +3504,22 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Ops / Hygiene</t>
+          <t>Ops / Launchd</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Reclaim ~6GB cache (stray bak + edgar TTL)</t>
+          <t>Decide momentum-snapshot job: load or disable</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>delete 300MB last_bundle.json.bak.precap_promote + add edgar companyfacts prune/TTL (6.1GB)</t>
+          <t>valid plist in repo but not currently loaded; decide launchctl bootstrap vs move to disabled/.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>cache cleanup + edgar_client TTL</t>
+          <t>infra/launchd/com.swingtrade.momentum-snapshot.plist</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -3534,13 +3534,13 @@
       <c r="M61" s="3" t="inlineStr"/>
       <c r="N61" s="8" t="inlineStr"/>
     </row>
-    <row r="62" ht="45" customHeight="1">
+    <row r="62" ht="60" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>JOBS-MOMENTUM-SNAPSHOT</t>
+          <t>DATA-FUTURE-OPS-TELEMETRY-6</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -3550,22 +3550,22 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Ops / Launchd</t>
+          <t>Ops / Telemetry (future)</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot job: load or disable</t>
+          <t>6 ops telemetry slots — app-side instrumentation</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>valid plist in repo but not currently loaded; decide launchctl bootstrap vs move to disabled/.</t>
+          <t>6 ops telemetry slots remain unbuilt because they require app-side instrumentation: server middleware, git hooks, scan-time emitters, executor probes, sub-tab render timings, fetch-latency probes.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd/com.swingtrade.momentum-snapshot.plist</t>
+          <t>Build a shared emitter (lib/telemetry.py) writing to a telemetry SQLite; instrument incrementally — server middleware first, then scan emitters; surface in System Status sub-tab.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-OPS-TELEMETRY-6</t>
+          <t>SCALE-4</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -3596,22 +3596,22 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Ops / Telemetry (future)</t>
+          <t>Ops · 500-user</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>6 ops telemetry slots — app-side instrumentation</t>
+          <t>Scan reliability so Home is not sparse</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>6 ops telemetry slots remain unbuilt because they require app-side instrumentation: server middleware, git hooks, scan-time emitters, executor probes, sub-tab render timings, fetch-latency probes.</t>
+          <t>When the daily scan is empty (EODHD quota outage), Home shows honest-empty sections + stale-badged regime; users landing mid-outage see little actionable content</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Build a shared emitter (lib/telemetry.py) writing to a telemetry SQLite; instrument incrementally — server middleware first, then scan emitters; surface in System Status sub-tab.</t>
+          <t>Ensure morning scan runs reliably + quota headroom; keep STALE badge UX; consider serving last-good bundle with clear age</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3626,13 +3626,13 @@
       <c r="M63" s="3" t="inlineStr"/>
       <c r="N63" s="8" t="inlineStr"/>
     </row>
-    <row r="64" ht="60" customHeight="1">
+    <row r="64" ht="75" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>SCALE-4</t>
+          <t>OV-INVEST-STRUCT</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -3642,22 +3642,22 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Ops · 500-user</t>
+          <t>Overview / Target Engine</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Scan reliability so Home is not sparse</t>
+          <t>Real structural invest targets (kill analyst-PT stub)</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>When the daily scan is empty (EODHD quota outage), Home shows honest-empty sections + stale-badged regime; users landing mid-outage see little actionable content</t>
+          <t>Invest-mode targets fall back to analyst 12mo PT (invest_stub) for low-vol names (e.g. AAPL) when no structural level qualifies in the invest R-band off the wider stop -&gt; near T1, poor R:R. Per-mode stop scaling fix (2026-06-08) made invest coherent for higher-vol names (NVDA stub=False) but low-vol names still stub.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Ensure morning scan runs reliably + quota headroom; keep STALE badge UX; consider serving last-good bundle with clear age</t>
+          <t>Wire multi-year structural levels (monthly/yearly swing highs, weekly Fib ext) into the invest candidate set so the invest R-band is populated without the analyst-PT fallback; raise invest max_reach_atr to match a 1-5yr horizon.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -3672,13 +3672,13 @@
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="8" t="inlineStr"/>
     </row>
-    <row r="65" ht="75" customHeight="1">
+    <row r="65" ht="60" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>OV-INVEST-STRUCT</t>
+          <t>SCALE-3</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -3688,22 +3688,22 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Overview / Target Engine</t>
+          <t>Portfolio · 500-user</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Real structural invest targets (kill analyst-PT stub)</t>
+          <t>Per-user portfolio vs shared automated book</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Invest-mode targets fall back to analyst 12mo PT (invest_stub) for low-vol names (e.g. AAPL) when no structural level qualifies in the invest R-band off the wider stop -&gt; near T1, poor R:R. Per-mode stop scaling fix (2026-06-08) made invest coherent for higher-vol names (NVDA stub=False) but low-vol names still stub.</t>
+          <t>Home AUTOMATED BOOK is the single shared Alpaca-paper auto-trade account; every viewer sees identical positions; no per-user book (NAV is per-user, positions are not)</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Wire multi-year structural levels (monthly/yearly swing highs, weekly Fib ext) into the invest candidate set so the invest R-band is populated without the analyst-PT fallback; raise invest max_reach_atr to match a 1-5yr horizon.</t>
+          <t>Decide: keep as shared model/track-record book by design, OR add a per-user position store keyed to UserPrefs auth id</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -3718,13 +3718,13 @@
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="8" t="inlineStr"/>
     </row>
-    <row r="66" ht="60" customHeight="1">
+    <row r="66" ht="90" customHeight="1">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>SCALE-3</t>
+          <t>QUANT-HMM-FF-LGBM-ROADMAP</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -3734,22 +3734,22 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Portfolio · 500-user</t>
+          <t>Quant / Modeling Roadmap</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Per-user portfolio vs shared automated book</t>
+          <t>HMM regime / Fama-French / LightGBM swap (status unclear)</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Home AUTOMATED BOOK is the single shared Alpaca-paper auto-trade account; every viewer sees identical positions; no per-user book (NAV is per-user, positions are not)</t>
+          <t>Roadmap items pasted as a status table — clarification pending whether user wants execution or just context tracking. Three potential upgrades: (a) HMM-based regime classifier replacing the rule-based 4-regime model, (b) Fama-French factor exposure analysis on closed trades, (c) LightGBM swap-in for HistGradientBoosting in ml/train_historical.py. Each 1-3 days.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Decide: keep as shared model/track-record book by design, OR add a per-user position store keyed to UserPrefs auth id</t>
+          <t>Confirm intent before executing. If go: HMM first (decouples regime classifier from heuristics, principle #18), then Fama-French attribution (per-strategy factor exposure), then LightGBM swap (likely-marginal accuracy gain vs current HistGB). Each upgrade gated by Wilson-LB validation vs current baseline.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -3764,13 +3764,13 @@
       <c r="M66" s="3" t="inlineStr"/>
       <c r="N66" s="8" t="inlineStr"/>
     </row>
-    <row r="67" ht="90" customHeight="1">
+    <row r="67" ht="60" customHeight="1">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>QUANT-HMM-FF-LGBM-ROADMAP</t>
+          <t>PARITY-SMART-RISK-LEVELS</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -3780,22 +3780,22 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Quant / Modeling Roadmap</t>
+          <t>Risk / Targets / Platform Parity</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>HMM regime / Fama-French / LightGBM swap (status unclear)</t>
+          <t>Smart Risk Levels (auto stop + T1/T2)</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Roadmap items pasted as a status table — clarification pending whether user wants execution or just context tracking. Three potential upgrades: (a) HMM-based regime classifier replacing the rule-based 4-regime model, (b) Fama-French factor exposure analysis on closed trades, (c) LightGBM swap-in for HistGradientBoosting in ml/train_historical.py. Each 1-3 days.</t>
+          <t>Auto-place stop / T1 / T2 dots on the chart with confluence reasoning (HVN, AVWAP, fractal, ATR, Fib). Already computed by the structural target engine but not surfaced on the new Chart sub-tab.</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Confirm intent before executing. If go: HMM first (decouples regime classifier from heuristics, principle #18), then Fama-French attribution (per-strategy factor exposure), then LightGBM swap (likely-marginal accuracy gain vs current HistGB). Each upgrade gated by Wilson-LB validation vs current baseline.</t>
+          <t>Read cache/target_engine/{TICKER}_{MODE}.json and overlay the levels on the chart canvas with hover tooltips citing the confluence factors; gated by use_structural_targets flag (M2.5 cutover).</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>PARITY-SMART-RISK-LEVELS</t>
+          <t>KAIROS-L2-BOOK</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -3826,22 +3826,22 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Risk / Targets / Platform Parity</t>
+          <t>Risk Lens / Execution</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Smart Risk Levels (auto stop + T1/T2)</t>
+          <t>L2 bid/ask depth at price levels</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Auto-place stop / T1 / T2 dots on the chart with confluence reasoning (HVN, AVWAP, fractal, ATR, Fib). Already computed by the structural target engine but not surfaced on the new Chart sub-tab.</t>
+          <t>Wire t.l2_book from Schwab streaming API → render in renderRisk_LiquidityLadder. Today: ADV-derived size tiers shown as scaffold. Schwab streaming requires WebSocket session — see schwab_client.py.</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Read cache/target_engine/{TICKER}_{MODE}.json and overlay the levels on the chart canvas with hover tooltips citing the confluence factors; gated by use_structural_targets flag (M2.5 cutover).</t>
+          <t>Subscribe to Schwab Level-II quote stream; persist top-of-book snapshot into t.l2_book = {bid:[{px,size}], ask:[{px,size}]}. Frontend already reads these fields if present.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -3856,13 +3856,13 @@
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="8" t="inlineStr"/>
     </row>
-    <row r="69" ht="60" customHeight="1">
+    <row r="69" ht="75" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-L2-BOOK</t>
+          <t>TECH-MOM-DIVERGENCE-PENALTY</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -3872,22 +3872,22 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Risk Lens / Execution</t>
+          <t>Scoring</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>L2 bid/ask depth at price levels</t>
+          <t>Momentum-divergence penalty for Technicals pillar (STAGED)</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Wire t.l2_book from Schwab streaming API → render in renderRisk_LiquidityLadder. Today: ADV-derived size tiers shown as scaffold. Schwab streaming requires WebSocket session — see schwab_client.py.</t>
+          <t>Strong-RS/trend names whose fast momentum rolled over (MACD death cross + light volume) score too high on Technicals because RS/trend mask the weak momentum sub-score (CTS: 63% with a death cross). Staged penalty docks the pillar (-3) when mom&lt;=2/5 AND rvol&lt;1.0 AND death_cross. Default OFF.</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Subscribe to Schwab Level-II quote stream; persist top-of-book snapshot into t.l2_book = {bid:[{px,size}], ask:[{px,size}]}. Frontend already reads these fields if present.</t>
+          <t>analysis.score_technicals + scoring.momentum_divergence_penalty config flag. ACTIVATION GATED on swing-WR/PF A/B backtest (principle 7) — do not flip _enabled without it. CTS 63%-&gt;55% when on.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>TECH-MOM-DIVERGENCE-PENALTY</t>
+          <t>BUY-FLOOR-72</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -3918,22 +3918,22 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Scoring</t>
+          <t>Signal Scoring</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Momentum-divergence penalty for Technicals pillar (STAGED)</t>
+          <t>Sub-70 BUY floor (staged OFF)</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Strong-RS/trend names whose fast momentum rolled over (MACD death cross + light volume) score too high on Technicals because RS/trend mask the weak momentum sub-score (CTS: 63% with a death cross). Staged penalty docks the pillar (-3) when mom&lt;=2/5 AND rvol&lt;1.0 AND death_cross. Default OFF.</t>
+          <t>Raise composite BUY floor 65-&gt;72 so sub-72 names demote BUY-&gt;WATCH (scoring untouched). Robust sub-70 loss: resolved BUY [65,72) PF 0.46 vs [70,90) 1.63, n=290 Wilson clears n&gt;=30, 95% plain composite breakout/trend not catalyst sleeves.</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>analysis.score_technicals + scoring.momentum_divergence_penalty config flag. ACTIVATION GATED on swing-WR/PF A/B backtest (principle 7) — do not flip _enabled without it. CTS 63%-&gt;55% when on.</t>
+          <t>config/config.json buy_score_floor block (default OFF, composite-only) + decision_engine.compute_final_verdict applies score&gt;=floor in both legacy and ranker promote paths. STAGED OFF pending walk_forward_v2 cross-regime confirm + ranker-overlap measurement (add rank_score to signal_log first). Reversible.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -3948,13 +3948,13 @@
       <c r="M70" s="3" t="inlineStr"/>
       <c r="N70" s="8" t="inlineStr"/>
     </row>
-    <row r="71" ht="75" customHeight="1">
+    <row r="71" ht="60" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>BUY-FLOOR-72</t>
+          <t>PARITY-AI-SIGNALS-V1</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -3964,22 +3964,22 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Signal Scoring</t>
+          <t>Signals / Platform Parity</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Sub-70 BUY floor (staged OFF)</t>
+          <t>1st-Gen AI Signals</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Raise composite BUY floor 65-&gt;72 so sub-72 names demote BUY-&gt;WATCH (scoring untouched). Robust sub-70 loss: resolved BUY [65,72) PF 0.46 vs [70,90) 1.63, n=290 Wilson clears n&gt;=30, 95% plain composite breakout/trend not catalyst sleeves.</t>
+          <t>Surface a baseline AI BUY/SELL signal stream on the chart as quick-glance arrows/dots — the competitor-platform feature (TrendSpider, Trade Ideas) users expect to see at a glance, separate from the full ML Edge sub-tab.</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>config/config.json buy_score_floor block (default OFF, composite-only) + decision_engine.compute_final_verdict applies score&gt;=floor in both legacy and ranker promote paths. STAGED OFF pending walk_forward_v2 cross-regime confirm + ranker-overlap measurement (add rank_score to signal_log first). Reversible.</t>
+          <t>Reuse ML Edge dir-head + cone outputs but render as 1-bar arrows/markers on the new Chart sub-tab; isolate from the 10-section Technicals view; respect cache/ml_edge_predictions.json freshness.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -3994,13 +3994,13 @@
       <c r="M71" s="3" t="inlineStr"/>
       <c r="N71" s="8" t="inlineStr"/>
     </row>
-    <row r="72" ht="60" customHeight="1">
+    <row r="72" ht="45" customHeight="1">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>PARITY-AI-SIGNALS-V1</t>
+          <t>TEST-AB-PAPER</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -4010,22 +4010,22 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Signals / Platform Parity</t>
+          <t>Testing / Validation (Tier 2)</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>1st-Gen AI Signals</t>
+          <t>A/B Paper Split — live comparison</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Surface a baseline AI BUY/SELL signal stream on the chart as quick-glance arrows/dots — the competitor-platform feature (TrendSpider, Trade Ideas) users expect to see at a glance, separate from the full ML Edge sub-tab.</t>
+          <t>Run config A on half the paper portfolio and config B on the other half; real-time comparison of WR / PF / equity divergence over 30-60d window.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>Reuse ML Edge dir-head + cone outputs but render as 1-bar arrows/markers on the new Chart sub-tab; isolate from the 10-section Technicals view; respect cache/ml_edge_predictions.json freshness.</t>
+          <t>Extend executor.py to accept --variant flag; persist per-variant portfolio state; cross-section panel in System Status sub-tab. Effort 3-4hr.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4040,13 +4040,13 @@
       <c r="M72" s="3" t="inlineStr"/>
       <c r="N72" s="8" t="inlineStr"/>
     </row>
-    <row r="73" ht="45" customHeight="1">
+    <row r="73" ht="60" customHeight="1">
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>TEST-AB-PAPER</t>
+          <t>TEST-BENCHMARK-SPY</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -4061,17 +4061,17 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>A/B Paper Split — live comparison</t>
+          <t>Benchmark vs SPY — alpha / beta / IR</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Run config A on half the paper portfolio and config B on the other half; real-time comparison of WR / PF / equity divergence over 30-60d window.</t>
+          <t>Compute strategy alpha, beta, information ratio vs SPY benchmark. Standard performance attribution; turns 'we made +X%' into 'we made +Y% over SPY at lower drawdown'.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Extend executor.py to accept --variant flag; persist per-variant portfolio state; cross-section panel in System Status sub-tab. Effort 3-4hr.</t>
+          <t>Daily portfolio_value series joined to SPY adjusted-close; regress daily returns -&gt; SPY returns for beta + alpha; IR = (mean excess return) / (std excess return); render in System Status. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>TEST-BENCHMARK-SPY</t>
+          <t>TEST-DD-DIST</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -4107,17 +4107,17 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Benchmark vs SPY — alpha / beta / IR</t>
+          <t>Drawdown Distribution Simulator</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Compute strategy alpha, beta, information ratio vs SPY benchmark. Standard performance attribution; turns 'we made +X%' into 'we made +Y% over SPY at lower drawdown'.</t>
+          <t>Bootstrap 1000 portfolio paths from closed-trade distribution; measure tail-drawdown probability at p95/p99; supports principle #9 (drawdown asymmetry — losing 50% requires +100% to recover).</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>Daily portfolio_value series joined to SPY adjusted-close; regress daily returns -&gt; SPY returns for beta + alpha; IR = (mean excess return) / (std excess return); render in System Status. Effort ~1hr.</t>
+          <t>Resample trade sequence with replacement; build equity curves; compute max-DD per path; histogram + tail percentiles; feed into position-sizing math. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>TEST-DD-DIST</t>
+          <t>TEST-SENSITIVITY</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
@@ -4153,17 +4153,17 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Drawdown Distribution Simulator</t>
+          <t>Sensitivity / Robustness Test</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Bootstrap 1000 portfolio paths from closed-trade distribution; measure tail-drawdown probability at p95/p99; supports principle #9 (drawdown asymmetry — losing 50% requires +100% to recover).</t>
+          <t>Perturb each config parameter +/-20% (score floors, stop ATR mult, R:R floor, regime thresholds) and check whether the strategy still passes the gate. Finds overfit knobs that only work at one exact value.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Resample trade sequence with replacement; build equity curves; compute max-DD per path; histogram + tail percentiles; feed into position-sizing math. Effort 2-3hr.</t>
+          <t>Grid-walk key config thresholds; re-run backtest at each point; build sensitivity heatmap (param vs PF); flag any knob whose +/-20% perturbation collapses PF &gt;50%. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>TEST-SENSITIVITY</t>
+          <t>TEST-SLIPPAGE-STRESS</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -4199,17 +4199,17 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Sensitivity / Robustness Test</t>
+          <t>Slippage Stress Test</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Perturb each config parameter +/-20% (score floors, stop ATR mult, R:R floor, regime thresholds) and check whether the strategy still passes the gate. Finds overfit knobs that only work at one exact value.</t>
+          <t>Double the slippage assumption (ATR/ADV-scaled model from audit #5) and recompute backtest stats. Validates fragile execution dependence per principle #19 (slippage realism).</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>Grid-walk key config thresholds; re-run backtest at each point; build sensitivity heatmap (param vs PF); flag any knob whose +/-20% perturbation collapses PF &gt;50%. Effort ~2hr.</t>
+          <t>Re-run backtest with SLIPPAGE_MULT=2.0; compare WR/PF/Sharpe deltas; if a strategy collapses at 2x slippage it is execution-fragile and should be down-sized. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>TEST-SLIPPAGE-STRESS</t>
+          <t>TEST-CORRELATED-FAILURE</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
@@ -4240,22 +4240,22 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Testing / Validation (Tier 2)</t>
+          <t>Testing / Validation (Tier 3)</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Slippage Stress Test</t>
+          <t>Correlated-Failure — what if EODHD goes down 24h?</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Double the slippage assumption (ATR/ADV-scaled model from audit #5) and recompute backtest stats. Validates fragile execution dependence per principle #19 (slippage realism).</t>
+          <t>Simulate the impact of the sole data provider (EODHD) being unavailable for 24-48h during market hours. What happens to (a) the scan, (b) live exec, (c) the dashboard?</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Re-run backtest with SLIPPAGE_MULT=2.0; compare WR/PF/Sharpe deltas; if a strategy collapses at 2x slippage it is execution-fragile and should be down-sized. Effort ~1hr.</t>
+          <t>Inject EODHD error responses in a paper environment; observe failure modes (fallback to last-known cache vs hard error vs degraded scan); document recovery RTO; tighten any silent-fail paths discovered. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -4270,13 +4270,13 @@
       <c r="M77" s="3" t="inlineStr"/>
       <c r="N77" s="8" t="inlineStr"/>
     </row>
-    <row r="78" ht="60" customHeight="1">
+    <row r="78" ht="45" customHeight="1">
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>TEST-CORRELATED-FAILURE</t>
+          <t>TEST-CRASH-REPLAY</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Correlated-Failure — what if EODHD goes down 24h?</t>
+          <t>Crash Replay — 2008/2020/2022 stress</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Simulate the impact of the sole data provider (EODHD) being unavailable for 24-48h during market hours. What happens to (a) the scan, (b) live exec, (c) the dashboard?</t>
+          <t>Apply current portfolio composition to historical crash days (2008 GFC, 2020 COVID, 2022 rate-shock); measure realized drawdown + recovery time per scenario.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Inject EODHD error responses in a paper environment; observe failure modes (fallback to last-known cache vs hard error vs degraded scan); document recovery RTO; tighten any silent-fail paths discovered. Effort 2-3hr.</t>
+          <t>Snapshot today's positions; price-replay against historical daily OHLC from those windows; report per-crisis max-DD and time-to-recovery. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -4316,13 +4316,13 @@
       <c r="M78" s="3" t="inlineStr"/>
       <c r="N78" s="8" t="inlineStr"/>
     </row>
-    <row r="79" ht="45" customHeight="1">
+    <row r="79" ht="60" customHeight="1">
       <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>TEST-CRASH-REPLAY</t>
+          <t>TEST-KELLY-SIM</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
@@ -4337,17 +4337,17 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Crash Replay — 2008/2020/2022 stress</t>
+          <t>Half-Kelly vs Full-Kelly sizing simulation</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Apply current portfolio composition to historical crash days (2008 GFC, 2020 COVID, 2022 rate-shock); measure realized drawdown + recovery time per scenario.</t>
+          <t>Visualize portfolio growth under Half-Kelly (current default) vs Full-Kelly vs Quarter-Kelly sizing rules; quantifies the volatility-vs-CAGR tradeoff that principle #9 codifies.</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Snapshot today's positions; price-replay against historical daily OHLC from those windows; report per-crisis max-DD and time-to-recovery. Effort 2-3hr.</t>
+          <t>Bootstrap N portfolio paths under each Kelly fraction; chart median equity curve + percentile fans; surface terminal-wealth distribution. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>TEST-KELLY-SIM</t>
+          <t>TEST-SLIPPAGE-ATTR</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Half-Kelly vs Full-Kelly sizing simulation</t>
+          <t>Slippage Attribution — signal PnL vs realized PnL gap</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Visualize portfolio growth under Half-Kelly (current default) vs Full-Kelly vs Quarter-Kelly sizing rules; quantifies the volatility-vs-CAGR tradeoff that principle #9 codifies.</t>
+          <t>For each closed trade, compute the gap between the model's predicted entry/exit and the actual fill price. Aggregate by setup/ticker/regime to find where slippage eats edge.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Bootstrap N portfolio paths under each Kelly fraction; chart median equity curve + percentile fans; surface terminal-wealth distribution. Effort ~2hr.</t>
+          <t>Read signal_log entries (which has the signal price) and join to paper_fills.json (which has the realized price); compute slippage_bp per trade; group + percentile. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>TEST-SLIPPAGE-ATTR</t>
+          <t>TEST-TAX-AWARE</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
@@ -4429,17 +4429,17 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Slippage Attribution — signal PnL vs realized PnL gap</t>
+          <t>Tax-Aware Backtest — short-term cap-gains haircut</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>For each closed trade, compute the gap between the model's predicted entry/exit and the actual fill price. Aggregate by setup/ticker/regime to find where slippage eats edge.</t>
+          <t>Apply short-term capital-gains tax (35-40% on gains held &lt;1yr) to backtest PnL. Real after-tax return for a US retail account is materially lower than gross.</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Read signal_log entries (which has the signal price) and join to paper_fills.json (which has the realized price); compute slippage_bp per trade; group + percentile. Effort ~2hr.</t>
+          <t>Add post_tax_pnl column to backtest output; apply 35% haircut to short-term gains (&gt;0 PnL, held &lt;365d) and 15% to long-term; report Sharpe / total-return pre vs post tax. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>TEST-TAX-AWARE</t>
+          <t>WAIT-CALIB-DRIFT-SPARK</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
@@ -4470,22 +4470,22 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Testing / Validation (Tier 3)</t>
+          <t>Time-Dependent / Calibration</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Tax-Aware Backtest — short-term cap-gains haircut</t>
+          <t>Calibration drift sparkline populates</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Apply short-term capital-gains tax (35-40% on gains held &lt;1yr) to backtest PnL. Real after-tax return for a US retail account is materially lower than gross.</t>
+          <t>The calibration-drift sparkline in the ML Edge sub-tab needs multiple training cycles to populate (weeks). Each morning scan retrains and appends a calibration row; the sparkline reads from that history table.</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Add post_tax_pnl column to backtest output; apply 35% haircut to short-term gains (&gt;0 PnL, held &lt;365d) and 15% to long-term; report Sharpe / total-return pre vs post tax. Effort ~2hr.</t>
+          <t>Passive wait. Re-check after 4-6 weekly retrain cycles. If still empty, verify ml.train_historical writes to cache/ml/calibration_history.jsonl on each run.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -4500,13 +4500,13 @@
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="8" t="inlineStr"/>
     </row>
-    <row r="83" ht="60" customHeight="1">
+    <row r="83" ht="45" customHeight="1">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>WAIT-CALIB-DRIFT-SPARK</t>
+          <t>WAIT-DRIFT-SNAPSHOTS</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
@@ -4516,22 +4516,22 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Calibration</t>
+          <t>Time-Dependent / Drift Tracking</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Calibration drift sparkline populates</t>
+          <t>Diff vs yesterday + 30-day drift populate</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>The calibration-drift sparkline in the ML Edge sub-tab needs multiple training cycles to populate (weeks). Each morning scan retrains and appends a calibration row; the sparkline reads from that history table.</t>
+          <t>The 'diff vs yesterday' + 30-day drift columns need 2+ daily snapshots stored. Starts populating tomorrow's scan.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check after 4-6 weekly retrain cycles. If still empty, verify ml.train_historical writes to cache/ml/calibration_history.jsonl on each run.</t>
+          <t>Passive wait; first populated values appear in the next morning's scan output. Verify the snapshot persister wrote a row today.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>WAIT-DRIFT-SNAPSHOTS</t>
+          <t>WAIT-ML-PICKS-RESOLVE</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
@@ -4562,22 +4562,22 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Drift Tracking</t>
+          <t>Time-Dependent / Picks History</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Diff vs yesterday + 30-day drift populate</t>
+          <t>Picks-history outcome resolution (resolve_ml_picks.py)</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>The 'diff vs yesterday' + 30-day drift columns need 2+ daily snapshots stored. Starts populating tomorrow's scan.</t>
+          <t>resolve_ml_picks.py needs 5 trading days from each pick to resolve outcomes. First AI Edge batch (picks from ~2026-05-18) resolves around 2026-05-23.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Passive wait; first populated values appear in the next morning's scan output. Verify the snapshot persister wrote a row today.</t>
+          <t>Passive wait. Re-check on 2026-05-23; verify resolve_ml_picks.py runs in run_daily_scan.sh and populates picks_history.json outcome columns.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -4592,13 +4592,13 @@
       <c r="M84" s="3" t="inlineStr"/>
       <c r="N84" s="8" t="inlineStr"/>
     </row>
-    <row r="85" ht="45" customHeight="1">
+    <row r="85" ht="60" customHeight="1">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>WAIT-ML-PICKS-RESOLVE</t>
+          <t>WAIT-SURVIVORSHIP-DECAY</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
@@ -4608,22 +4608,22 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Picks History</t>
+          <t>Time-Dependent / Survivorship Haircut</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>Picks-history outcome resolution (resolve_ml_picks.py)</t>
+          <t>Survivorship haircut shrinking 3pp -&gt; 0.5pp</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>resolve_ml_picks.py needs 5 trading days from each pick to resolve outcomes. First AI Edge batch (picks from ~2026-05-18) resolves around 2026-05-23.</t>
+          <t>The -3pp WR survivorship haircut should shrink as monthly S&amp;P 500 / R1000 membership snapshots accumulate (Wikipedia revision history). Once 24+ months of snapshots are stored, the haircut can fade toward 0.5pp.</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check on 2026-05-23; verify resolve_ml_picks.py runs in run_daily_scan.sh and populates picks_history.json outcome columns.</t>
+          <t>Passive wait — currently only current-membership data. Re-evaluate annually. Until then keep -3pp haircut per CLAUDE.md principle #6.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>WAIT-SURVIVORSHIP-DECAY</t>
+          <t>WAIT-WF-EQUITY-REAL</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
@@ -4654,22 +4654,22 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Survivorship Haircut</t>
+          <t>Time-Dependent / Walk-Forward</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Survivorship haircut shrinking 3pp -&gt; 0.5pp</t>
+          <t>Walk-forward equity curve switches to REAL track</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>The -3pp WR survivorship haircut should shrink as monthly S&amp;P 500 / R1000 membership snapshots accumulate (Wikipedia revision history). Once 24+ months of snapshots are stored, the haircut can fade toward 0.5pp.</t>
+          <t>Currently the equity curve renders backtest-derived returns. Switches to REAL track once 5+ resolved AI Edge picks are available — first batch resolves ~2026-05-23, so REAL curve activates ~2026-05-24.</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Passive wait — currently only current-membership data. Re-evaluate annually. Until then keep -3pp haircut per CLAUDE.md principle #6.</t>
+          <t>Passive wait. Re-check on 2026-05-24; verify the equity curve flips from BACKTEST badge to REAL badge once n_resolved &gt;= 5.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>WAIT-WF-EQUITY-REAL</t>
+          <t>PARITY-10-CHARTS-GRID</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
@@ -4700,22 +4700,22 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Walk-Forward</t>
+          <t>UI / Layout / Platform Parity</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward equity curve switches to REAL track</t>
+          <t>10-chart multi-pane grid</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Currently the equity curve renders backtest-derived returns. Switches to REAL track once 5+ resolved AI Edge picks are available — first batch resolves ~2026-05-23, so REAL curve activates ~2026-05-24.</t>
+          <t>Display up to 10 ticker charts side-by-side in a configurable grid (2x5, 3x4, etc.) for at-a-glance correlation/leadership reads — what TrendSpider and Trade Ideas users default to.</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check on 2026-05-24; verify the equity curve flips from BACKTEST badge to REAL badge once n_resolved &gt;= 5.</t>
+          <t>New 'Grid' workspace in kairos that renders N lightweight-chart canvases; ticker list drag-droppable; persists ticker set per layout.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>PARITY-10-CHARTS-GRID</t>
+          <t>PARITY-CUSTOM-LAYOUTS</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
@@ -4751,17 +4751,17 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>10-chart multi-pane grid</t>
+          <t>Customizable Layouts (save/load workspace presets)</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Display up to 10 ticker charts side-by-side in a configurable grid (2x5, 3x4, etc.) for at-a-glance correlation/leadership reads — what TrendSpider and Trade Ideas users default to.</t>
+          <t>User drags/resizes panels in the kairos workspace and saves the arrangement as a named preset (Day-Trade view / Swing view / Research view) and switches between them.</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>New 'Grid' workspace in kairos that renders N lightweight-chart canvases; ticker list drag-droppable; persists ticker set per layout.</t>
+          <t>Persist layout JSON in cache/user_layouts.json (per-user once auth lands); sidebar dropdown to switch; default presets shipped (Swing / Position / Research).</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
@@ -4776,84 +4776,84 @@
       <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="8" t="inlineStr"/>
     </row>
-    <row r="89" ht="60" customHeight="1">
+    <row r="89" ht="90" customHeight="1">
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>PARITY-CUSTOM-LAYOUTS</t>
-        </is>
-      </c>
-      <c r="C89" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>RANK-REBUILD-2026-06-13</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>UI / Layout / Platform Parity</t>
+          <t>Signal Screener</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>Customizable Layouts (save/load workspace presets)</t>
+          <t>Regime-conditional rank score (composite anti-correlation fix)</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>User drags/resizes panels in the kairos workspace and saves the arrangement as a named preset (Day-Trade view / Swing view / Research view) and switches between them.</t>
+          <t>Composite 5-pillar score is ANTI-correlated with realized return (IC -0.10, t=-4.0); inversion is regime-conditional + Zacks/news bonus is a crowding fade. Built signal_rank.compute_rank_score (regime-conditional cat+qg-led blend from PRE-bonus pillar norms); composite demoted to &gt;=60 quality gate. Validated: per-day top tercile PF 1.01-&gt;1.71; absolute rank&gt;=50 =&gt; PF 1.91 monotone.</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>Persist layout JSON in cache/user_layouts.json (per-user once auth lands); sidebar dropdown to switch; default presets shipped (Swing / Position / Research).</t>
+          <t>Flag-gated config.regime_conditional_ranker._enabled (DEFAULT OFF). rank_score always computed+emitted for A/B; drives verdict in decision_engine only when enabled. Activation path: paper A/B + per-regime rank_buy_threshold calibration before live (principle 19).</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="5" t="inlineStr"/>
       <c r="J89" s="5" t="inlineStr"/>
-      <c r="K89" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="K89" s="11" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="8" t="inlineStr"/>
     </row>
-    <row r="90" ht="90" customHeight="1">
+    <row r="90" ht="60" customHeight="1">
       <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>RANK-REBUILD-2026-06-13</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>ENTRY-WATCH-2</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Signal Screener</t>
+          <t>Alerts</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional rank score (composite anti-correlation fix)</t>
+          <t>Validate entry-zone event before live alerts</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Composite 5-pillar score is ANTI-correlated with realized return (IC -0.10, t=-4.0); inversion is regime-conditional + Zacks/news bonus is a crowding fade. Built signal_rank.compute_rank_score (regime-conditional cat+qg-led blend from PRE-bonus pillar norms); composite demoted to &gt;=60 quality gate. Validated: per-day top tercile PF 1.01-&gt;1.71; absolute rank&gt;=50 =&gt; PF 1.91 monotone.</t>
+          <t>Zone-entry event unvalidated; naive proxies anti-predictive (score r=-0.10, entry-quality inverted). Zero-EODHD audit-ledger analysis: TC zone-entries PF 1.8 @2-5d (n=65), BE 0.78, Impulse 0.15 -- but IN-SAMPLE</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Flag-gated config.regime_conditional_ranker._enabled (DEFAULT OFF). rank_score always computed+emitted for A/B; drives verdict in decision_engine only when enabled. Activation path: paper A/B + per-regime rank_buy_threshold calibration before live (principle 19).</t>
+          <t>SHADOW logs all bullish-extended families to cache/entry_watch_shadow.jsonl; family allowlist (TC-only) wired as live send-gate; flip send_enabled only after OOS shadow record clears PF~1.2 n&gt;=30 at half-size</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
@@ -4868,38 +4868,38 @@
       <c r="M90" s="3" t="inlineStr"/>
       <c r="N90" s="8" t="inlineStr"/>
     </row>
-    <row r="91" ht="60" customHeight="1">
+    <row r="91" ht="90" customHeight="1">
       <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-WATCH-2</t>
-        </is>
-      </c>
-      <c r="C91" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>SMC-OB-CONFLUENCE-1</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Alerts</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>Validate entry-zone event before live alerts</t>
+          <t>BOS+FVG order-block confluence</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Zone-entry event unvalidated; naive proxies anti-predictive (score r=-0.10, entry-quality inverted). Zero-EODHD audit-ledger analysis: TC zone-entries PF 1.8 @2-5d (n=65), BE 0.78, Impulse 0.15 -- but IN-SAMPLE</t>
+          <t>OBs scored in isolation — no BOS-confirmation or FVG-confluence boost despite both being detected separately; the strongest OBs have both.</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>SHADOW logs all bullish-extended families to cache/entry_watch_shadow.jsonl; family allowlist (TC-only) wired as live send-gate; flip send_enabled only after OOS shadow record clears PF~1.2 n&gt;=30 at half-size</t>
+          <t>Implemented flag-gated ob_confluence in smart_money.score_smc() (config scoring.smc_ob_confluence._enabled, default OFF): tags BOS+FVG confluence on fresh bullish OBs, applies bonus only when enabled. Extended validate_ob_confluence.py with OB-BOS-FVG intersection subsets. Validated on 154-trade backtest: all subsets n&lt;30 (full confluence n=5) -&gt; INSUFFICIENT, flag stays OFF pending n&gt;=30.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
@@ -4914,13 +4914,13 @@
       <c r="M91" s="3" t="inlineStr"/>
       <c r="N91" s="8" t="inlineStr"/>
     </row>
-    <row r="92" ht="90" customHeight="1">
+    <row r="92" ht="75" customHeight="1">
       <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>SMC-OB-CONFLUENCE-1</t>
+          <t>STRUCT-TARGETS-PHASE2</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
@@ -4930,27 +4930,39 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>BOS+FVG order-block confluence</t>
+          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>OBs scored in isolation — no BOS-confirmation or FVG-confluence boost despite both being detected separately; the strongest OBs have both.</t>
+          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>Implemented flag-gated ob_confluence in smart_money.score_smc() (config scoring.smc_ob_confluence._enabled, default OFF): tags BOS+FVG confluence on fresh bullish OBs, applies bonus only when enabled. Extended validate_ob_confluence.py with OB-BOS-FVG intersection subsets. Validated on 154-trade backtest: all subsets n&lt;30 (full confluence n=5) -&gt; INSUFFICIENT, flag stays OFF pending n&gt;=30.</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="5" t="inlineStr"/>
-      <c r="J92" s="5" t="inlineStr"/>
+          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>1 day + backtest</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>High win potential, medium risk</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
+        </is>
+      </c>
       <c r="K92" s="11" t="inlineStr">
         <is>
           <t>IN_PROGRESS</t>
@@ -4958,7 +4970,11 @@
       </c>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="3" t="inlineStr"/>
-      <c r="N92" s="8" t="inlineStr"/>
+      <c r="N92" s="8" t="inlineStr">
+        <is>
+          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="75" customHeight="1">
       <c r="A93" s="2" t="n">
@@ -4966,69 +4982,77 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-PHASE2</t>
-        </is>
-      </c>
-      <c r="C93" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>1 day + backtest</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>High win potential, medium risk</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J93" s="5" t="inlineStr">
         <is>
-          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
-        </is>
-      </c>
-      <c r="K93" s="11" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr"/>
-      <c r="M93" s="3" t="inlineStr"/>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+        </is>
+      </c>
+      <c r="K93" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>2c9b9f339</t>
+        </is>
+      </c>
       <c r="N93" s="8" t="inlineStr">
         <is>
-          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="75" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="90" customHeight="1">
       <c r="A94" s="2" t="n">
         <v>93</v>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>B3-WEEKLY-FIX</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -5038,37 +5062,29 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I94" s="5" t="inlineStr">
-        <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
-        </is>
-      </c>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="5" t="inlineStr"/>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
         </is>
       </c>
       <c r="K94" s="12" t="inlineStr">
@@ -5078,27 +5094,27 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>2c9b9f339</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N94" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="90" customHeight="1">
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="75" customHeight="1">
       <c r="A95" s="2" t="n">
         <v>94</v>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>B3-WEEKLY-FIX</t>
+          <t>VARIANT-F-BT</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -5108,31 +5124,27 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Bug Fix</t>
+          <t>Backtest Parity</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
+          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
+          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="5" t="inlineStr"/>
-      <c r="J95" s="5" t="inlineStr">
-        <is>
-          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
-        </is>
-      </c>
+      <c r="J95" s="5" t="inlineStr"/>
       <c r="K95" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5145,22 +5157,18 @@
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N95" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N95" s="8" t="inlineStr"/>
+    </row>
+    <row r="96" ht="45" customHeight="1">
       <c r="A96" s="2" t="n">
         <v>95</v>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F-BT</t>
+          <t>P0-WEEKLY</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -5170,27 +5178,39 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Backtest Parity</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="5" t="inlineStr"/>
-      <c r="J96" s="5" t="inlineStr"/>
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL — system was unable to backtest</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+        </is>
+      </c>
       <c r="K96" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5203,18 +5223,22 @@
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N96" s="8" t="inlineStr"/>
-    </row>
-    <row r="97" ht="45" customHeight="1">
+          <t>985cd182b</t>
+        </is>
+      </c>
+      <c r="N96" s="8" t="inlineStr">
+        <is>
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="75" customHeight="1">
       <c r="A97" s="2" t="n">
         <v>96</v>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>P0-WEEKLY</t>
+          <t>SIGLOG-ORDER-FIX</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -5224,39 +5248,27 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Data Integrity</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
+          <t>signal_log records pre-ranker verdicts</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
+          <t>signal_log was written BEFORE the canonical compute_final_verdict (ranker/gate_floor/kill) pass, so it logged pre-ranker buy_candidates as BUY (e.g. 27 BUYs when engine emitted 1-2). Contaminated tracker win-rate, rolling_sharpe_kill, audit ledger, and all signal-quality analysis.</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="I97" s="5" t="inlineStr">
-        <is>
-          <t>CRITICAL — system was unable to backtest</t>
-        </is>
-      </c>
-      <c r="J97" s="5" t="inlineStr">
-        <is>
-          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
-        </is>
-      </c>
+          <t>Deferred the signal_log write in swing_trade.py to AFTER the canonical verdict pass + reroute (uses rerouted bundle[buy_candidates]/[watch_list]); logs BUYs as BUY, genuine WATCH as WATCH, AVOID/WAIT excluded. Verified static (last_bundle: 1 BUY vs 27). Needs weekday-scan end-to-end confirm.</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="5" t="inlineStr"/>
+      <c r="J97" s="5" t="inlineStr"/>
       <c r="K97" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5264,19 +5276,15 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N97" s="8" t="inlineStr">
-        <is>
-          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
-        </is>
-      </c>
+          <t>0a768e81e</t>
+        </is>
+      </c>
+      <c r="N97" s="8" t="inlineStr"/>
     </row>
     <row r="98" ht="75" customHeight="1">
       <c r="A98" s="2" t="n">
@@ -5284,7 +5292,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>SIGLOG-ORDER-FIX</t>
+          <t>ROLLING-SHARPE-FIX</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -5294,22 +5302,22 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Data Integrity</t>
+          <t>Decision Engine / Bug</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>signal_log records pre-ranker verdicts</t>
+          <t>Rolling-Sharpe brake firing on contaminated data</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>signal_log was written BEFORE the canonical compute_final_verdict (ranker/gate_floor/kill) pass, so it logged pre-ranker buy_candidates as BUY (e.g. 27 BUYs when engine emitted 1-2). Contaminated tracker win-rate, rolling_sharpe_kill, audit ledger, and all signal-quality analysis.</t>
+          <t>Two bugs: (a) WATCH-conviction signals being written with verdict='BUY' inflated loss count; (b) same physical trade re-emitted as fresh daily signal counted 3× in rolling-20 window. Net: false brake activation pausing ALL new BUYs system-wide. Real Sharpe -0.42; system reported -1.732</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Deferred the signal_log write in swing_trade.py to AFTER the canonical verdict pass + reroute (uses rerouted bundle[buy_candidates]/[watch_list]); logs BUYs as BUY, genuine WATCH as WATCH, AVOID/WAIT excluded. Verified static (last_bundle: 1 BUY vs 27). Needs weekday-scan end-to-end confirm.</t>
+          <t>Upstream fix: swing_trade.py line 3110 _resolve_verdict() detects WATCH conviction and overrides bucket label. Read-time fix: decision_engine.compute_rolling_sharpe_kill_state dedupes by (ticker,entry,pnl,exit_reason). Historical cleanup: scripts/dedupe_signal_log.py removed 133 mislabels + 90 dupes (backed up)</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
@@ -5322,23 +5330,23 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>0a768e81e</t>
+          <t>27fd646b1</t>
         </is>
       </c>
       <c r="N98" s="8" t="inlineStr"/>
     </row>
-    <row r="99" ht="75" customHeight="1">
+    <row r="99" ht="90" customHeight="1">
       <c r="A99" s="2" t="n">
         <v>98</v>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>ROLLING-SHARPE-FIX</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -5348,27 +5356,39 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine / Bug</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>Rolling-Sharpe brake firing on contaminated data</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>Two bugs: (a) WATCH-conviction signals being written with verdict='BUY' inflated loss count; (b) same physical trade re-emitted as fresh daily signal counted 3× in rolling-20 window. Net: false brake activation pausing ALL new BUYs system-wide. Real Sharpe -0.42; system reported -1.732</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>Upstream fix: swing_trade.py line 3110 _resolve_verdict() detects WATCH conviction and overrides bucket label. Read-time fix: decision_engine.compute_rolling_sharpe_kill_state dedupes by (ticker,entry,pnl,exit_reason). Historical cleanup: scripts/dedupe_signal_log.py removed 133 mislabels + 90 dupes (backed up)</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="5" t="inlineStr"/>
-      <c r="J99" s="5" t="inlineStr"/>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+        </is>
+      </c>
       <c r="K99" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5376,23 +5396,27 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N99" s="8" t="inlineStr"/>
-    </row>
-    <row r="100" ht="90" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N99" s="8" t="inlineStr">
+        <is>
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="60" customHeight="1">
       <c r="A100" s="2" t="n">
         <v>99</v>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>EXEC-TRADABLE-ENUM</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -5402,39 +5426,27 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Execution · Auto-Trade</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Stock executor skipped all active names (enum bug)</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>alpaca-py AssetStatus enum stringified to 'AssetStatus.ACTIVE'; check 'assetstatus.active' != 'active' wrongly skipped EVERY tradable stock since ~2026-05-28 → stock auto-trade silently dead, options-only</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I100" s="5" t="inlineStr">
-        <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
-        </is>
-      </c>
-      <c r="J100" s="5" t="inlineStr">
-        <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
-        </is>
-      </c>
+          <t>executor.py: read enum .value ('active') before lowercasing</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="5" t="inlineStr"/>
+      <c r="J100" s="5" t="inlineStr"/>
       <c r="K100" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5442,27 +5454,23 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N100" s="8" t="inlineStr">
-        <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="60" customHeight="1">
+          <t>c7098178a</t>
+        </is>
+      </c>
+      <c r="N100" s="8" t="inlineStr"/>
+    </row>
+    <row r="101" ht="105" customHeight="1">
       <c r="A101" s="2" t="n">
         <v>100</v>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>EXEC-TRADABLE-ENUM</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -5472,27 +5480,39 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Execution · Auto-Trade</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>Stock executor skipped all active names (enum bug)</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>alpaca-py AssetStatus enum stringified to 'AssetStatus.ACTIVE'; check 'assetstatus.active' != 'active' wrongly skipped EVERY tradable stock since ~2026-05-28 → stock auto-trade silently dead, options-only</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>executor.py: read enum .value ('active') before lowercasing</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="5" t="inlineStr"/>
-      <c r="J101" s="5" t="inlineStr"/>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+        </is>
+      </c>
       <c r="K101" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5500,15 +5520,19 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>c7098178a</t>
-        </is>
-      </c>
-      <c r="N101" s="8" t="inlineStr"/>
+          <t>0574c60d4</t>
+        </is>
+      </c>
+      <c r="N101" s="8" t="inlineStr">
+        <is>
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="105" customHeight="1">
       <c r="A102" s="2" t="n">
@@ -5516,7 +5540,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>ML-FEATURE-MISMATCH</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -5526,39 +5550,27 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>ML · Inference</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>Live predict_one degenerate — 29-feat model vs 17-feat extractor</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Models retrained 2026-06-09 on 29 features but ml.feature_extractor.FEATURE_COLS still emits 17, so live predict_one feeds a mismatched vector and returns ~0 p_up for EVERY ticker (AI Edge 0% bug, all names). Batch ml-predict path extracts 29 correctly. /api/ml now prefers the batch cache + rejects degenerate live; ROOT FIX still needed: align FEATURE_COLS to 29 (or guard retrain to the live feature set). Also cache 4d stale.</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I102" s="5" t="inlineStr">
-        <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
-        </is>
-      </c>
-      <c r="J102" s="5" t="inlineStr">
-        <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
-        </is>
-      </c>
+          <t>server /api/ml cache-first + degenerate guard (done); align ml/feature_extractor.FEATURE_COLS to model n_features_in_ (pending)</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="5" t="inlineStr"/>
+      <c r="J102" s="5" t="inlineStr"/>
       <c r="K102" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5566,27 +5578,23 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
-        </is>
-      </c>
-      <c r="N102" s="8" t="inlineStr">
-        <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="105" customHeight="1">
+          <t>33877186c</t>
+        </is>
+      </c>
+      <c r="N102" s="8" t="inlineStr"/>
+    </row>
+    <row r="103" ht="45" customHeight="1">
       <c r="A103" s="2" t="n">
         <v>102</v>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>ML-FEATURE-MISMATCH</t>
+          <t>IPAD-3</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -5596,27 +5604,39 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>ML · Inference</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>Live predict_one degenerate — 29-feat model vs 17-feat extractor</t>
+          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>Models retrained 2026-06-09 on 29 features but ml.feature_extractor.FEATURE_COLS still emits 17, so live predict_one feeds a mismatched vector and returns ~0 p_up for EVERY ticker (AI Edge 0% bug, all names). Batch ml-predict path extracts 29 correctly. /api/ml now prefers the batch cache + rejects degenerate live; ROOT FIX still needed: align FEATURE_COLS to 29 (or guard retrain to the live feature set). Also cache 4d stale.</t>
+          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>server /api/ml cache-first + degenerate guard (done); align ml/feature_extractor.FEATURE_COLS to model n_features_in_ (pending)</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="5" t="inlineStr"/>
-      <c r="J103" s="5" t="inlineStr"/>
+          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>Low / Required</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
+        </is>
+      </c>
       <c r="K103" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5624,23 +5644,27 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
-          <t>33877186c</t>
-        </is>
-      </c>
-      <c r="N103" s="8" t="inlineStr"/>
-    </row>
-    <row r="104" ht="45" customHeight="1">
+          <t>b0e5ef6a1</t>
+        </is>
+      </c>
+      <c r="N103" s="8" t="inlineStr">
+        <is>
+          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="120" customHeight="1">
       <c r="A104" s="2" t="n">
         <v>103</v>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>IPAD-3</t>
+          <t>ALPACA-SYNC</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -5650,39 +5674,27 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Paper Trading/State Sync</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
+          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
+          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="I104" s="5" t="inlineStr">
-        <is>
-          <t>Low / Required</t>
-        </is>
-      </c>
-      <c r="J104" s="5" t="inlineStr">
-        <is>
-          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
-        </is>
-      </c>
+          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="5" t="inlineStr"/>
+      <c r="J104" s="5" t="inlineStr"/>
       <c r="K104" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5695,22 +5707,18 @@
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
-          <t>b0e5ef6a1</t>
-        </is>
-      </c>
-      <c r="N104" s="8" t="inlineStr">
-        <is>
-          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="120" customHeight="1">
+          <t>f26e1deb2</t>
+        </is>
+      </c>
+      <c r="N104" s="8" t="inlineStr"/>
+    </row>
+    <row r="105" ht="60" customHeight="1">
       <c r="A105" s="2" t="n">
         <v>104</v>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>ALPACA-SYNC</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -5720,27 +5728,39 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Paper Trading/State Sync</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="5" t="inlineStr"/>
-      <c r="J105" s="5" t="inlineStr"/>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+        </is>
+      </c>
       <c r="K105" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5748,23 +5768,27 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>f26e1deb2</t>
-        </is>
-      </c>
-      <c r="N105" s="8" t="inlineStr"/>
-    </row>
-    <row r="106" ht="60" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N105" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="45" customHeight="1">
       <c r="A106" s="2" t="n">
         <v>105</v>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -5779,32 +5803,32 @@
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K106" s="12" t="inlineStr">
@@ -5824,7 +5848,7 @@
       </c>
       <c r="N106" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5858,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -5849,17 +5873,17 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5869,12 +5893,12 @@
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K107" s="12" t="inlineStr">
@@ -5894,17 +5918,17 @@
       </c>
       <c r="N107" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="45" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="60" customHeight="1">
       <c r="A108" s="2" t="n">
         <v>107</v>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>Q1-step4</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -5919,32 +5943,32 @@
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K108" s="12" t="inlineStr">
@@ -5954,27 +5978,27 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N108" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="60" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="180" customHeight="1">
       <c r="A109" s="2" t="n">
         <v>108</v>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
+          <t>Q1-step5</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -5989,32 +6013,32 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K109" s="12" t="inlineStr">
@@ -6029,22 +6053,22 @@
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N109" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="180" customHeight="1">
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="45" customHeight="1">
       <c r="A110" s="2" t="n">
         <v>109</v>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
+          <t>Q1-step6</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -6059,32 +6083,32 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K110" s="12" t="inlineStr">
@@ -6099,22 +6123,22 @@
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N110" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="90" customHeight="1">
       <c r="A111" s="2" t="n">
         <v>110</v>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -6124,37 +6148,37 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K111" s="12" t="inlineStr">
@@ -6164,27 +6188,27 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>f47958fc9</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N111" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="90" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="45" customHeight="1">
       <c r="A112" s="2" t="n">
         <v>111</v>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -6194,22 +6218,22 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6219,12 +6243,12 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K112" s="12" t="inlineStr">
@@ -6239,12 +6263,12 @@
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N112" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6278,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -6269,32 +6293,32 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K113" s="12" t="inlineStr">
@@ -6309,22 +6333,22 @@
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N113" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="45" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="105" customHeight="1">
       <c r="A114" s="2" t="n">
         <v>113</v>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>VAR-F</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -6334,37 +6358,29 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Recovery</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>shipped (revert candidate)</t>
-        </is>
-      </c>
-      <c r="I114" s="5" t="inlineStr">
-        <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
-        </is>
-      </c>
+          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="5" t="inlineStr"/>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
         </is>
       </c>
       <c r="K114" s="12" t="inlineStr">
@@ -6374,27 +6390,27 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>f0a66543e + 363984181</t>
         </is>
       </c>
       <c r="N114" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="105" customHeight="1">
+          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="60" customHeight="1">
       <c r="A115" s="2" t="n">
         <v>114</v>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>VAR-F</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -6404,29 +6420,37 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>Quant / Recovery</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr"/>
-      <c r="I115" s="5" t="inlineStr"/>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>Win: single most important Vinod rule per coaching call.</t>
+        </is>
+      </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K115" s="12" t="inlineStr">
@@ -6436,27 +6460,27 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e + 363984181</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N115" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="90" customHeight="1">
       <c r="A116" s="2" t="n">
         <v>115</v>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -6466,37 +6490,37 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
         </is>
       </c>
       <c r="K116" s="12" t="inlineStr">
@@ -6506,27 +6530,27 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N116" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="90" customHeight="1">
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="75" customHeight="1">
       <c r="A117" s="2" t="n">
         <v>116</v>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>KILL-MULT0</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -6536,39 +6560,27 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Scoring/Kill List</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>in flight</t>
-        </is>
-      </c>
-      <c r="I117" s="5" t="inlineStr">
-        <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
-        </is>
-      </c>
-      <c r="J117" s="5" t="inlineStr">
-        <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
-        </is>
-      </c>
+          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="5" t="inlineStr"/>
+      <c r="J117" s="5" t="inlineStr"/>
       <c r="K117" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6581,22 +6593,18 @@
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
-        </is>
-      </c>
-      <c r="N117" s="8" t="inlineStr">
-        <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N117" s="8" t="inlineStr"/>
+    </row>
+    <row r="118" ht="45" customHeight="1">
       <c r="A118" s="2" t="n">
         <v>117</v>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>KILL-MULT0</t>
+          <t>VARIANT-F</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -6606,27 +6614,39 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Scoring/Kill List</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
+          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
+          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr"/>
-      <c r="I118" s="5" t="inlineStr"/>
-      <c r="J118" s="5" t="inlineStr"/>
+          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>High — addresses #1 PF drag</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+        </is>
+      </c>
       <c r="K118" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6639,18 +6659,22 @@
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N118" s="8" t="inlineStr"/>
-    </row>
-    <row r="119" ht="45" customHeight="1">
+          <t>f0a66543e</t>
+        </is>
+      </c>
+      <c r="N118" s="8" t="inlineStr">
+        <is>
+          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="60" customHeight="1">
       <c r="A119" s="2" t="n">
         <v>118</v>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -6660,37 +6684,37 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>High — addresses #1 PF drag</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K119" s="12" t="inlineStr">
@@ -6700,17 +6724,17 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N119" s="8" t="inlineStr">
         <is>
-          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
         </is>
       </c>
     </row>
@@ -6720,7 +6744,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -6735,17 +6759,17 @@
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6755,12 +6779,12 @@
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
       <c r="K120" s="12" t="inlineStr">
@@ -6775,12 +6799,12 @@
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N120" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6814,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>STRATEGY-TUNE-20260519</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -6800,39 +6824,27 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Strategy Tuning</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>5 data-backed fixes from 986-trade backtest analysis</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>Sector blocklist (Energy/BasicMat/ConsumerCyclical/CommServices), FRESH entry block, Impulse Catalyst kill in choppy, score floor 65, MISSED relaxed in trending</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I121" s="5" t="inlineStr">
-        <is>
-          <t>Win: bull-only strategy, period.</t>
-        </is>
-      </c>
-      <c r="J121" s="5" t="inlineStr">
-        <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
-        </is>
-      </c>
+          <t>decision_engine.py + config.json</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="5" t="inlineStr"/>
+      <c r="J121" s="5" t="inlineStr"/>
       <c r="K121" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6840,27 +6852,23 @@
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N121" s="8" t="inlineStr">
-        <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="60" customHeight="1">
+          <t>29578a5fb</t>
+        </is>
+      </c>
+      <c r="N121" s="8" t="inlineStr"/>
+    </row>
+    <row r="122" ht="75" customHeight="1">
       <c r="A122" s="2" t="n">
         <v>121</v>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>STRATEGY-TUNE-20260519</t>
+          <t>TARGET-CAP-10WK</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -6870,22 +6878,22 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Strategy Tuning</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>5 data-backed fixes from 986-trade backtest analysis</t>
+          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>Sector blocklist (Energy/BasicMat/ConsumerCyclical/CommServices), FRESH entry block, Impulse Catalyst kill in choppy, score floor 65, MISSED relaxed in trending</t>
+          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>decision_engine.py + config.json</t>
+          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr"/>
@@ -6898,23 +6906,23 @@
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
-          <t>29578a5fb</t>
+          <t>87336f2de</t>
         </is>
       </c>
       <c r="N122" s="8" t="inlineStr"/>
     </row>
-    <row r="123" ht="75" customHeight="1">
+    <row r="123" ht="45" customHeight="1">
       <c r="A123" s="2" t="n">
         <v>122</v>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-10WK</t>
+          <t>STOCKSMITH-MODE-CASCADE</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -6924,22 +6932,22 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>V2 Dashboard / Detail</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
+          <t>Global SWING/POSITION/INVESTMENT mode cascade (§5,A,B)</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
+          <t>mode drives Overview/Plan/Risk-cones/AI-Edge/Chart-TF/Options-DTE + cross-mode + defensive tape + projection; window.__tmode</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
+          <t>Stocksmith.html AICrossMode + MODE_TF/MODE_DTE + SmrRiskCones</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr"/>
@@ -6952,12 +6960,12 @@
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M123" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
+          <t>eb83a151d</t>
         </is>
       </c>
       <c r="N123" s="8" t="inlineStr"/>
@@ -6968,7 +6976,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-MODE-CASCADE</t>
+          <t>STOCKSMITH-AI-CHART</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -6978,22 +6986,22 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Detail</t>
+          <t>V2 Dashboard / ML Predictions</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>Global SWING/POSITION/INVESTMENT mode cascade (§5,A,B)</t>
+          <t>AI Price-Projection Chart (§1)</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>mode drives Overview/Plan/Risk-cones/AI-Edge/Chart-TF/Options-DTE + cross-mode + defensive tape + projection; window.__tmode</t>
+          <t>candlestick chart MA20/50/200 + swing dots + breakout box + mode-aware forward AI zone/target; real OHLCV + /api/ml quantiles; AI Edge + Patterns</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html AICrossMode + MODE_TF/MODE_DTE + SmrRiskCones</t>
+          <t>Stocksmith.html AIProjectionChart</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr"/>
@@ -7011,7 +7019,7 @@
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>eb83a151d</t>
+          <t>a5dcb06c9</t>
         </is>
       </c>
       <c r="N124" s="8" t="inlineStr"/>
@@ -7022,7 +7030,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-AI-CHART</t>
+          <t>STOCKSMITH-OPTIONS-CALC</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -7032,22 +7040,22 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / ML Predictions</t>
+          <t>V2 Dashboard / Options</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>AI Price-Projection Chart (§1)</t>
+          <t>Options Profit Calculator grid + manual mode/presets (§2+§8)</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>candlestick chart MA20/50/200 + swing dots + breakout box + mode-aware forward AI zone/target; real OHLCV + /api/ml quantiles; AI Edge + Patterns</t>
+          <t>%-return-on-premium heatmap, IV-shift + ER crush, 6 strategy presets, BS pricer; real Schwab spot/IV/DTE</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html AIProjectionChart</t>
+          <t>Stocksmith.html OtkProfitGrid + eoBuildOptTicket</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr"/>
@@ -7065,43 +7073,43 @@
       </c>
       <c r="M125" s="3" t="inlineStr">
         <is>
-          <t>a5dcb06c9</t>
+          <t>932cef7fe</t>
         </is>
       </c>
       <c r="N125" s="8" t="inlineStr"/>
     </row>
-    <row r="126" ht="45" customHeight="1">
+    <row r="126" ht="60" customHeight="1">
       <c r="A126" s="2" t="n">
         <v>125</v>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-OPTIONS-CALC</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>ENTRY-WATCH-1</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Options</t>
+          <t>Alerts</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>Options Profit Calculator grid + manual mode/presets (§2+§8)</t>
+          <t>Intraday entry-zone watcher</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>%-return-on-premium heatmap, IV-shift + ER crush, 6 strategy presets, BS pricer; real Schwab spot/IV/DTE</t>
+          <t>Bullish-bias names had no intraday alert when they pulled into a buyable zone; morning briefing only pushed actionable BUYs, so extended WATCH names (e.g. VIRT) were silently missed</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html OtkProfitGrid + eoBuildOptTicket</t>
+          <t>entry_watch.py: per-name EMA/ATR/S-R buy zone from last_bundle; Schwab batch quote (zero EODHD); two-tier soft/firm; launchd com.swingtrade.entrywatch 5min market-hours. SHADOW MODE default (send_enabled=false) until validated</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr"/>
@@ -7114,23 +7122,23 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
-          <t>932cef7fe</t>
+          <t>696b8d033</t>
         </is>
       </c>
       <c r="N126" s="8" t="inlineStr"/>
     </row>
-    <row r="127" ht="60" customHeight="1">
+    <row r="127" ht="45" customHeight="1">
       <c r="A127" s="2" t="n">
         <v>126</v>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-WATCH-1</t>
+          <t>PICK-FORENSICS</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
@@ -7140,22 +7148,22 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>Alerts</t>
+          <t>Audit / Attribution</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>Intraday entry-zone watcher</t>
+          <t>Why did BUY lose / AVOID win — per-pick post-mortem</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>Bullish-bias names had no intraday alert when they pulled into a buyable zone; morning briefing only pushed actionable BUYs, so extended WATCH names (e.g. VIRT) were silently missed</t>
+          <t>join decision verdict+gates x realized outcome x setup-regime stats; aggregate where calls fail</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>entry_watch.py: per-name EMA/ATR/S-R buy zone from last_bundle; Schwab batch quote (zero EODHD); two-tier soft/firm; launchd com.swingtrade.entrywatch 5min market-hours. SHADOW MODE default (send_enabled=false) until validated</t>
+          <t>scripts/pick_forensics.py + dashboard tab</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr"/>
@@ -7168,23 +7176,23 @@
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
-          <t>696b8d033</t>
+          <t>5e6375889</t>
         </is>
       </c>
       <c r="N127" s="8" t="inlineStr"/>
     </row>
-    <row r="128" ht="45" customHeight="1">
+    <row r="128" ht="75" customHeight="1">
       <c r="A128" s="2" t="n">
         <v>127</v>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>PICK-FORENSICS</t>
+          <t>AUDIT-PENDING-UX</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
@@ -7194,22 +7202,22 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Audit / Attribution</t>
+          <t>Audit Trail / Maturation UX</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>Why did BUY lose / AVOID win — per-pick post-mortem</t>
+          <t>Pending rows handled cleanly · maturation chip · refresh button · TTL cache</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>join decision verdict+gates x realized outcome x setup-regime stats; aggregate where calls fail</t>
+          <t>Records with no matured horizon get faded 50% opacity + 🕓 prefix. Default 'Hide Pending' filter ON so user opens to actionable data. Manual ↻ Refresh button busts cache. 5-min TTL on _ledgerCache so backend rebuilds become visible without page reload. Toolbar shows N matured · K pending · generated Nm ago</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>scripts/pick_forensics.py + dashboard tab</t>
+          <t>kairos.html QuantHistoryLedger _filters.hidePending + _qauditTogglePending + _qauditForceRefresh + qhist-pending CSS class</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr"/>
@@ -7222,12 +7230,12 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
-          <t>5e6375889</t>
+          <t>dfbe955fe</t>
         </is>
       </c>
       <c r="N128" s="8" t="inlineStr"/>
@@ -7238,7 +7246,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>AUDIT-PENDING-UX</t>
+          <t>AUDIT-D0-INTRADAY</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
@@ -7248,22 +7256,22 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Audit Trail / Maturation UX</t>
+          <t>Audit Trail / Same-Day Returns</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>Pending rows handled cleanly · maturation chip · refresh button · TTL cache</t>
+          <t>D0 column · same-day entry→close return</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>Records with no matured horizon get faded 50% opacity + 🕓 prefix. Default 'Hide Pending' filter ON so user opens to actionable data. Manual ↻ Refresh button busts cache. 5-min TTL on _ledgerCache so backend rebuilds become visible without page reload. Toolbar shows N matured · K pending · generated Nm ago</t>
+          <t>Today's picks now show real return on same day instead of waiting until tomorrow's close. Computed in build_audit_ledger.py for any pick where price_at_pick differs from anchor close by ≥0.05%. Today: 112/117 May 18 picks show D0 (ZS +8.47%, VRT -8.41%)</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantHistoryLedger _filters.hidePending + _qauditTogglePending + _qauditForceRefresh + qhist-pending CSS class</t>
+          <t>infra/prototype/build_audit_ledger.py d0 computation + kairos.html D0 column + DAILY group colspan 7→8</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr"/>
@@ -7286,13 +7294,13 @@
       </c>
       <c r="N129" s="8" t="inlineStr"/>
     </row>
-    <row r="130" ht="75" customHeight="1">
+    <row r="130" ht="60" customHeight="1">
       <c r="A130" s="2" t="n">
         <v>129</v>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>AUDIT-D0-INTRADAY</t>
+          <t>AUDIT-LEDGER-CADENCE</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
@@ -7302,22 +7310,22 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Audit Trail / Same-Day Returns</t>
+          <t>Audit Trail / Scheduled Rebuilds</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>D0 column · same-day entry→close return</t>
+          <t>Multi-time-of-day ledger rebuild</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>Today's picks now show real return on same day instead of waiting until tomorrow's close. Computed in build_audit_ledger.py for any pick where price_at_pick differs from anchor close by ≥0.05%. Today: 112/117 May 18 picks show D0 (ZS +8.47%, VRT -8.41%)</t>
+          <t>Three new launchd jobs · 9/11/3 PM PT intraday · 1:30 PM PT post-close · combined with the existing 6:30 AM morning briefing's audit rebuild. Yesterday's D1 fills 30 min after today's close. Today's D0 updates every 2hrs intraday</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>infra/prototype/build_audit_ledger.py d0 computation + kairos.html D0 column + DAILY group colspan 7→8</t>
+          <t>infra/launchd/com.swingtrade.audit-ledger-eod.plist + .audit-ledger-intraday.plist</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr"/>
@@ -7340,13 +7348,13 @@
       </c>
       <c r="N130" s="8" t="inlineStr"/>
     </row>
-    <row r="131" ht="60" customHeight="1">
+    <row r="131" ht="75" customHeight="1">
       <c r="A131" s="2" t="n">
         <v>130</v>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>AUDIT-LEDGER-CADENCE</t>
+          <t>AUTO-STOP-FLATTEN</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
@@ -7356,22 +7364,22 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Audit Trail / Scheduled Rebuilds</t>
+          <t>Automation</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>Multi-time-of-day ledger rebuild</t>
+          <t>Auto-engine past-stop flatten</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>Three new launchd jobs · 9/11/3 PM PT intraday · 1:30 PM PT post-close · combined with the existing 6:30 AM morning briefing's audit rebuild. Yesterday's D1 fills 30 min after today's close. Today's D0 updates every 2hrs intraday</t>
+          <t>Protective-stop placement emitted structurally-invalid StopOrderRequest when price had already breached the stop (long last&lt;=stop / short last&gt;=stop); Alpaca rejected it and the position was left naked (NEM short Jun-2/Jun-4, AFRM/RVTY Jun-2).</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd/com.swingtrade.audit-ledger-eod.plist + .audit-ledger-intraday.plist</t>
+          <t>Added PAST-STOP GUARD in auto_engine.py exit loop block 5a: if price past stop, market-close (flatten) via close_position instead of submitting invalid stop; Slack AUTO-STOP-HIT alert; logged as CLOSE. Validated against 5 historical cases.</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr"/>
@@ -7384,12 +7392,12 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
-          <t>dfbe955fe</t>
+          <t>033e2b1a8</t>
         </is>
       </c>
       <c r="N131" s="8" t="inlineStr"/>
@@ -7400,7 +7408,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>AUTO-STOP-FLATTEN</t>
+          <t>AUTO-STOP-SIDE</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
@@ -7410,22 +7418,22 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Automation</t>
+          <t>Automation / Exits</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>Auto-engine past-stop flatten</t>
+          <t>Wrong-sided protective stop on shorts</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>Protective-stop placement emitted structurally-invalid StopOrderRequest when price had already breached the stop (long last&lt;=stop / short last&gt;=stop); Alpaca rejected it and the position was left naked (NEM short Jun-2/Jun-4, AFRM/RVTY Jun-2).</t>
+          <t>auto_engine.run_exits blindly submitted the stored plan stop; a long-style stop (entry-ATR) synced onto a short is a buy-stop below market -&gt; Alpaca rejects it ('stop price must be greater than current price'), leaving the short unprotected (NEM).</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>Added PAST-STOP GUARD in auto_engine.py exit loop block 5a: if price past stop, market-close (flatten) via close_position instead of submitting invalid stop; Slack AUTO-STOP-HIT alert; logged as CLOSE. Validated against 5 historical cases.</t>
+          <t>Added _protective_stop() validating side vs live price (sell-stop below mkt for longs, buy-stop above for shorts); self-heals missing/wrong-sided stops to a side-correct fallback. Placed live NEM buy-stop $116.61; corrected stored portfolio_state stop 98.18-&gt;116.61.</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr"/>
@@ -7438,23 +7446,23 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>033e2b1a8</t>
+          <t>2e5dff9a0</t>
         </is>
       </c>
       <c r="N132" s="8" t="inlineStr"/>
     </row>
-    <row r="133" ht="75" customHeight="1">
+    <row r="133" ht="60" customHeight="1">
       <c r="A133" s="2" t="n">
         <v>132</v>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>AUTO-STOP-SIDE</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
@@ -7464,27 +7472,39 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>Automation / Exits</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>Wrong-sided protective stop on shorts</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>auto_engine.run_exits blindly submitted the stored plan stop; a long-style stop (entry-ATR) synced onto a short is a buy-stop below market -&gt; Alpaca rejects it ('stop price must be greater than current price'), leaving the short unprotected (NEM).</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Added _protective_stop() validating side vs live price (sell-stop below mkt for longs, buy-stop above for shorts); self-heals missing/wrong-sided stops to a side-correct fallback. Placed live NEM buy-stop $116.61; corrected stored portfolio_state stop 98.18-&gt;116.61.</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr"/>
-      <c r="I133" s="5" t="inlineStr"/>
-      <c r="J133" s="5" t="inlineStr"/>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>shipped (diagnosis); pending (fix)</t>
+        </is>
+      </c>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+        </is>
+      </c>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
+        </is>
+      </c>
       <c r="K133" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -7492,23 +7512,27 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>2e5dff9a0</t>
-        </is>
-      </c>
-      <c r="N133" s="8" t="inlineStr"/>
-    </row>
-    <row r="134" ht="60" customHeight="1">
+          <t>9bc015562</t>
+        </is>
+      </c>
+      <c r="N133" s="8" t="inlineStr">
+        <is>
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="105" customHeight="1">
       <c r="A134" s="2" t="n">
         <v>133</v>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>BACKTEST-MTM-CLOSE</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
@@ -7518,37 +7542,37 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
+          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
         </is>
       </c>
       <c r="K134" s="12" t="inlineStr">
@@ -7558,27 +7582,27 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N134" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="105" customHeight="1">
+          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="45" customHeight="1">
       <c r="A135" s="2" t="n">
         <v>134</v>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>BACKTEST-MTM-CLOSE</t>
+          <t>PERF-OPT-1</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
@@ -7588,37 +7612,37 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
+          <t>backtest.py --smoke (5d quick-validate mode)</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
+          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
+          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K135" s="12" t="inlineStr">
@@ -7628,7 +7652,7 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M135" s="3" t="inlineStr">
@@ -7638,7 +7662,7 @@
       </c>
       <c r="N135" s="8" t="inlineStr">
         <is>
-          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
+          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
         </is>
       </c>
     </row>
@@ -7648,7 +7672,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-1</t>
+          <t>PERF-OPT-2</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
@@ -7663,22 +7687,22 @@
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --smoke (5d quick-validate mode)</t>
+          <t>yfinance info disk cache (24h TTL)</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
+          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
+          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I136" s="5" t="inlineStr">
@@ -7688,7 +7712,7 @@
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
         </is>
       </c>
       <c r="K136" s="12" t="inlineStr">
@@ -7708,7 +7732,7 @@
       </c>
       <c r="N136" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
+          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7742,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-2</t>
+          <t>PERF-OPT-3</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
@@ -7733,32 +7757,32 @@
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>yfinance info disk cache (24h TTL)</t>
+          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
+          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
+          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Low risk / High win (evidence-based opt)</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K137" s="12" t="inlineStr">
@@ -7778,17 +7802,17 @@
       </c>
       <c r="N137" s="8" t="inlineStr">
         <is>
-          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="45" customHeight="1">
+          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="60" customHeight="1">
       <c r="A138" s="2" t="n">
         <v>137</v>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-3</t>
+          <t>PERF-OPT-4</t>
         </is>
       </c>
       <c r="C138" s="9" t="inlineStr">
@@ -7803,32 +7827,32 @@
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
+          <t>walk_forward_v2 fold parallelization (--parallel)</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
+          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
+          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win (evidence-based opt)</t>
+          <t>Low risk / Massive time savings</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
         </is>
       </c>
       <c r="K138" s="12" t="inlineStr">
@@ -7848,17 +7872,17 @@
       </c>
       <c r="N138" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="60" customHeight="1">
+          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="105" customHeight="1">
       <c r="A139" s="2" t="n">
         <v>138</v>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-4</t>
+          <t>BULLVEDA-FUNNEL-MARKETGATE</t>
         </is>
       </c>
       <c r="C139" s="9" t="inlineStr">
@@ -7868,39 +7892,27 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>BullVeda / Home</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>walk_forward_v2 fold parallelization (--parallel)</t>
+          <t>Scan funnel paints whole universe bearish on market-gate days</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
+          <t>On a market-wide entry-gate day (SPY -2.6% + 7 distribution days, 2026-06-08) the Home scan funnel showed 0 bullish / 0 neutral / 1000 avoid: realFunnel read decisions_by_mode (stamped AVOID on every gate-blocked name) and the universe tile read scan_count from the empty all_scored list. Engine was correct (no new longs on a crash day); the dashboard misrepresented it as universe-wide bearishness.</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>1 hr</t>
-        </is>
-      </c>
-      <c r="I139" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / Massive time savings</t>
-        </is>
-      </c>
-      <c r="J139" s="5" t="inlineStr">
-        <is>
-          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
-        </is>
-      </c>
+          <t>realFunnel un-collapses entry-gate AVOIDs to the composite verdict + adds a 'no new longs today' banner (committed 57df99939/eb960bde8); build_data.py scan_count = len(all_scored)+len(killed); served data.critical.json scan_count patched 0-&gt;1000.</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr"/>
+      <c r="I139" s="5" t="inlineStr"/>
+      <c r="J139" s="5" t="inlineStr"/>
       <c r="K139" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -7908,27 +7920,23 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N139" s="8" t="inlineStr">
-        <is>
-          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="105" customHeight="1">
+          <t>eb960bde8</t>
+        </is>
+      </c>
+      <c r="N139" s="8" t="inlineStr"/>
+    </row>
+    <row r="140" ht="45" customHeight="1">
       <c r="A140" s="2" t="n">
         <v>139</v>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>BULLVEDA-FUNNEL-MARKETGATE</t>
+          <t>PEAD-7</t>
         </is>
       </c>
       <c r="C140" s="9" t="inlineStr">
@@ -7938,22 +7946,22 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>BullVeda / Home</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>Scan funnel paints whole universe bearish on market-gate days</t>
+          <t>PEAD data pipeline</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>On a market-wide entry-gate day (SPY -2.6% + 7 distribution days, 2026-06-08) the Home scan funnel showed 0 bullish / 0 neutral / 1000 avoid: realFunnel read decisions_by_mode (stamped AVOID on every gate-blocked name) and the universe tile read scan_count from the empty all_scored list. Engine was correct (no new longs on a crash day); the dashboard misrepresented it as universe-wide bearishness.</t>
+          <t>Wire EODHD past-earnings surprise + post-report gap</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>realFunnel un-collapses entry-gate AVOIDs to the composite verdict + adds a 'no new longs today' banner (committed 57df99939/eb960bde8); build_data.py scan_count = len(all_scored)+len(killed); served data.critical.json scan_count patched 0-&gt;1000.</t>
+          <t>data_fetcher._load_recent_earnings_surprises_global + _compute_post_report_gap_pct; revenue + analyst-revision gates relaxed (data not plumbed yet)</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr"/>
@@ -7966,23 +7974,23 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
-          <t>eb960bde8</t>
+          <t>f089b48ef</t>
         </is>
       </c>
       <c r="N140" s="8" t="inlineStr"/>
     </row>
-    <row r="141" ht="45" customHeight="1">
+    <row r="141" ht="60" customHeight="1">
       <c r="A141" s="2" t="n">
         <v>140</v>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>PEAD-7</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C141" s="9" t="inlineStr">
@@ -7992,27 +8000,39 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>PEAD data pipeline</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>Wire EODHD past-earnings surprise + post-report gap</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher._load_recent_earnings_surprises_global + _compute_post_report_gap_pct; revenue + analyst-revision gates relaxed (data not plumbed yet)</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr"/>
-      <c r="I141" s="5" t="inlineStr"/>
-      <c r="J141" s="5" t="inlineStr"/>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>10 min after answer</t>
+        </is>
+      </c>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
+          <t>Win: -158 lines + clearer docs.</t>
+        </is>
+      </c>
+      <c r="J141" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+        </is>
+      </c>
       <c r="K141" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8020,23 +8040,27 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>f089b48ef</t>
-        </is>
-      </c>
-      <c r="N141" s="8" t="inlineStr"/>
-    </row>
-    <row r="142" ht="60" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N141" s="8" t="inlineStr">
+        <is>
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="90" customHeight="1">
       <c r="A142" s="2" t="n">
         <v>141</v>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C142" s="9" t="inlineStr">
@@ -8051,32 +8075,32 @@
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>30 min after answers</t>
         </is>
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Win: ~3-5K lines if mostly stale.</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K142" s="12" t="inlineStr">
@@ -8096,17 +8120,17 @@
       </c>
       <c r="N142" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="90" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="75" customHeight="1">
       <c r="A143" s="2" t="n">
         <v>142</v>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>FUNNEL-BIAS-1</t>
         </is>
       </c>
       <c r="C143" s="9" t="inlineStr">
@@ -8116,39 +8140,27 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>Scan funnel collapses on macro-gate days</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>BullVeda home SCAN FUNNEL classified direction by the macro-gated action verdict, not bias. On the 2026-06-11 CPI blackout day the top-level gate flattened every verdict to WAIT, so the funnel showed 1 bullish / 1074 neutral / 0 avoid when the real bias distribution was 263 bull / 456 neu / 189 bear.</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>30 min after answers</t>
-        </is>
-      </c>
-      <c r="I143" s="5" t="inlineStr">
-        <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
-        </is>
-      </c>
-      <c r="J143" s="5" t="inlineStr">
-        <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
-        </is>
-      </c>
+          <t>realFunnel now classifies by the per-mode bias axis (decisions_by_mode[key].bias -&gt; raw.bias -&gt; window.biasRead), gate-blind; gateBlocked overlay + extracted gateReason (top-level decision.reason) drives the 'No new longs today · Macro blackout: CPI — 719 entry-gated' banner. Rebuilt via build_bullveda.cjs.</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr"/>
+      <c r="I143" s="5" t="inlineStr"/>
+      <c r="J143" s="5" t="inlineStr"/>
       <c r="K143" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8156,19 +8168,15 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N143" s="8" t="inlineStr">
-        <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
+          <t>1d6fdb14a</t>
+        </is>
+      </c>
+      <c r="N143" s="8" t="inlineStr"/>
     </row>
     <row r="144" ht="75" customHeight="1">
       <c r="A144" s="2" t="n">
@@ -8176,7 +8184,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>FUNNEL-BIAS-1</t>
+          <t>FUNNEL-BIAS-2</t>
         </is>
       </c>
       <c r="C144" s="9" t="inlineStr">
@@ -8191,17 +8199,17 @@
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>Scan funnel collapses on macro-gate days</t>
+          <t>Funnel click-through blanked the scanner</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>BullVeda home SCAN FUNNEL classified direction by the macro-gated action verdict, not bias. On the 2026-06-11 CPI blackout day the top-level gate flattened every verdict to WAIT, so the funnel showed 1 bullish / 1074 neutral / 0 avoid when the real bias distribution was 263 bull / 456 neu / 189 bear.</t>
+          <t>Clicking the SCAN FUNNEL 'bullish' stat passed scan('BUY') which filtered the scanner by t.verdict==='BUY'. After FUNNEL-BIAS-1 the funnel counts by bias (263) but the scanner still filtered by the macro-gated verdict (1 BUY on CPI day) -&gt; scanner showed blank.</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>realFunnel now classifies by the per-mode bias axis (decisions_by_mode[key].bias -&gt; raw.bias -&gt; window.biasRead), gate-blind; gateBlocked overlay + extracted gateReason (top-level decision.reason) drives the 'No new longs today · Macro blackout: CPI — 719 entry-gated' banner. Rebuilt via build_bullveda.cjs.</t>
+          <t>Added per-mode biasByMode to the scanRows row (boot.js from decisions_by_mode[k].bias); scanner 'Directional bias' side toggle now filters by per-mode bias (window.__tmode) with t.bias-&gt;verdict fallback. Funnel and scanner now show identical per-mode counts (swing 263/456/189). Rebuilt.</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr"/>
@@ -8224,13 +8232,13 @@
       </c>
       <c r="N144" s="8" t="inlineStr"/>
     </row>
-    <row r="145" ht="75" customHeight="1">
+    <row r="145" ht="90" customHeight="1">
       <c r="A145" s="2" t="n">
         <v>144</v>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>FUNNEL-BIAS-2</t>
+          <t>FUNNEL-BIAS-3</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
@@ -8245,17 +8253,17 @@
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>Funnel click-through blanked the scanner</t>
+          <t>Scanner frozen to page-load snapshot</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>Clicking the SCAN FUNNEL 'bullish' stat passed scan('BUY') which filtered the scanner by t.verdict==='BUY'. After FUNNEL-BIAS-1 the funnel counts by bias (263) but the scanner still filtered by the macro-gated verdict (1 BUY on CPI day) -&gt; scanner showed blank.</t>
+          <t>surface-signal SS_UNIVERSE is a module-level const evaluated once at page-load; the rows memo read it directly. The home SCAN FUNNEL reads scanRows() live every render, so after any data auto-refresh (5-min poll) or a new scan landing, funnel and scanner drifted apart — funnel 336 (live per-mode bullish) vs scanner 233 (older frozen snapshot).</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>Added per-mode biasByMode to the scanRows row (boot.js from decisions_by_mode[k].bias); scanner 'Directional bias' side toggle now filters by per-mode bias (window.__tmode) with t.bias-&gt;verdict fallback. Funnel and scanner now show identical per-mode counts (swing 263/456/189). Rebuilt.</t>
+          <t>rows memo now reads window.__BV.scanRows() live (with SS_UNIVERSE mock fallback offline) instead of the frozen const, so the scanner always reflects the same snapshot the funnel does. Rebuilt.</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr"/>
@@ -8278,13 +8286,13 @@
       </c>
       <c r="N145" s="8" t="inlineStr"/>
     </row>
-    <row r="146" ht="90" customHeight="1">
+    <row r="146" ht="105" customHeight="1">
       <c r="A146" s="2" t="n">
         <v>145</v>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>FUNNEL-BIAS-3</t>
+          <t>SCANNER-FILTER-AUDIT-1</t>
         </is>
       </c>
       <c r="C146" s="9" t="inlineStr">
@@ -8299,17 +8307,17 @@
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>Scanner frozen to page-load snapshot</t>
+          <t>Scanner filter audit — 6 bugs</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>surface-signal SS_UNIVERSE is a module-level const evaluated once at page-load; the rows memo read it directly. The home SCAN FUNNEL reads scanRows() live every render, so after any data auto-refresh (5-min poll) or a new scan landing, funnel and scanner drifted apart — funnel 336 (live per-mode bullish) vs scanner 233 (older frozen snapshot).</t>
+          <t>Full audit of scanner tabs+pills+side+columns. Bugs: (1) INSIDER pill filtered t.sent NEWS sentiment not insider data; (2) INSIDER signal flag filtered empty insUsd; (3) EXCLUDED tab used gated verdict==AVOID → 0 on macro-gate days; (4) FRESH tab was a slice(0,3) placeholder; (5) TOP 20% SCORE pill used absolute score&gt;=70 (top ~12pct) not a real percentile; (6) tab badge counts frozen to module-const SS_UNIVERSE (EARNINGS 161 vs live 36).</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>rows memo now reads window.__BV.scanRows() live (with SS_UNIVERSE mock fallback offline) instead of the frozen const, so the scanner always reflects the same snapshot the funnel does. Rebuilt.</t>
+          <t>INSIDER pill+signal -&gt; insider_net&gt;0; EXCLUDED -&gt; bias bearish (matches funnel, 224); FRESH -&gt; entry_quality==FRESH (125); TOP20 -&gt; true 80th-pctile (score&gt;=63, 220); tab counts recomputed live from scanRows. Rebuilt. Noted feed-limited: insider_usd empty, ai-edge p_up sparse, breakout pill = family-match incl coiled.</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr"/>
@@ -8327,18 +8335,18 @@
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
-          <t>1d6fdb14a</t>
+          <t>8182c3977</t>
         </is>
       </c>
       <c r="N146" s="8" t="inlineStr"/>
     </row>
-    <row r="147" ht="105" customHeight="1">
+    <row r="147" ht="75" customHeight="1">
       <c r="A147" s="2" t="n">
         <v>146</v>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-FILTER-AUDIT-1</t>
+          <t>STRUCT-LADDER-UNIFY</t>
         </is>
       </c>
       <c r="C147" s="9" t="inlineStr">
@@ -8353,17 +8361,17 @@
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>Scanner filter audit — 6 bugs</t>
+          <t>Unify T1/T2/stop across all surfaces to the Overview structural ladder</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>Full audit of scanner tabs+pills+side+columns. Bugs: (1) INSIDER pill filtered t.sent NEWS sentiment not insider data; (2) INSIDER signal flag filtered empty insUsd; (3) EXCLUDED tab used gated verdict==AVOID → 0 on macro-gate days; (4) FRESH tab was a slice(0,3) placeholder; (5) TOP 20% SCORE pill used absolute score&gt;=70 (top ~12pct) not a real percentile; (6) tab badge counts frozen to module-const SS_UNIVERSE (EARNINGS 161 vs live 36).</t>
+          <t>Three divergent ladders: scanner/chat used canonical_trade_plan (split-poisoned, NOW swing showed t1=35.33/t2=-8.95/rr=-3.21), decisions_by_mode used ATR 3R5R, Overview used structural target_engine — same ticker showed different numbers per tab/chat</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>INSIDER pill+signal -&gt; insider_net&gt;0; EXCLUDED -&gt; bias bearish (matches funnel, 224); FRESH -&gt; entry_quality==FRESH (125); TOP20 -&gt; true 80th-pctile (score&gt;=63, 220); tab counts recomputed live from scanRows. Rebuilt. Noted feed-limited: insider_usd empty, ai-edge p_up sparse, breakout pill = family-match incl coiled.</t>
+          <t>Phase 1 DISPLAY-ONLY: server.py _structural_ladder() overlays precomputed cache/target_engine/{SYM}_{MODE} onto each scan row (stop/entry/t1/t2/t3/rr) + struct_by_mode; surface-agent.jsx chat binds plan to trade_engine cache per mode + stops substituting ML q-levels. Verdict gate untouched (decisions_by_mode)</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr"/>
@@ -8376,23 +8384,23 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
-          <t>8182c3977</t>
+          <t>4660fbe26</t>
         </is>
       </c>
       <c r="N147" s="8" t="inlineStr"/>
     </row>
-    <row r="148" ht="75" customHeight="1">
+    <row r="148" ht="60" customHeight="1">
       <c r="A148" s="2" t="n">
         <v>147</v>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-LADDER-UNIFY</t>
+          <t>EODHD-RATE-FIX</t>
         </is>
       </c>
       <c r="C148" s="9" t="inlineStr">
@@ -8402,22 +8410,22 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Data / EODHD (rate-limit)</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>Unify T1/T2/stop across all surfaces to the Overview structural ladder</t>
+          <t>Per-minute rate-limit fix — enrichment burst</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>Three divergent ladders: scanner/chat used canonical_trade_plan (split-poisoned, NOW swing showed t1=35.33/t2=-8.95/rr=-3.21), decisions_by_mode used ATR 3R5R, Overview used structural target_engine — same ticker showed different numbers per tab/chat</t>
+          <t>max_enrichment_tickers regressed 3000 (was 300/700); deep-enriched ~2500 tickers x ~14 endpoints, bursting EODHD 950/min. Reverted to validated 700. Bulk endpoint + dedup were ALREADY done (brief diagnosis was wrong).</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 DISPLAY-ONLY: server.py _structural_ladder() overlays precomputed cache/target_engine/{SYM}_{MODE} onto each scan row (stop/entry/t1/t2/t3/rr) + struct_by_mode; surface-agent.jsx chat binds plan to trade_engine cache per mode + stops substituting ML q-levels. Verdict gate untouched (decisions_by_mode)</t>
+          <t>config max_enrichment_tickers + job-restructure (cross-process limiter)</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr"/>
@@ -8430,23 +8438,23 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
-          <t>4660fbe26</t>
+          <t>0a346032b</t>
         </is>
       </c>
       <c r="N148" s="8" t="inlineStr"/>
     </row>
-    <row r="149" ht="60" customHeight="1">
+    <row r="149" ht="75" customHeight="1">
       <c r="A149" s="2" t="n">
         <v>148</v>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>EODHD-RATE-FIX</t>
+          <t>SIGLOG-VERIFY-MON</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
@@ -8456,22 +8464,22 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>Data / EODHD (rate-limit)</t>
+          <t>Data Integrity</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>Per-minute rate-limit fix — enrichment burst</t>
+          <t>Confirm SIGLOG-ORDER-FIX end-to-end on a live scan</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>max_enrichment_tickers regressed 3000 (was 300/700); deep-enriched ~2500 tickers x ~14 endpoints, bursting EODHD 950/min. Reverted to validated 700. Bulk endpoint + dedup were ALREADY done (brief diagnosis was wrong).</t>
+          <t>The signal_log ordering fix (SIGLOG-ORDER-FIX) is verified statically but not yet on a live post-fix scan (weekend quota gate blocked running one).</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>config max_enrichment_tickers + job-restructure (cross-process limiter)</t>
+          <t>Added scripts/verify_signal_log_fix.py + launchd com.swingtrade.siglog-verify (Mon 7:30am PT, after the 6:30 scan) — compares signal_log BUYs vs canonical bundle BUYs + flags sub-60 leakage, posts result to Slack (PASS=INFO/MISMATCH=WARN). Recurring weekly = ongoing regression guard. Awaiting Monday 2026-06-22 run.</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr"/>
@@ -8484,12 +8492,12 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
-          <t>0a346032b</t>
+          <t>98397f15b</t>
         </is>
       </c>
       <c r="N149" s="8" t="inlineStr"/>
@@ -18280,13 +18288,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" s="18" t="n">
         <v>63</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
@@ -18318,13 +18326,13 @@
         <v>33</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>91</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5">

--- a/cache/open_items_2026-06-20.xlsx
+++ b/cache/open_items_2026-06-20.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N316"/>
+  <dimension ref="A1:N317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -15124,7 +15124,7 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>UI-MLEDGE-1</t>
+          <t>TUNNEL-HARDEN-247</t>
         </is>
       </c>
       <c r="C264" s="10" t="inlineStr">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>ML Edge Tab</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E264" s="6" t="inlineStr">
         <is>
-          <t>Theme switching + tf-* visual port</t>
+          <t>Harden Mac+tunnel for 24/7 always-on serving</t>
         </is>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
+          <t>Serving had two gaps: caffeinate only ran weekday 6:20a-1:20p (Mac could sleep nights/weekends -&gt; server+tunnel unreachable); healthcheck detected origin-down but only alerted a human (no self-heal, and KeepAlive cannot restart a HUNG server)</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
+          <t>Added com.swingtrade.always-awake (caffeinate -i -s, KeepAlive, 24/7 wake lock); tunnel-healthcheck.sh now force-kickstarts com.swingtrade.server on 530/000/502/503/504 before alerting; alert reworded to fire only when self-heal FAILED. Server+cloudflared already had KeepAlive. Residual: cloudflared hang (1033) needs sudo to restart</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr"/>
@@ -15162,23 +15162,23 @@
       </c>
       <c r="L264" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>8b2395396</t>
         </is>
       </c>
       <c r="N264" s="8" t="inlineStr"/>
     </row>
-    <row r="265" ht="45" customHeight="1">
+    <row r="265" ht="90" customHeight="1">
       <c r="A265" s="2" t="n">
         <v>264</v>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>UI-MLEDGE-1</t>
         </is>
       </c>
       <c r="C265" s="10" t="inlineStr">
@@ -15188,39 +15188,27 @@
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>ML Edge Tab</t>
         </is>
       </c>
       <c r="E265" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>Theme switching + tf-* visual port</t>
         </is>
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>ML Edge per-ticker sub-tab had hardcoded dark CSS vars inline on #qd-ml-root, blocking the body.light theme toggle. Workspace ML Edge used legacy rk-* class system, not the prototype tf-* design language.</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
-        </is>
-      </c>
-      <c r="H265" s="2" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="I265" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J265" s="5" t="inlineStr">
-        <is>
-          <t>Sub-task of IPAD-1.</t>
-        </is>
-      </c>
+          <t>Moved palette from inline style to _ensureMlEdgeStyles() with body.light overrides. Then ported workspace QuantMlEdge module to tf-* visual system: tf-hero 3-col + tf-pulse-strip 4 live feeds (top bulls/bears/flips/health) + tf-confluence (4 KPI cells + X/4 score) + tf-vbar (verdict badge). All 6 sections rewritten. Memory: feedback_inline_css_vars_break_theming.md.</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr"/>
+      <c r="I265" s="5" t="inlineStr"/>
+      <c r="J265" s="5" t="inlineStr"/>
       <c r="K265" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15228,19 +15216,15 @@
       </c>
       <c r="L265" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
-        </is>
-      </c>
-      <c r="N265" s="8" t="inlineStr">
-        <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
-        </is>
-      </c>
+          <t>696731a4d</t>
+        </is>
+      </c>
+      <c r="N265" s="8" t="inlineStr"/>
     </row>
     <row r="266" ht="45" customHeight="1">
       <c r="A266" s="2" t="n">
@@ -15248,7 +15232,7 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>SLACK-NEWSLETTER-MLALERT</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C266" s="10" t="inlineStr">
@@ -15258,27 +15242,39 @@
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E266" s="6" t="inlineStr">
         <is>
-          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd + scripts/ml_alert_slack.py</t>
-        </is>
-      </c>
-      <c r="H266" s="2" t="inlineStr"/>
-      <c r="I266" s="5" t="inlineStr"/>
-      <c r="J266" s="5" t="inlineStr"/>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="I266" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J266" s="5" t="inlineStr">
+        <is>
+          <t>Sub-task of IPAD-1.</t>
+        </is>
+      </c>
       <c r="K266" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15286,15 +15282,19 @@
       </c>
       <c r="L266" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
-          <t>d1ea97913</t>
-        </is>
-      </c>
-      <c r="N266" s="8" t="inlineStr"/>
+          <t>79fa01a75</t>
+        </is>
+      </c>
+      <c r="N266" s="8" t="inlineStr">
+        <is>
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="45" customHeight="1">
       <c r="A267" s="2" t="n">
@@ -15302,7 +15302,7 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>FORENSICS-WEEKLY-SLACK</t>
+          <t>SLACK-NEWSLETTER-MLALERT</t>
         </is>
       </c>
       <c r="C267" s="10" t="inlineStr">
@@ -15312,22 +15312,22 @@
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>Notifications / Audit</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="E267" s="6" t="inlineStr">
         <is>
-          <t>Weekly pick-forensics Slack digest</t>
+          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
         </is>
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
-          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
+          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+          <t>infra/launchd + scripts/ml_alert_slack.py</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr"/>
@@ -15345,18 +15345,18 @@
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>d1ea97913</t>
         </is>
       </c>
       <c r="N267" s="8" t="inlineStr"/>
     </row>
-    <row r="268" ht="75" customHeight="1">
+    <row r="268" ht="45" customHeight="1">
       <c r="A268" s="2" t="n">
         <v>267</v>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>FORENSICS-WEEKLY-SLACK</t>
         </is>
       </c>
       <c r="C268" s="10" t="inlineStr">
@@ -15366,39 +15366,27 @@
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Notifications / Audit</t>
         </is>
       </c>
       <c r="E268" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Weekly pick-forensics Slack digest</t>
         </is>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
-        </is>
-      </c>
-      <c r="H268" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I268" s="5" t="inlineStr">
-        <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
-        </is>
-      </c>
-      <c r="J268" s="5" t="inlineStr">
-        <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
-        </is>
-      </c>
+          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr"/>
+      <c r="I268" s="5" t="inlineStr"/>
+      <c r="J268" s="5" t="inlineStr"/>
       <c r="K268" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15406,27 +15394,23 @@
       </c>
       <c r="L268" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N268" s="8" t="inlineStr">
-        <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="269" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N268" s="8" t="inlineStr"/>
+    </row>
+    <row r="269" ht="75" customHeight="1">
       <c r="A269" s="2" t="n">
         <v>268</v>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C269" s="10" t="inlineStr">
@@ -15436,37 +15420,37 @@
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E269" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I269" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J269" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K269" s="12" t="inlineStr">
@@ -15476,17 +15460,17 @@
       </c>
       <c r="L269" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N269" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -15496,7 +15480,7 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C270" s="10" t="inlineStr">
@@ -15511,32 +15495,32 @@
       </c>
       <c r="E270" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I270" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J270" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K270" s="12" t="inlineStr">
@@ -15556,7 +15540,7 @@
       </c>
       <c r="N270" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -15566,7 +15550,7 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C271" s="10" t="inlineStr">
@@ -15581,32 +15565,32 @@
       </c>
       <c r="E271" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I271" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J271" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K271" s="12" t="inlineStr">
@@ -15626,7 +15610,7 @@
       </c>
       <c r="N271" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
         </is>
       </c>
     </row>
@@ -15636,7 +15620,7 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C272" s="10" t="inlineStr">
@@ -15651,32 +15635,32 @@
       </c>
       <c r="E272" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I272" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J272" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K272" s="12" t="inlineStr">
@@ -15686,27 +15670,27 @@
       </c>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N272" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="273" ht="45" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="60" customHeight="1">
       <c r="A273" s="2" t="n">
         <v>272</v>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>SCAN-FAILURE-ALERT</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C273" s="10" t="inlineStr">
@@ -15716,27 +15700,39 @@
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>Ops / Alerts</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E273" s="6" t="inlineStr">
         <is>
-          <t>Scan-failure + EODHD-quota Slack alert</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
-          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>swing_trade.py exit hook</t>
-        </is>
-      </c>
-      <c r="H273" s="2" t="inlineStr"/>
-      <c r="I273" s="5" t="inlineStr"/>
-      <c r="J273" s="5" t="inlineStr"/>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I273" s="5" t="inlineStr">
+        <is>
+          <t>Win: fast iteration on report templates.</t>
+        </is>
+      </c>
+      <c r="J273" s="5" t="inlineStr">
+        <is>
+          <t>Trivial CLI wrapper.</t>
+        </is>
+      </c>
       <c r="K273" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15744,15 +15740,19 @@
       </c>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
-          <t>0dc7675ee</t>
-        </is>
-      </c>
-      <c r="N273" s="8" t="inlineStr"/>
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
+      <c r="N273" s="8" t="inlineStr">
+        <is>
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="45" customHeight="1">
       <c r="A274" s="2" t="n">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
+          <t>SCAN-FAILURE-ALERT</t>
         </is>
       </c>
       <c r="C274" s="10" t="inlineStr">
@@ -15770,22 +15770,22 @@
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>Ops / Launchd</t>
+          <t>Ops / Alerts</t>
         </is>
       </c>
       <c r="E274" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot: load or retire</t>
+          <t>Scan-failure + EODHD-quota Slack alert</t>
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
+          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd</t>
+          <t>swing_trade.py exit hook</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr"/>
@@ -15808,13 +15808,13 @@
       </c>
       <c r="N274" s="8" t="inlineStr"/>
     </row>
-    <row r="275" ht="60" customHeight="1">
+    <row r="275" ht="45" customHeight="1">
       <c r="A275" s="2" t="n">
         <v>274</v>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>OVERVIEW-TQ-LABEL</t>
+          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
         </is>
       </c>
       <c r="C275" s="10" t="inlineStr">
@@ -15824,22 +15824,22 @@
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Ops / Launchd</t>
         </is>
       </c>
       <c r="E275" s="6" t="inlineStr">
         <is>
-          <t>Strategy-Fit verdict used action verbs colliding with canonical verdict</t>
+          <t>Decide momentum-snapshot: load or retire</t>
         </is>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
-          <t>_deriveVerdict emitted BUY·ENTER/HOLD·ADD DIP/WEAK·SKIP from target-quality math in same vocabulary as canonical BUY/WATCH/AVOID action verdict — user could misread the target-quality chip as THE verdict</t>
+          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>relabel to PRIME/GOOD/WEAK TARGET nouns under a TARGET QUALITY caption; canonical exec-brief verdict (binds T.stage) untouched</t>
+          <t>infra/launchd</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr"/>
@@ -15852,23 +15852,23 @@
       </c>
       <c r="L275" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
+          <t>0dc7675ee</t>
         </is>
       </c>
       <c r="N275" s="8" t="inlineStr"/>
     </row>
-    <row r="276" ht="150" customHeight="1">
+    <row r="276" ht="60" customHeight="1">
       <c r="A276" s="2" t="n">
         <v>275</v>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>OVERVIEW-TQ-LABEL</t>
         </is>
       </c>
       <c r="C276" s="10" t="inlineStr">
@@ -15878,31 +15878,27 @@
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="E276" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Strategy-Fit verdict used action verbs colliding with canonical verdict</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>_deriveVerdict emitted BUY·ENTER/HOLD·ADD DIP/WEAK·SKIP from target-quality math in same vocabulary as canonical BUY/WATCH/AVOID action verdict — user could misread the target-quality chip as THE verdict</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+          <t>relabel to PRIME/GOOD/WEAK TARGET nouns under a TARGET QUALITY caption; canonical exec-brief verdict (binds T.stage) untouched</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr"/>
       <c r="I276" s="5" t="inlineStr"/>
-      <c r="J276" s="5" t="inlineStr">
-        <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
-        </is>
-      </c>
+      <c r="J276" s="5" t="inlineStr"/>
       <c r="K276" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15910,27 +15906,23 @@
       </c>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
-        </is>
-      </c>
-      <c r="N276" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="277" ht="105" customHeight="1">
+          <t>15f8f9600</t>
+        </is>
+      </c>
+      <c r="N276" s="8" t="inlineStr"/>
+    </row>
+    <row r="277" ht="150" customHeight="1">
       <c r="A277" s="2" t="n">
         <v>276</v>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>SMC-OB-DISPLAY-1</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C277" s="10" t="inlineStr">
@@ -15940,27 +15932,31 @@
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E277" s="6" t="inlineStr">
         <is>
-          <t>OB confluence badges in SMC tab</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>SMC-tab order blocks (engines/smc.py) showed bare lo/hi/type/state — no BOS/FVG/volume/HTF/reaction confluence context for the user to judge OB quality.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (display-only, informational): engines/smc.py._order_blocks + detect() enrich each OB with bos_type/rel_vol/has_fvg/htf_aligned/reaction/confluence[]/confluence_n; surfaced as a Confluence column + chips in lens-smc-risk.jsx and a board tag in surface-smc-patterns.jsx. smc_score + ranking UNCHANGED. Phase 2 (re-rank on these factors) deferred until OB Wilson-bucket win-rates clear n&gt;=30 OOS per the 500-user signal-enable bar.</t>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr"/>
       <c r="I277" s="5" t="inlineStr"/>
-      <c r="J277" s="5" t="inlineStr"/>
+      <c r="J277" s="5" t="inlineStr">
+        <is>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+        </is>
+      </c>
       <c r="K277" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -15968,23 +15964,27 @@
       </c>
       <c r="L277" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M277" s="3" t="inlineStr">
         <is>
-          <t>8182c3977</t>
-        </is>
-      </c>
-      <c r="N277" s="8" t="inlineStr"/>
-    </row>
-    <row r="278" ht="75" customHeight="1">
+          <t>cf30df858</t>
+        </is>
+      </c>
+      <c r="N277" s="8" t="inlineStr">
+        <is>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="105" customHeight="1">
       <c r="A278" s="2" t="n">
         <v>277</v>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-COMPANY-NAMES</t>
+          <t>SMC-OB-DISPLAY-1</t>
         </is>
       </c>
       <c r="C278" s="10" t="inlineStr">
@@ -15994,22 +15994,22 @@
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>Scanner UI</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="E278" s="6" t="inlineStr">
         <is>
-          <t>NAME column duplicated TICKER (no company names)</t>
+          <t>OB confluence badges in SMC tab</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>Scan feed set name=ticker; no cached name source (fundamentals.db raw_json has 0 names). NAME column was redundant.</t>
+          <t>SMC-tab order blocks (engines/smc.py) showed bare lo/hi/type/state — no BOS/FVG/volume/HTF/reaction confluence context for the user to judge OB quality.</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>Free Wikipedia S&amp;P1500+NDX+Dow name map (scripts/build_ticker_names.py -&gt; cache/ticker_names.json, 1508 names); joined in /api/universe _ticker_names(); weekly refresh in weekly_diagnostics.sh. 70% live coverage, honest ticker fallback for the tail. No paid data.</t>
+          <t>Phase 1 (display-only, informational): engines/smc.py._order_blocks + detect() enrich each OB with bos_type/rel_vol/has_fvg/htf_aligned/reaction/confluence[]/confluence_n; surfaced as a Confluence column + chips in lens-smc-risk.jsx and a board tag in surface-smc-patterns.jsx. smc_score + ranking UNCHANGED. Phase 2 (re-rank on these factors) deferred until OB Wilson-bucket win-rates clear n&gt;=30 OOS per the 500-user signal-enable bar.</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr"/>
@@ -16022,23 +16022,23 @@
       </c>
       <c r="L278" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
-          <t>48f6a2fbf</t>
+          <t>8182c3977</t>
         </is>
       </c>
       <c r="N278" s="8" t="inlineStr"/>
     </row>
-    <row r="279" ht="45" customHeight="1">
+    <row r="279" ht="75" customHeight="1">
       <c r="A279" s="2" t="n">
         <v>278</v>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-1</t>
+          <t>SCANNER-COMPANY-NAMES</t>
         </is>
       </c>
       <c r="C279" s="10" t="inlineStr">
@@ -16048,22 +16048,22 @@
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Scanner UI</t>
         </is>
       </c>
       <c r="E279" s="6" t="inlineStr">
         <is>
-          <t>Sharpe gate in momentum detector</t>
+          <t>NAME column duplicated TICKER (no company names)</t>
         </is>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
-          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
+          <t>Scan feed set name=ticker; no cached name source (fundamentals.db raw_json has 0 names). NAME column was redundant.</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
+          <t>Free Wikipedia S&amp;P1500+NDX+Dow name map (scripts/build_ticker_names.py -&gt; cache/ticker_names.json, 1508 names); joined in /api/universe _ticker_names(); weekly refresh in weekly_diagnostics.sh. 70% live coverage, honest ticker fallback for the tail. No paid data.</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr"/>
@@ -16076,12 +16076,12 @@
       </c>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="M279" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
+          <t>48f6a2fbf</t>
         </is>
       </c>
       <c r="N279" s="8" t="inlineStr"/>
@@ -16092,7 +16092,7 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-10</t>
+          <t>SHARPE-1</t>
         </is>
       </c>
       <c r="C280" s="10" t="inlineStr">
@@ -16107,17 +16107,17 @@
       </c>
       <c r="E280" s="6" t="inlineStr">
         <is>
-          <t>Sharpe alerts for watchlist</t>
+          <t>Sharpe gate in momentum detector</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
+          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr"/>
@@ -16146,7 +16146,7 @@
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-11</t>
+          <t>SHARPE-10</t>
         </is>
       </c>
       <c r="C281" s="10" t="inlineStr">
@@ -16161,17 +16161,17 @@
       </c>
       <c r="E281" s="6" t="inlineStr">
         <is>
-          <t>Per-trade Sharpe attribution</t>
+          <t>Sharpe alerts for watchlist</t>
         </is>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
+          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr"/>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-12</t>
+          <t>SHARPE-11</t>
         </is>
       </c>
       <c r="C282" s="10" t="inlineStr">
@@ -16215,17 +16215,17 @@
       </c>
       <c r="E282" s="6" t="inlineStr">
         <is>
-          <t>Sharpe consistency check</t>
+          <t>Per-trade Sharpe attribution</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
+          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr"/>
@@ -16254,7 +16254,7 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-2</t>
+          <t>SHARPE-12</t>
         </is>
       </c>
       <c r="C283" s="10" t="inlineStr">
@@ -16269,17 +16269,17 @@
       </c>
       <c r="E283" s="6" t="inlineStr">
         <is>
-          <t>Sharpe column in v2 dashboard</t>
+          <t>Sharpe consistency check</t>
         </is>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>Surface 126d Sharpe per ticker as sortable column</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
+          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr"/>
@@ -16308,7 +16308,7 @@
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-3</t>
+          <t>SHARPE-2</t>
         </is>
       </c>
       <c r="C284" s="10" t="inlineStr">
@@ -16323,17 +16323,17 @@
       </c>
       <c r="E284" s="6" t="inlineStr">
         <is>
-          <t>Per-stock Sharpe by regime</t>
+          <t>Sharpe column in v2 dashboard</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>Decompose per-stock Sharpe by historical regime tags</t>
+          <t>Surface 126d Sharpe per ticker as sortable column</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
+          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr"/>
@@ -16362,7 +16362,7 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-4</t>
+          <t>SHARPE-3</t>
         </is>
       </c>
       <c r="C285" s="10" t="inlineStr">
@@ -16377,17 +16377,17 @@
       </c>
       <c r="E285" s="6" t="inlineStr">
         <is>
-          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
+          <t>Per-stock Sharpe by regime</t>
         </is>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
+          <t>Decompose per-stock Sharpe by historical regime tags</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
+          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr"/>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-5</t>
+          <t>SHARPE-4</t>
         </is>
       </c>
       <c r="C286" s="10" t="inlineStr">
@@ -16431,17 +16431,17 @@
       </c>
       <c r="E286" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-weighted position sizing</t>
+          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr"/>
@@ -16470,7 +16470,7 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-6</t>
+          <t>SHARPE-5</t>
         </is>
       </c>
       <c r="C287" s="10" t="inlineStr">
@@ -16485,17 +16485,17 @@
       </c>
       <c r="E287" s="6" t="inlineStr">
         <is>
-          <t>Portfolio Sharpe KPI vs target</t>
+          <t>Sharpe-weighted position sizing</t>
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>Annualized Sharpe target tracking + gap report</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
+          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr"/>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-7</t>
+          <t>SHARPE-6</t>
         </is>
       </c>
       <c r="C288" s="10" t="inlineStr">
@@ -16539,17 +16539,17 @@
       </c>
       <c r="E288" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-based stop sizing</t>
+          <t>Portfolio Sharpe KPI vs target</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Annualized Sharpe target tracking + gap report</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-8</t>
+          <t>SHARPE-7</t>
         </is>
       </c>
       <c r="C289" s="10" t="inlineStr">
@@ -16593,17 +16593,17 @@
       </c>
       <c r="E289" s="6" t="inlineStr">
         <is>
-          <t>Sortino computation alongside Sharpe</t>
+          <t>Sharpe-based stop sizing</t>
         </is>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>Downside-only vol denominator added everywhere</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
+          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr"/>
@@ -16632,7 +16632,7 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-9</t>
+          <t>SHARPE-8</t>
         </is>
       </c>
       <c r="C290" s="10" t="inlineStr">
@@ -16647,17 +16647,17 @@
       </c>
       <c r="E290" s="6" t="inlineStr">
         <is>
-          <t>SPY-Sharpe regime cross-validation</t>
+          <t>Sortino computation alongside Sharpe</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Downside-only vol denominator added everywhere</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr"/>
@@ -16680,13 +16680,13 @@
       </c>
       <c r="N290" s="8" t="inlineStr"/>
     </row>
-    <row r="291" ht="60" customHeight="1">
+    <row r="291" ht="45" customHeight="1">
       <c r="A291" s="2" t="n">
         <v>290</v>
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-RECUR-CHIP</t>
+          <t>SHARPE-9</t>
         </is>
       </c>
       <c r="C291" s="10" t="inlineStr">
@@ -16696,22 +16696,22 @@
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>Signal Scanner</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E291" s="6" t="inlineStr">
         <is>
-          <t>Recurrence chip</t>
+          <t>SPY-Sharpe regime cross-validation</t>
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker 'seen N× + W-L' chip on scanner rows, deep-links to Track Record · The Ledger filtered for that ticker</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>Server: _signal_recurrence_map() over signal_log.json joined onto /api/universe; boot maps recurrence→seen/wlb/n/pf; SeenChip in surface-signal.jsx; window.__trkIntent one-shot intent consumed by SurfaceTrackRecord</t>
+          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr"/>
@@ -16724,23 +16724,23 @@
       </c>
       <c r="L291" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M291" s="3" t="inlineStr">
         <is>
-          <t>cf702f2b4</t>
+          <t>dbbd6b5f6</t>
         </is>
       </c>
       <c r="N291" s="8" t="inlineStr"/>
     </row>
-    <row r="292" ht="120" customHeight="1">
+    <row r="292" ht="60" customHeight="1">
       <c r="A292" s="2" t="n">
         <v>291</v>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-TIER-WIRE</t>
+          <t>SCANNER-RECUR-CHIP</t>
         </is>
       </c>
       <c r="C292" s="10" t="inlineStr">
@@ -16750,39 +16750,27 @@
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Conviction</t>
+          <t>Signal Scanner</t>
         </is>
       </c>
       <c r="E292" s="6" t="inlineStr">
         <is>
-          <t>Conviction tier: simplified to score-band only</t>
+          <t>Recurrence chip</t>
         </is>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+          <t>Per-ticker 'seen N× + W-L' chip on scanner rows, deep-links to Track Record · The Ledger filtered for that ticker</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
-        </is>
-      </c>
-      <c r="H292" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs + backtest validation</t>
-        </is>
-      </c>
-      <c r="I292" s="5" t="inlineStr">
-        <is>
-          <t>Medium — changes live size or eliminates a layer</t>
-        </is>
-      </c>
-      <c r="J292" s="5" t="inlineStr">
-        <is>
-          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
-        </is>
-      </c>
+          <t>Server: _signal_recurrence_map() over signal_log.json joined onto /api/universe; boot maps recurrence→seen/wlb/n/pf; SeenChip in surface-signal.jsx; window.__trkIntent one-shot intent consumed by SurfaceTrackRecord</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr"/>
+      <c r="I292" s="5" t="inlineStr"/>
+      <c r="J292" s="5" t="inlineStr"/>
       <c r="K292" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16790,27 +16778,23 @@
       </c>
       <c r="L292" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M292" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N292" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
-        </is>
-      </c>
-    </row>
-    <row r="293" ht="75" customHeight="1">
+          <t>cf702f2b4</t>
+        </is>
+      </c>
+      <c r="N292" s="8" t="inlineStr"/>
+    </row>
+    <row r="293" ht="120" customHeight="1">
       <c r="A293" s="2" t="n">
         <v>292</v>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-Q-AB</t>
+          <t>CONVICTION-TIER-WIRE</t>
         </is>
       </c>
       <c r="C293" s="10" t="inlineStr">
@@ -16820,27 +16804,39 @@
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Gates</t>
+          <t>Strategy / Conviction</t>
         </is>
       </c>
       <c r="E293" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entry_quality A/B</t>
+          <t>Conviction tier: simplified to score-band only</t>
         </is>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
-          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
-        </is>
-      </c>
-      <c r="H293" s="2" t="inlineStr"/>
-      <c r="I293" s="5" t="inlineStr"/>
-      <c r="J293" s="5" t="inlineStr"/>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs + backtest validation</t>
+        </is>
+      </c>
+      <c r="I293" s="5" t="inlineStr">
+        <is>
+          <t>Medium — changes live size or eliminates a layer</t>
+        </is>
+      </c>
+      <c r="J293" s="5" t="inlineStr">
+        <is>
+          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
+        </is>
+      </c>
       <c r="K293" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -16848,23 +16844,27 @@
       </c>
       <c r="L293" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
-          <t>07c3af6a3</t>
-        </is>
-      </c>
-      <c r="N293" s="8" t="inlineStr"/>
-    </row>
-    <row r="294" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N293" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="75" customHeight="1">
       <c r="A294" s="2" t="n">
         <v>293</v>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-1</t>
+          <t>ENTRY-Q-AB</t>
         </is>
       </c>
       <c r="C294" s="10" t="inlineStr">
@@ -16874,22 +16874,22 @@
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Options Paper</t>
+          <t>Strategy / Gates</t>
         </is>
       </c>
       <c r="E294" s="6" t="inlineStr">
         <is>
-          <t>Signal -&gt; options-structure mapper</t>
+          <t>Regime-conditional entry_quality A/B</t>
         </is>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
+          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
+          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr"/>
@@ -16902,23 +16902,23 @@
       </c>
       <c r="L294" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
-          <t>9c3a2a58d</t>
+          <t>07c3af6a3</t>
         </is>
       </c>
       <c r="N294" s="8" t="inlineStr"/>
     </row>
-    <row r="295" ht="45" customHeight="1">
+    <row r="295" ht="60" customHeight="1">
       <c r="A295" s="2" t="n">
         <v>294</v>
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-2</t>
+          <t>OPT-PAPER-1</t>
         </is>
       </c>
       <c r="C295" s="10" t="inlineStr">
@@ -16933,17 +16933,17 @@
       </c>
       <c r="E295" s="6" t="inlineStr">
         <is>
-          <t>Contract selection from Schwab chain</t>
+          <t>Signal -&gt; options-structure mapper</t>
         </is>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
+          <t>Engine emits equity plans only; no layer maps a stock BUY to a defined-risk options structure. GATED: equity sleeves still Phase-1. See docs/scope_options_paper.md.</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
+          <t>Map equity plan -&gt; defined-risk structure by setup family / R:R / IV rank (3:1 high-conviction -&gt; debit call spread; clean trend -&gt; long call 30-45 DTE). Underlying stop = thesis invalidation. Defined-risk ONLY, paper ONLY.</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr"/>
@@ -16966,13 +16966,13 @@
       </c>
       <c r="N295" s="8" t="inlineStr"/>
     </row>
-    <row r="296" ht="60" customHeight="1">
+    <row r="296" ht="45" customHeight="1">
       <c r="A296" s="2" t="n">
         <v>295</v>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-3</t>
+          <t>OPT-PAPER-2</t>
         </is>
       </c>
       <c r="C296" s="10" t="inlineStr">
@@ -16987,17 +16987,17 @@
       </c>
       <c r="E296" s="6" t="inlineStr">
         <is>
-          <t>Alpaca paper options orders in executor.py</t>
+          <t>Contract selection from Schwab chain</t>
         </is>
       </c>
       <c r="F296" s="5" t="inlineStr">
         <is>
-          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
+          <t>We have chain+Greeks data (schwab_client.get_chains/extract_chain_greeks) but no contract picker. Dep: SCHWAB-REAUTH-PENDING (Greeks freshness).</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr">
         <is>
-          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
+          <t>Pick by delta/DTE/spread width from the Schwab chain; size on premium-at-risk &lt;=1% equity. No naked options.</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr"/>
@@ -17020,13 +17020,13 @@
       </c>
       <c r="N296" s="8" t="inlineStr"/>
     </row>
-    <row r="297" ht="45" customHeight="1">
+    <row r="297" ht="60" customHeight="1">
       <c r="A297" s="2" t="n">
         <v>296</v>
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-4</t>
+          <t>OPT-PAPER-3</t>
         </is>
       </c>
       <c r="C297" s="10" t="inlineStr">
@@ -17041,17 +17041,17 @@
       </c>
       <c r="E297" s="6" t="inlineStr">
         <is>
-          <t>Options position tracking + contract P&amp;L</t>
+          <t>Alpaca paper options orders in executor.py</t>
         </is>
       </c>
       <c r="F297" s="5" t="inlineStr">
         <is>
-          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
+          <t>executor.py has zero options code (equity brackets only); Alpaca SDK supports OptionLegRequest/GetOptionContractsRequest.</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
+          <t>Construct+submit single + vertical OptionLegRequest in executor.py, PAPER only behind the config.alpaca.paper hard guard. Never live (feedback_paper_only_automation).</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr"/>
@@ -17069,7 +17069,7 @@
       </c>
       <c r="M297" s="3" t="inlineStr">
         <is>
-          <t>635ae960f</t>
+          <t>9c3a2a58d</t>
         </is>
       </c>
       <c r="N297" s="8" t="inlineStr"/>
@@ -17080,7 +17080,7 @@
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>OPT-PAPER-5</t>
+          <t>OPT-PAPER-4</t>
         </is>
       </c>
       <c r="C298" s="10" t="inlineStr">
@@ -17095,17 +17095,17 @@
       </c>
       <c r="E298" s="6" t="inlineStr">
         <is>
-          <t>Options-specific exits</t>
+          <t>Options position tracking + contract P&amp;L</t>
         </is>
       </c>
       <c r="F298" s="5" t="inlineStr">
         <is>
-          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
+          <t>Portfolio tracker is share-P&amp;L only; can't track premium/Greeks/theta/DTE.</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
         <is>
-          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
+          <t>Extend portfolio tracker for contracts: premium, Greeks, theta decay, IV, DTE, mark-to-market.</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr"/>
@@ -17128,13 +17128,13 @@
       </c>
       <c r="N298" s="8" t="inlineStr"/>
     </row>
-    <row r="299" ht="120" customHeight="1">
+    <row r="299" ht="45" customHeight="1">
       <c r="A299" s="2" t="n">
         <v>298</v>
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>UI-STRAT-1</t>
+          <t>OPT-PAPER-5</t>
         </is>
       </c>
       <c r="C299" s="10" t="inlineStr">
@@ -17144,22 +17144,22 @@
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>Strategy Lab</t>
+          <t>Strategy / Options Paper</t>
         </is>
       </c>
       <c r="E299" s="6" t="inlineStr">
         <is>
-          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
+          <t>Options-specific exits</t>
         </is>
       </c>
       <c r="F299" s="5" t="inlineStr">
         <is>
-          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
+          <t>Equity exits are price-stop only; options need IV/theta/expiry-aware exits.</t>
         </is>
       </c>
       <c r="G299" s="5" t="inlineStr">
         <is>
-          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
+          <t>IV-crush-around-earnings rule, time-stop before expiry, profit-take on the CONTRACT not the underlying, assignment handling.</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr"/>
@@ -17172,23 +17172,23 @@
       </c>
       <c r="L299" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M299" s="3" t="inlineStr">
         <is>
-          <t>93ec11842</t>
+          <t>635ae960f</t>
         </is>
       </c>
       <c r="N299" s="8" t="inlineStr"/>
     </row>
-    <row r="300" ht="60" customHeight="1">
+    <row r="300" ht="120" customHeight="1">
       <c r="A300" s="2" t="n">
         <v>299</v>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>TE-SESSION-CACHE</t>
+          <t>UI-STRAT-1</t>
         </is>
       </c>
       <c r="C300" s="10" t="inlineStr">
@@ -17198,22 +17198,22 @@
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>Structural Targets</t>
+          <t>Strategy Lab</t>
         </is>
       </c>
       <c r="E300" s="6" t="inlineStr">
         <is>
-          <t>Session-date cache invalidation</t>
+          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
         </is>
       </c>
       <c r="F300" s="5" t="inlineStr">
         <is>
-          <t>target_engine cache used 12h wall-clock TTL → expired mid-session (15:00-19:30 PT dead-zone) causing on-demand recomputes on tab open</t>
+          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr">
         <is>
-          <t>Switched _cache_is_fresh to session-date keying (_latest_completed_session) + 36h backstop + legacy grandfather; _cache_write stamps session_date. 0 added EODHD, recompute only on new daily bar.</t>
+          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr"/>
@@ -17226,12 +17226,12 @@
       </c>
       <c r="L300" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M300" s="3" t="inlineStr">
         <is>
-          <t>33146be5e</t>
+          <t>93ec11842</t>
         </is>
       </c>
       <c r="N300" s="8" t="inlineStr"/>
@@ -17242,7 +17242,7 @@
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>TE-STRATEGY-MODE</t>
+          <t>TE-SESSION-CACHE</t>
         </is>
       </c>
       <c r="C301" s="10" t="inlineStr">
@@ -17252,22 +17252,22 @@
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>Target Engine</t>
+          <t>Structural Targets</t>
         </is>
       </c>
       <c r="E301" s="6" t="inlineStr">
         <is>
-          <t>_strategy_mode read but never written</t>
+          <t>Session-date cache invalidation</t>
         </is>
       </c>
       <c r="F301" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
+          <t>target_engine cache used 12h wall-clock TTL → expired mid-session (15:00-19:30 PT dead-zone) causing on-demand recomputes on tab open</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
+          <t>Switched _cache_is_fresh to session-date keying (_latest_completed_session) + 36h backstop + legacy grandfather; _cache_write stamps session_date. 0 added EODHD, recompute only on new daily bar.</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr"/>
@@ -17280,23 +17280,23 @@
       </c>
       <c r="L301" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M301" s="3" t="inlineStr">
         <is>
-          <t>15f8f9600</t>
+          <t>33146be5e</t>
         </is>
       </c>
       <c r="N301" s="8" t="inlineStr"/>
     </row>
-    <row r="302" ht="105" customHeight="1">
+    <row r="302" ht="60" customHeight="1">
       <c r="A302" s="2" t="n">
         <v>301</v>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>TE-STRATEGY-MODE</t>
         </is>
       </c>
       <c r="C302" s="10" t="inlineStr">
@@ -17306,31 +17306,27 @@
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>Target Engine</t>
         </is>
       </c>
       <c r="E302" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>_strategy_mode read but never written</t>
         </is>
       </c>
       <c r="F302" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>compute_trade_plan structural override read config['_strategy_mode'] which is set nowhere → override always ran mode=swing, silently mis-targeting any position/invest plan routed through it</t>
         </is>
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+          <t>promoted to discoverable strategy_mode='swing' kwarg on compute_trade_plan; config injection still wins (mirrors _regime_name convention); behavior-neutral today</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr"/>
       <c r="I302" s="5" t="inlineStr"/>
-      <c r="J302" s="5" t="inlineStr">
-        <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
-        </is>
-      </c>
+      <c r="J302" s="5" t="inlineStr"/>
       <c r="K302" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -17338,27 +17334,23 @@
       </c>
       <c r="L302" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M302" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N302" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="303" ht="135" customHeight="1">
+          <t>15f8f9600</t>
+        </is>
+      </c>
+      <c r="N302" s="8" t="inlineStr"/>
+    </row>
+    <row r="303" ht="105" customHeight="1">
       <c r="A303" s="2" t="n">
         <v>302</v>
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>TRACKER-BUY-FILTER</t>
         </is>
       </c>
       <c r="C303" s="10" t="inlineStr">
@@ -17368,37 +17360,29 @@
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Tracker/Feedback Loop</t>
         </is>
       </c>
       <c r="E303" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
         </is>
       </c>
       <c r="F303" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H303" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I303" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr"/>
+      <c r="I303" s="5" t="inlineStr"/>
       <c r="J303" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
         </is>
       </c>
       <c r="K303" s="12" t="inlineStr">
@@ -17408,27 +17392,27 @@
       </c>
       <c r="L303" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M303" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N303" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="304" ht="45" customHeight="1">
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="135" customHeight="1">
       <c r="A304" s="2" t="n">
         <v>303</v>
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-BOOK-RISK</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C304" s="10" t="inlineStr">
@@ -17438,27 +17422,39 @@
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Risk</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E304" s="6" t="inlineStr">
         <is>
-          <t>Book Risk surface + per-lens analytics (§6)</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F304" s="5" t="inlineStr">
         <is>
-          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
-        </is>
-      </c>
-      <c r="H304" s="2" t="inlineStr"/>
-      <c r="I304" s="5" t="inlineStr"/>
-      <c r="J304" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I304" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J304" s="5" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+        </is>
+      </c>
       <c r="K304" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -17466,23 +17462,27 @@
       </c>
       <c r="L304" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M304" s="3" t="inlineStr">
         <is>
-          <t>50cace567</t>
-        </is>
-      </c>
-      <c r="N304" s="8" t="inlineStr"/>
-    </row>
-    <row r="305" ht="120" customHeight="1">
+          <t>42c36ef91</t>
+        </is>
+      </c>
+      <c r="N304" s="8" t="inlineStr">
+        <is>
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="45" customHeight="1">
       <c r="A305" s="2" t="n">
         <v>304</v>
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
+          <t>STOCKSMITH-BOOK-RISK</t>
         </is>
       </c>
       <c r="C305" s="10" t="inlineStr">
@@ -17492,31 +17492,27 @@
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>V2 Dashboard / Risk</t>
         </is>
       </c>
       <c r="E305" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Book Risk surface + per-lens analytics (§6)</t>
         </is>
       </c>
       <c r="F305" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
         </is>
       </c>
       <c r="G305" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr"/>
       <c r="I305" s="5" t="inlineStr"/>
-      <c r="J305" s="5" t="inlineStr">
-        <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
-        </is>
-      </c>
+      <c r="J305" s="5" t="inlineStr"/>
       <c r="K305" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -17524,27 +17520,23 @@
       </c>
       <c r="L305" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M305" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N305" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="306" ht="60" customHeight="1">
+          <t>50cace567</t>
+        </is>
+      </c>
+      <c r="N305" s="8" t="inlineStr"/>
+    </row>
+    <row r="306" ht="120" customHeight="1">
       <c r="A306" s="2" t="n">
         <v>305</v>
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-TAB</t>
+          <t>RECENCY-FLOOR</t>
         </is>
       </c>
       <c r="C306" s="10" t="inlineStr">
@@ -17554,27 +17546,31 @@
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Momentum</t>
+          <t>Validation Hygiene</t>
         </is>
       </c>
       <c r="E306" s="6" t="inlineStr">
         <is>
-          <t>New 🚀 Momentum workspace tab</t>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
         </is>
       </c>
       <c r="F306" s="5" t="inlineStr">
         <is>
-          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
         </is>
       </c>
       <c r="G306" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr"/>
       <c r="I306" s="5" t="inlineStr"/>
-      <c r="J306" s="5" t="inlineStr"/>
+      <c r="J306" s="5" t="inlineStr">
+        <is>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+        </is>
+      </c>
       <c r="K306" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -17582,15 +17578,19 @@
       </c>
       <c r="L306" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N306" s="8" t="inlineStr"/>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N306" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="60" customHeight="1">
       <c r="A307" s="2" t="n">
@@ -17598,7 +17598,7 @@
       </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-QUICK-PANELS</t>
+          <t>MOMENTUM-TAB</t>
         </is>
       </c>
       <c r="C307" s="10" t="inlineStr">
@@ -17608,22 +17608,22 @@
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Signal Scanner</t>
+          <t>Workspaces / Momentum</t>
         </is>
       </c>
       <c r="E307" s="6" t="inlineStr">
         <is>
-          <t>5 quick-glance panels above watchlist table</t>
+          <t>New 🚀 Momentum workspace tab</t>
         </is>
       </c>
       <c r="F307" s="5" t="inlineStr">
         <is>
-          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
+          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
         </is>
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr"/>
@@ -17641,60 +17641,48 @@
       </c>
       <c r="M307" s="3" t="inlineStr">
         <is>
-          <t>dfbe955fe</t>
+          <t>27fd646b1</t>
         </is>
       </c>
       <c r="N307" s="8" t="inlineStr"/>
     </row>
-    <row r="308" ht="45" customHeight="1">
+    <row r="308" ht="60" customHeight="1">
       <c r="A308" s="2" t="n">
         <v>307</v>
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C308" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SCANNER-QUICK-PANELS</t>
+        </is>
+      </c>
+      <c r="C308" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Workspaces / Signal Scanner</t>
         </is>
       </c>
       <c r="E308" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>5 quick-glance panels above watchlist table</t>
         </is>
       </c>
       <c r="F308" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
         </is>
       </c>
       <c r="G308" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H308" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I308" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
-      <c r="J308" s="5" t="inlineStr">
-        <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
-        </is>
-      </c>
+          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr"/>
+      <c r="I308" s="5" t="inlineStr"/>
+      <c r="J308" s="5" t="inlineStr"/>
       <c r="K308" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -17702,15 +17690,15 @@
       </c>
       <c r="L308" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M308" s="3" t="inlineStr"/>
-      <c r="N308" s="8" t="inlineStr">
-        <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M308" s="3" t="inlineStr">
+        <is>
+          <t>dfbe955fe</t>
+        </is>
+      </c>
+      <c r="N308" s="8" t="inlineStr"/>
     </row>
     <row r="309" ht="45" customHeight="1">
       <c r="A309" s="2" t="n">
@@ -17718,7 +17706,7 @@
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C309" s="13" t="inlineStr">
@@ -17733,32 +17721,32 @@
       </c>
       <c r="E309" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F309" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I309" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J309" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
         </is>
       </c>
       <c r="K309" s="12" t="inlineStr">
@@ -17774,7 +17762,7 @@
       <c r="M309" s="3" t="inlineStr"/>
       <c r="N309" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -17784,7 +17772,7 @@
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="C310" s="13" t="inlineStr">
@@ -17794,35 +17782,39 @@
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E310" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F310" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I310" s="5" t="inlineStr">
         <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
-      <c r="J310" s="5" t="inlineStr"/>
+          <t>Win: confirms infrastructure still healthy.</t>
+        </is>
+      </c>
+      <c r="J310" s="5" t="inlineStr">
+        <is>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
       <c r="K310" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -17830,17 +17822,13 @@
       </c>
       <c r="L310" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M310" s="3" t="inlineStr">
-        <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M310" s="3" t="inlineStr"/>
       <c r="N310" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -17850,59 +17838,63 @@
       </c>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C311" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C311" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E311" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Remove emoji icons from Thesis + Research labels</t>
         </is>
       </c>
       <c r="F311" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
         </is>
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I311" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
-        </is>
-      </c>
-      <c r="J311" s="5" t="inlineStr">
-        <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K311" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L311" s="2" t="inlineStr"/>
-      <c r="M311" s="3" t="inlineStr"/>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J311" s="5" t="inlineStr"/>
+      <c r="K311" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L311" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M311" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
       <c r="N311" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
         </is>
       </c>
     </row>
@@ -17912,7 +17904,7 @@
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>CLEAN-2</t>
         </is>
       </c>
       <c r="C312" s="10" t="inlineStr">
@@ -17922,37 +17914,37 @@
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E312" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F312" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I312" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J312" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
+          <t>Standard data-migration retention practice.</t>
         </is>
       </c>
       <c r="K312" s="14" t="inlineStr">
@@ -17974,109 +17966,109 @@
       </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C313" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C313" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E313" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F313" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I313" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J313" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K313" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K313" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="L313" s="2" t="inlineStr"/>
       <c r="M313" s="3" t="inlineStr"/>
       <c r="N313" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="314" ht="75" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="45" customHeight="1">
       <c r="A314" s="2" t="n">
         <v>313</v>
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C314" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C314" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E314" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
         </is>
       </c>
       <c r="F314" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
         </is>
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I314" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J314" s="5" t="inlineStr">
         <is>
-          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+          <t>Agents skim and miss post-filter subset analysis.</t>
         </is>
       </c>
       <c r="K314" s="15" t="inlineStr">
@@ -18084,147 +18076,209 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L314" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+      <c r="L314" s="2" t="inlineStr"/>
       <c r="M314" s="3" t="inlineStr"/>
       <c r="N314" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="315" ht="195" customHeight="1">
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="75" customHeight="1">
       <c r="A315" s="2" t="n">
         <v>314</v>
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C315" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D315" s="5" t="inlineStr">
+        <is>
+          <t>UI / Modularization</t>
+        </is>
+      </c>
+      <c r="E315" s="6" t="inlineStr">
+        <is>
+          <t>Pixel-diff regression baseline</t>
+        </is>
+      </c>
+      <c r="F315" s="5" t="inlineStr">
+        <is>
+          <t>After modularization, no automated visual-regression catch.</t>
+        </is>
+      </c>
+      <c r="G315" s="5" t="inlineStr">
+        <is>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I315" s="5" t="inlineStr">
+        <is>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
+      <c r="J315" s="5" t="inlineStr">
+        <is>
+          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+        </is>
+      </c>
+      <c r="K315" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L315" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M315" s="3" t="inlineStr"/>
+      <c r="N315" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="195" customHeight="1">
+      <c r="A316" s="2" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
           <t>OB-CONFLUENCE-PROPOSAL-REJECTED</t>
         </is>
       </c>
-      <c r="C315" s="10" t="inlineStr">
+      <c r="C316" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D315" s="5" t="inlineStr">
+      <c r="D316" s="5" t="inlineStr">
         <is>
           <t>Signals / Cross-Check</t>
         </is>
       </c>
-      <c r="E315" s="6" t="inlineStr">
+      <c r="E316" s="6" t="inlineStr">
         <is>
           <t>OB-confluence Wilson bump + OB-aware stop — proposals KILLED by backtest evidence</t>
         </is>
       </c>
-      <c r="F315" s="5" t="inlineStr">
+      <c r="F316" s="5" t="inlineStr">
         <is>
           <t>User asked 2026-05-12 to ship #2 (Wilson-bump score factor for bullish OB confluence within 5% of entry) and #5 (OB-low as stop instead of 1.25xATR). Per Principle 1 / Principle 7, ran post-hoc validation: scripts/validate_ob_confluence.py retroactively tags every closed trade from existing portfolio_backtest outputs with SMC state at entry date, computes Wilson 95% LB per subset.
 RESULT (750-day backtest · n=384): Bull OB confluence within 5% of entry DECREASES Wilson LB by -8.6pp (14.6% vs baseline 23.1%). BOS-bullish boost: -3.4pp. SMC-bullish direction boost: -3.6pp. Per #5 simulation, 35 of 39 (90%) OB-low-as-stop would have loosened the stop; 25 of those still ended in losses (looser stops do not rescue broken setups, they extend exposure).
 Principle 4 fires: proposals FALSIFIED, killed permanently (not retuned). Doing the change without this validation would have introduced a 6-9pp Wilson-LB drag on every BUY signal.</t>
         </is>
       </c>
-      <c r="G315" s="5" t="inlineStr">
+      <c r="G316" s="5" t="inlineStr">
         <is>
           <t>Built scripts/validate_ob_confluence.py to retroactively run smart_money.score_smc() on the historical OHLCV at each trade's entry date, tag with OB-confluence + BOS + CHoCH flags, compute Wilson 95% LB per subset, and apply Principle 1 gates (n&gt;=30, lift&gt;=5pp). Cross-validated on 250d (n=142) and 750d (n=384) backtest outputs. Both agree: NO EDGE.</t>
         </is>
       </c>
-      <c r="H315" s="2" t="inlineStr">
+      <c r="H316" s="2" t="inlineStr">
         <is>
           <t>Days of work avoided (would have shipped a degrading change).</t>
         </is>
       </c>
-      <c r="I315" s="5" t="inlineStr">
+      <c r="I316" s="5" t="inlineStr">
         <is>
           <t>Mechanism (Principle 2): institutional OBs are supposed to mark re-add zones for smart money. Falsification (Principle 4): if the data doesn't show OB-confluent trades winning more, the mechanism either doesn't exist for retail-accessible OB detection at daily resolution OR is already priced into our 5-pillar score. Either way: ship nothing. The proposals are dead. Win: prevented a 6-9pp Wilson-LB drag from being added to live scoring. Lost: nothing — we didn't change live scoring, no opportunity cost.</t>
         </is>
       </c>
-      <c r="J315" s="5" t="inlineStr">
+      <c r="J316" s="5" t="inlineStr">
         <is>
           <t>Validator script is reusable infrastructure. Re-run any time the SMC detection logic or score thresholds change. NOTE: baseline WR in 750d backtest is 27.3% (low) — the absolute level reflects backtest-window-specific market conditions; the SUBSET comparisons are valid regardless because they share the same baseline. Do not interpret 23.1% Wilson LB as a system-level edge — that's a separate question. This validation answers ONLY: does OB-confluence improve selection within whatever the system already does.</t>
         </is>
       </c>
-      <c r="K315" s="15" t="inlineStr">
+      <c r="K316" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L315" s="2" t="inlineStr">
+      <c r="L316" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="M315" s="3" t="inlineStr"/>
-      <c r="N315" s="8" t="inlineStr">
-        <is>
-          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="316" ht="90" customHeight="1">
-      <c r="A316" s="2" t="n">
-        <v>315</v>
-      </c>
-      <c r="B316" s="3" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C316" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="D316" s="5" t="inlineStr">
-        <is>
-          <t>Data / Universe</t>
-        </is>
-      </c>
-      <c r="E316" s="6" t="inlineStr">
-        <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
-        </is>
-      </c>
-      <c r="F316" s="5" t="inlineStr">
-        <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
-        </is>
-      </c>
-      <c r="G316" s="5" t="inlineStr">
-        <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
-        </is>
-      </c>
-      <c r="H316" s="2" t="inlineStr">
-        <is>
-          <t>$$ + 1 day</t>
-        </is>
-      </c>
-      <c r="I316" s="5" t="inlineStr">
-        <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
-        </is>
-      </c>
-      <c r="J316" s="5" t="inlineStr">
-        <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
-        </is>
-      </c>
-      <c r="K316" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L316" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M316" s="3" t="inlineStr"/>
       <c r="N316" s="8" t="inlineStr">
+        <is>
+          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="90" customHeight="1">
+      <c r="A317" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C317" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E317" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F317" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G317" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I317" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J317" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K317" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L317" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M317" s="3" t="inlineStr"/>
+      <c r="N317" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -18329,10 +18383,10 @@
         <v>91</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5">
@@ -18386,10 +18440,10 @@
         <v>116</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
